--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7958,7 +7958,7 @@
         <v>129271581</v>
       </c>
       <c r="B67" t="n">
-        <v>92863</v>
+        <v>92866</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7958,7 +7958,7 @@
         <v>129271581</v>
       </c>
       <c r="B67" t="n">
-        <v>92866</v>
+        <v>92894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7958,7 +7958,7 @@
         <v>129271581</v>
       </c>
       <c r="B67" t="n">
-        <v>92894</v>
+        <v>92900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -7958,7 +7958,7 @@
         <v>129271581</v>
       </c>
       <c r="B67" t="n">
-        <v>92900</v>
+        <v>92901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AY122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8054,6 +8054,5974 @@
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>129944164</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>471363</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6770736</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129944452</v>
+      </c>
+      <c r="B69" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>471330</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6770712</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129944454</v>
+      </c>
+      <c r="B70" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>471330</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6770712</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129944817</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>471247</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6770726</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129944495</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>471288</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6770728</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129946408</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>470921</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6770579</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129946062</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>471161</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6770705</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129946170</v>
+      </c>
+      <c r="B75" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>471030</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6770688</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129946586</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>471095</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6770660</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129944813</v>
+      </c>
+      <c r="B77" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>471248</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6770737</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129944762</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>471276</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6770703</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129946436</v>
+      </c>
+      <c r="B79" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>470971</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6770603</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129945104</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>471219</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6770720</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129946182</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>471000</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6770675</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129944210</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>471390</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6770705</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129944037</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>471417</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6770738</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129946321</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>470871</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6770635</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129946047</v>
+      </c>
+      <c r="B85" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>471161</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6770705</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129946029</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>471185</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6770690</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129944466</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>471322</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6770702</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129945509</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>471198</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6770689</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129944473</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>471328</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6770726</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129946708</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>471171</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6770660</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129944975</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>471242</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6770682</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129945161</v>
+      </c>
+      <c r="B92" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>471198</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6770725</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129943855</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>471451</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6770706</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129945066</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>471239</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6770732</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129944756</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>471288</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6770685</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129944878</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>471258</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6770712</v>
+      </c>
+      <c r="S96" t="n">
+        <v>50</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129946391</v>
+      </c>
+      <c r="B97" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>470921</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6770579</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129946444</v>
+      </c>
+      <c r="B98" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>470971</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6770603</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129944926</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>471263</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6770694</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129945156</v>
+      </c>
+      <c r="B100" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>471198</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6770725</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129944544</v>
+      </c>
+      <c r="B101" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>471330</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6770712</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129943809</v>
+      </c>
+      <c r="B102" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>471447</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6770716</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>129945457</v>
+      </c>
+      <c r="B103" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>471189</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6770706</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>129944062</v>
+      </c>
+      <c r="B104" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>471432</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6770716</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129943541</v>
+      </c>
+      <c r="B105" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>471478</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6770707</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129943849</v>
+      </c>
+      <c r="B106" t="n">
+        <v>91620</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>471451</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6770706</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>129943914</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>471432</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6770701</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129944178</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>471372</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6770719</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>129944592</v>
+      </c>
+      <c r="B109" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>471313</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6770688</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>129944488</v>
+      </c>
+      <c r="B110" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>471318</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6770729</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>129943763</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>471466</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6770713</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>129944804</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>471271</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6770733</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>129946334</v>
+      </c>
+      <c r="B113" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>470871</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6770635</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>129946197</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>470971</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6770676</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>129946117</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>471106</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6770711</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>129943529</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>471492</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6770712</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>129945078</v>
+      </c>
+      <c r="B117" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>471209</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6770731</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129946365</v>
+      </c>
+      <c r="B118" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>470910</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6770605</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>129944158</v>
+      </c>
+      <c r="B119" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>471363</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6770736</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>129944523</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>471303</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6770699</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>129945444</v>
+      </c>
+      <c r="B121" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>471189</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6770706</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>129945440</v>
+      </c>
+      <c r="B122" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Svenlindor, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>471189</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6770706</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -8056,10 +8056,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129944452</v>
+        <v>129944495</v>
       </c>
       <c r="B68" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8067,39 +8067,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471330</v>
+        <v>471288</v>
       </c>
       <c r="R68" t="n">
-        <v>6770712</v>
+        <v>6770728</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8168,7 +8163,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129944817</v>
+        <v>129946062</v>
       </c>
       <c r="B69" t="n">
         <v>79084</v>
@@ -8203,10 +8198,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471247</v>
+        <v>471161</v>
       </c>
       <c r="R69" t="n">
-        <v>6770726</v>
+        <v>6770705</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8275,7 +8270,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129944495</v>
+        <v>129946408</v>
       </c>
       <c r="B70" t="n">
         <v>79084</v>
@@ -8310,10 +8305,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471288</v>
+        <v>470921</v>
       </c>
       <c r="R70" t="n">
-        <v>6770728</v>
+        <v>6770579</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8382,7 +8377,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129946062</v>
+        <v>129944164</v>
       </c>
       <c r="B71" t="n">
         <v>79084</v>
@@ -8417,10 +8412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471161</v>
+        <v>471363</v>
       </c>
       <c r="R71" t="n">
-        <v>6770705</v>
+        <v>6770736</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8489,7 +8484,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129946408</v>
+        <v>129944817</v>
       </c>
       <c r="B72" t="n">
         <v>79084</v>
@@ -8524,10 +8519,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470921</v>
+        <v>471247</v>
       </c>
       <c r="R72" t="n">
-        <v>6770579</v>
+        <v>6770726</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8596,10 +8591,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129944164</v>
+        <v>129944452</v>
       </c>
       <c r="B73" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8607,34 +8602,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471363</v>
+        <v>471330</v>
       </c>
       <c r="R73" t="n">
-        <v>6770736</v>
+        <v>6770712</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9676,32 +9676,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944037</v>
+        <v>129946047</v>
       </c>
       <c r="B83" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471417</v>
+        <v>471161</v>
       </c>
       <c r="R83" t="n">
-        <v>6770738</v>
+        <v>6770705</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944210</v>
+        <v>129944037</v>
       </c>
       <c r="B84" t="n">
         <v>79084</v>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471390</v>
+        <v>471417</v>
       </c>
       <c r="R84" t="n">
-        <v>6770705</v>
+        <v>6770738</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9890,32 +9890,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129946047</v>
+        <v>129944210</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471161</v>
+        <v>471390</v>
       </c>
       <c r="R85" t="n">
         <v>6770705</v>
@@ -9997,7 +9997,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129945509</v>
+        <v>129946029</v>
       </c>
       <c r="B86" t="n">
         <v>79084</v>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471198</v>
+        <v>471185</v>
       </c>
       <c r="R86" t="n">
-        <v>6770689</v>
+        <v>6770690</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10078,11 +10078,6 @@
       <c r="AB86" t="inlineStr">
         <is>
           <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10109,7 +10104,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129946029</v>
+        <v>129944466</v>
       </c>
       <c r="B87" t="n">
         <v>79084</v>
@@ -10144,10 +10139,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471185</v>
+        <v>471322</v>
       </c>
       <c r="R87" t="n">
-        <v>6770690</v>
+        <v>6770702</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10216,7 +10211,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129944466</v>
+        <v>129945509</v>
       </c>
       <c r="B88" t="n">
         <v>79084</v>
@@ -10251,10 +10246,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471322</v>
+        <v>471198</v>
       </c>
       <c r="R88" t="n">
-        <v>6770702</v>
+        <v>6770689</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10297,6 +10292,11 @@
       <c r="AB88" t="inlineStr">
         <is>
           <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10430,45 +10430,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129944975</v>
+        <v>129945161</v>
       </c>
       <c r="B90" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471242</v>
+        <v>471198</v>
       </c>
       <c r="R90" t="n">
-        <v>6770682</v>
+        <v>6770725</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10537,7 +10542,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129946708</v>
+        <v>129944975</v>
       </c>
       <c r="B91" t="n">
         <v>79084</v>
@@ -10572,10 +10577,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471171</v>
+        <v>471242</v>
       </c>
       <c r="R91" t="n">
-        <v>6770660</v>
+        <v>6770682</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10644,50 +10649,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129945161</v>
+        <v>129946708</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471198</v>
+        <v>471171</v>
       </c>
       <c r="R92" t="n">
-        <v>6770725</v>
+        <v>6770660</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129946391</v>
+        <v>129944878</v>
       </c>
       <c r="B93" t="n">
-        <v>57734</v>
+        <v>57895</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10767,27 +10767,31 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10796,13 +10800,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>470921</v>
+        <v>471258</v>
       </c>
       <c r="R93" t="n">
-        <v>6770579</v>
+        <v>6770712</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10868,7 +10872,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129945066</v>
+        <v>129943855</v>
       </c>
       <c r="B94" t="n">
         <v>79084</v>
@@ -10903,10 +10907,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471239</v>
+        <v>471451</v>
       </c>
       <c r="R94" t="n">
-        <v>6770732</v>
+        <v>6770706</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10975,10 +10979,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129944878</v>
+        <v>129945066</v>
       </c>
       <c r="B95" t="n">
-        <v>57895</v>
+        <v>79084</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10986,46 +10990,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471258</v>
+        <v>471239</v>
       </c>
       <c r="R95" t="n">
-        <v>6770712</v>
+        <v>6770732</v>
       </c>
       <c r="S95" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11091,50 +11086,45 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129946444</v>
+        <v>129944756</v>
       </c>
       <c r="B96" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>470971</v>
+        <v>471288</v>
       </c>
       <c r="R96" t="n">
-        <v>6770603</v>
+        <v>6770685</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11203,10 +11193,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129943855</v>
+        <v>129946391</v>
       </c>
       <c r="B97" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11214,34 +11204,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471451</v>
+        <v>470921</v>
       </c>
       <c r="R97" t="n">
-        <v>6770706</v>
+        <v>6770579</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11310,45 +11305,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129944756</v>
+        <v>129946444</v>
       </c>
       <c r="B98" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471288</v>
+        <v>470971</v>
       </c>
       <c r="R98" t="n">
-        <v>6770685</v>
+        <v>6770603</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11417,10 +11417,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129945156</v>
+        <v>129944926</v>
       </c>
       <c r="B99" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11428,39 +11428,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471198</v>
+        <v>471263</v>
       </c>
       <c r="R99" t="n">
-        <v>6770725</v>
+        <v>6770694</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11529,7 +11524,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944926</v>
+        <v>129944544</v>
       </c>
       <c r="B100" t="n">
         <v>79084</v>
@@ -11564,10 +11559,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471263</v>
+        <v>471330</v>
       </c>
       <c r="R100" t="n">
-        <v>6770694</v>
+        <v>6770712</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11636,10 +11631,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129944544</v>
+        <v>129945156</v>
       </c>
       <c r="B101" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11647,34 +11642,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471330</v>
+        <v>471198</v>
       </c>
       <c r="R101" t="n">
-        <v>6770712</v>
+        <v>6770725</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12069,7 +12069,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129943914</v>
+        <v>129944178</v>
       </c>
       <c r="B105" t="n">
         <v>79084</v>
@@ -12104,10 +12104,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471432</v>
+        <v>471372</v>
       </c>
       <c r="R105" t="n">
-        <v>6770701</v>
+        <v>6770719</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129943849</v>
+        <v>129943914</v>
       </c>
       <c r="B106" t="n">
-        <v>91623</v>
+        <v>79084</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12187,38 +12187,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471451</v>
+        <v>471432</v>
       </c>
       <c r="R106" t="n">
-        <v>6770706</v>
+        <v>6770701</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12287,7 +12283,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129944178</v>
+        <v>129944488</v>
       </c>
       <c r="B107" t="n">
         <v>79084</v>
@@ -12322,10 +12318,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471372</v>
+        <v>471318</v>
       </c>
       <c r="R107" t="n">
-        <v>6770719</v>
+        <v>6770729</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12394,7 +12390,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129944488</v>
+        <v>129943541</v>
       </c>
       <c r="B108" t="n">
         <v>79084</v>
@@ -12429,10 +12425,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471318</v>
+        <v>471478</v>
       </c>
       <c r="R108" t="n">
-        <v>6770729</v>
+        <v>6770707</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12501,7 +12497,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129943541</v>
+        <v>129944592</v>
       </c>
       <c r="B109" t="n">
         <v>79084</v>
@@ -12536,10 +12532,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471478</v>
+        <v>471313</v>
       </c>
       <c r="R109" t="n">
-        <v>6770707</v>
+        <v>6770688</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12608,10 +12604,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129944592</v>
+        <v>129943849</v>
       </c>
       <c r="B110" t="n">
-        <v>79084</v>
+        <v>91623</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12619,34 +12615,38 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471313</v>
+        <v>471451</v>
       </c>
       <c r="R110" t="n">
-        <v>6770688</v>
+        <v>6770706</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13362,10 +13362,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129946365</v>
+        <v>129945078</v>
       </c>
       <c r="B117" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13373,39 +13373,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>470910</v>
+        <v>471209</v>
       </c>
       <c r="R117" t="n">
-        <v>6770605</v>
+        <v>6770731</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13474,10 +13469,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129945078</v>
+        <v>129946365</v>
       </c>
       <c r="B118" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13485,34 +13480,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>471209</v>
+        <v>470910</v>
       </c>
       <c r="R118" t="n">
-        <v>6770731</v>
+        <v>6770605</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14024,7 +14024,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129957713</v>
+        <v>129960901</v>
       </c>
       <c r="B123" t="n">
         <v>79084</v>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>470904</v>
+        <v>471185</v>
       </c>
       <c r="R123" t="n">
-        <v>6770718</v>
+        <v>6770590</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14131,10 +14131,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129962374</v>
+        <v>129959787</v>
       </c>
       <c r="B124" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14142,39 +14142,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
-      <c r="M124" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P124" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>470996</v>
+        <v>470900</v>
       </c>
       <c r="R124" t="n">
-        <v>6770611</v>
+        <v>6770473</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14243,50 +14238,45 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129962376</v>
+        <v>129957713</v>
       </c>
       <c r="B125" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470996</v>
+        <v>470904</v>
       </c>
       <c r="R125" t="n">
-        <v>6770611</v>
+        <v>6770718</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14355,7 +14345,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129954413</v>
+        <v>129958842</v>
       </c>
       <c r="B126" t="n">
         <v>79084</v>
@@ -14390,10 +14380,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>471028</v>
+        <v>470820</v>
       </c>
       <c r="R126" t="n">
-        <v>6770675</v>
+        <v>6770624</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14462,7 +14452,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129960901</v>
+        <v>129959479</v>
       </c>
       <c r="B127" t="n">
         <v>79084</v>
@@ -14497,10 +14487,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>471185</v>
+        <v>470837</v>
       </c>
       <c r="R127" t="n">
-        <v>6770590</v>
+        <v>6770498</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14569,7 +14559,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129960002</v>
+        <v>129954413</v>
       </c>
       <c r="B128" t="n">
         <v>79084</v>
@@ -14604,10 +14594,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470932</v>
+        <v>471028</v>
       </c>
       <c r="R128" t="n">
-        <v>6770480</v>
+        <v>6770675</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14676,7 +14666,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129959787</v>
+        <v>129959122</v>
       </c>
       <c r="B129" t="n">
         <v>79084</v>
@@ -14711,10 +14701,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470900</v>
+        <v>470926</v>
       </c>
       <c r="R129" t="n">
-        <v>6770473</v>
+        <v>6770613</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14890,7 +14880,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129958842</v>
+        <v>129960002</v>
       </c>
       <c r="B131" t="n">
         <v>79084</v>
@@ -14925,10 +14915,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470820</v>
+        <v>470932</v>
       </c>
       <c r="R131" t="n">
-        <v>6770624</v>
+        <v>6770480</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15104,10 +15094,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129959479</v>
+        <v>129962374</v>
       </c>
       <c r="B133" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15115,34 +15105,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>470837</v>
+        <v>470996</v>
       </c>
       <c r="R133" t="n">
-        <v>6770498</v>
+        <v>6770611</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15211,45 +15206,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129959122</v>
+        <v>129962376</v>
       </c>
       <c r="B134" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>470926</v>
+        <v>470996</v>
       </c>
       <c r="R134" t="n">
-        <v>6770613</v>
+        <v>6770611</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15318,45 +15318,50 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129959047</v>
+        <v>129959110</v>
       </c>
       <c r="B135" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470908</v>
+        <v>470926</v>
       </c>
       <c r="R135" t="n">
-        <v>6770622</v>
+        <v>6770613</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15532,50 +15537,45 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129959110</v>
+        <v>129954531</v>
       </c>
       <c r="B137" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P137" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470926</v>
+        <v>471106</v>
       </c>
       <c r="R137" t="n">
-        <v>6770613</v>
+        <v>6770683</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15644,7 +15644,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129954531</v>
+        <v>129958010</v>
       </c>
       <c r="B138" t="n">
         <v>79084</v>
@@ -15679,10 +15679,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>471106</v>
+        <v>470894</v>
       </c>
       <c r="R138" t="n">
-        <v>6770683</v>
+        <v>6770713</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15751,7 +15751,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129961622</v>
+        <v>129958895</v>
       </c>
       <c r="B139" t="n">
         <v>79084</v>
@@ -15786,10 +15786,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>471262</v>
+        <v>470887</v>
       </c>
       <c r="R139" t="n">
-        <v>6770622</v>
+        <v>6770658</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15858,7 +15858,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129958895</v>
+        <v>129959047</v>
       </c>
       <c r="B140" t="n">
         <v>79084</v>
@@ -15893,10 +15893,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470887</v>
+        <v>470908</v>
       </c>
       <c r="R140" t="n">
-        <v>6770658</v>
+        <v>6770622</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15965,7 +15965,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129955100</v>
+        <v>129961622</v>
       </c>
       <c r="B141" t="n">
         <v>79084</v>
@@ -16000,10 +16000,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>470981</v>
+        <v>471262</v>
       </c>
       <c r="R141" t="n">
-        <v>6770691</v>
+        <v>6770622</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16072,7 +16072,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129958010</v>
+        <v>129958499</v>
       </c>
       <c r="B142" t="n">
         <v>79084</v>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>470894</v>
+        <v>470850</v>
       </c>
       <c r="R142" t="n">
-        <v>6770713</v>
+        <v>6770690</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16179,7 +16179,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129958499</v>
+        <v>129955100</v>
       </c>
       <c r="B143" t="n">
         <v>79084</v>
@@ -16214,10 +16214,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>470850</v>
+        <v>470981</v>
       </c>
       <c r="R143" t="n">
-        <v>6770690</v>
+        <v>6770691</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16286,45 +16286,50 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129958802</v>
+        <v>129960827</v>
       </c>
       <c r="B144" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>470858</v>
+        <v>471078</v>
       </c>
       <c r="R144" t="n">
-        <v>6770602</v>
+        <v>6770561</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16393,10 +16398,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129962430</v>
+        <v>129958802</v>
       </c>
       <c r="B145" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16404,39 +16409,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>470989</v>
+        <v>470858</v>
       </c>
       <c r="R145" t="n">
-        <v>6770629</v>
+        <v>6770602</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16612,10 +16612,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129962343</v>
+        <v>129959352</v>
       </c>
       <c r="B147" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16623,39 +16623,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>471017</v>
+        <v>470879</v>
       </c>
       <c r="R147" t="n">
-        <v>6770613</v>
+        <v>6770545</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16724,50 +16719,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129960827</v>
+        <v>129958937</v>
       </c>
       <c r="B148" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>471078</v>
+        <v>470897</v>
       </c>
       <c r="R148" t="n">
-        <v>6770561</v>
+        <v>6770647</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16836,7 +16826,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129958937</v>
+        <v>129962073</v>
       </c>
       <c r="B149" t="n">
         <v>79084</v>
@@ -16871,10 +16861,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>470897</v>
+        <v>471222</v>
       </c>
       <c r="R149" t="n">
-        <v>6770647</v>
+        <v>6770635</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16943,10 +16933,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129962073</v>
+        <v>129962430</v>
       </c>
       <c r="B150" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16954,34 +16944,39 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>471222</v>
+        <v>470989</v>
       </c>
       <c r="R150" t="n">
-        <v>6770635</v>
+        <v>6770629</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17050,10 +17045,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129959352</v>
+        <v>129962343</v>
       </c>
       <c r="B151" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17061,34 +17056,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>470879</v>
+        <v>471017</v>
       </c>
       <c r="R151" t="n">
-        <v>6770545</v>
+        <v>6770613</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17264,7 +17264,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129954408</v>
+        <v>129954803</v>
       </c>
       <c r="B153" t="n">
         <v>79084</v>
@@ -17299,10 +17299,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>471019</v>
+        <v>470938</v>
       </c>
       <c r="R153" t="n">
-        <v>6770666</v>
+        <v>6770693</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17371,7 +17371,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129954803</v>
+        <v>129954408</v>
       </c>
       <c r="B154" t="n">
         <v>79084</v>
@@ -17406,10 +17406,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>470938</v>
+        <v>471019</v>
       </c>
       <c r="R154" t="n">
-        <v>6770693</v>
+        <v>6770666</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17478,7 +17478,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129958545</v>
+        <v>129959294</v>
       </c>
       <c r="B155" t="n">
         <v>79084</v>
@@ -17513,10 +17513,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470877</v>
+        <v>470904</v>
       </c>
       <c r="R155" t="n">
-        <v>6770687</v>
+        <v>6770537</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17585,7 +17585,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129959294</v>
+        <v>129958545</v>
       </c>
       <c r="B156" t="n">
         <v>79084</v>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>470904</v>
+        <v>470877</v>
       </c>
       <c r="R156" t="n">
-        <v>6770537</v>
+        <v>6770687</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17692,7 +17692,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129958754</v>
+        <v>129959389</v>
       </c>
       <c r="B157" t="n">
         <v>79084</v>
@@ -17727,10 +17727,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>470817</v>
+        <v>470824</v>
       </c>
       <c r="R157" t="n">
-        <v>6770608</v>
+        <v>6770523</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17799,7 +17799,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129959389</v>
+        <v>129959519</v>
       </c>
       <c r="B158" t="n">
         <v>79084</v>
@@ -17834,10 +17834,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470824</v>
+        <v>470822</v>
       </c>
       <c r="R158" t="n">
-        <v>6770523</v>
+        <v>6770452</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17906,7 +17906,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129959519</v>
+        <v>129954452</v>
       </c>
       <c r="B159" t="n">
         <v>79084</v>
@@ -17941,10 +17941,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>470822</v>
+        <v>471058</v>
       </c>
       <c r="R159" t="n">
-        <v>6770452</v>
+        <v>6770677</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18120,7 +18120,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129954452</v>
+        <v>129960763</v>
       </c>
       <c r="B161" t="n">
         <v>79084</v>
@@ -18155,10 +18155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>471058</v>
+        <v>471062</v>
       </c>
       <c r="R161" t="n">
-        <v>6770677</v>
+        <v>6770538</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18227,10 +18227,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129960763</v>
+        <v>129960642</v>
       </c>
       <c r="B162" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18238,34 +18238,39 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>471062</v>
+        <v>471025</v>
       </c>
       <c r="R162" t="n">
-        <v>6770538</v>
+        <v>6770488</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18334,10 +18339,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129960642</v>
+        <v>129958754</v>
       </c>
       <c r="B163" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18345,39 +18350,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>471025</v>
+        <v>470817</v>
       </c>
       <c r="R163" t="n">
-        <v>6770488</v>
+        <v>6770608</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18446,7 +18446,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129958841</v>
+        <v>129955313</v>
       </c>
       <c r="B164" t="n">
         <v>79084</v>
@@ -18481,10 +18481,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>470828</v>
+        <v>470992</v>
       </c>
       <c r="R164" t="n">
-        <v>6770636</v>
+        <v>6770702</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18553,7 +18553,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129955313</v>
+        <v>129960929</v>
       </c>
       <c r="B165" t="n">
         <v>79084</v>
@@ -18588,10 +18588,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>470992</v>
+        <v>471159</v>
       </c>
       <c r="R165" t="n">
-        <v>6770702</v>
+        <v>6770613</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18660,7 +18660,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129958466</v>
+        <v>129958775</v>
       </c>
       <c r="B166" t="n">
         <v>79084</v>
@@ -18695,10 +18695,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470812</v>
+        <v>470803</v>
       </c>
       <c r="R166" t="n">
-        <v>6770670</v>
+        <v>6770595</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18767,7 +18767,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129962390</v>
+        <v>129958466</v>
       </c>
       <c r="B167" t="n">
         <v>79084</v>
@@ -18802,10 +18802,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>471004</v>
+        <v>470812</v>
       </c>
       <c r="R167" t="n">
-        <v>6770581</v>
+        <v>6770670</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18874,10 +18874,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129954441</v>
+        <v>129958841</v>
       </c>
       <c r="B168" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18885,39 +18885,34 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
-      <c r="M168" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P168" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>471052</v>
+        <v>470828</v>
       </c>
       <c r="R168" t="n">
-        <v>6770696</v>
+        <v>6770636</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18986,7 +18981,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129960929</v>
+        <v>129959994</v>
       </c>
       <c r="B169" t="n">
         <v>79084</v>
@@ -19021,10 +19016,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>471159</v>
+        <v>470954</v>
       </c>
       <c r="R169" t="n">
-        <v>6770613</v>
+        <v>6770475</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19093,7 +19088,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129959994</v>
+        <v>129962390</v>
       </c>
       <c r="B170" t="n">
         <v>79084</v>
@@ -19128,10 +19123,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>470954</v>
+        <v>471004</v>
       </c>
       <c r="R170" t="n">
-        <v>6770475</v>
+        <v>6770581</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19200,10 +19195,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129958775</v>
+        <v>129954441</v>
       </c>
       <c r="B171" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19211,34 +19206,39 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>470803</v>
+        <v>471052</v>
       </c>
       <c r="R171" t="n">
-        <v>6770595</v>
+        <v>6770696</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19307,7 +19307,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129959740</v>
+        <v>129959717</v>
       </c>
       <c r="B172" t="n">
         <v>79084</v>
@@ -19342,10 +19342,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>470905</v>
+        <v>470864</v>
       </c>
       <c r="R172" t="n">
-        <v>6770435</v>
+        <v>6770438</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19414,7 +19414,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129959717</v>
+        <v>129959740</v>
       </c>
       <c r="B173" t="n">
         <v>79084</v>
@@ -19449,10 +19449,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>470864</v>
+        <v>470905</v>
       </c>
       <c r="R173" t="n">
-        <v>6770438</v>
+        <v>6770435</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19521,50 +19521,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129959579</v>
+        <v>129962243</v>
       </c>
       <c r="B174" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>470822</v>
+        <v>471074</v>
       </c>
       <c r="R174" t="n">
-        <v>6770452</v>
+        <v>6770617</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19633,50 +19628,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129959285</v>
+        <v>129962351</v>
       </c>
       <c r="B175" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>470922</v>
+        <v>471017</v>
       </c>
       <c r="R175" t="n">
-        <v>6770556</v>
+        <v>6770613</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19745,7 +19735,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129962243</v>
+        <v>129962290</v>
       </c>
       <c r="B176" t="n">
         <v>79084</v>
@@ -19780,10 +19770,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471074</v>
+        <v>471033</v>
       </c>
       <c r="R176" t="n">
-        <v>6770617</v>
+        <v>6770614</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19852,45 +19842,50 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129962351</v>
+        <v>129959285</v>
       </c>
       <c r="B177" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>471017</v>
+        <v>470922</v>
       </c>
       <c r="R177" t="n">
-        <v>6770613</v>
+        <v>6770556</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19959,45 +19954,50 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129962290</v>
+        <v>129962436</v>
       </c>
       <c r="B178" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>471033</v>
+        <v>470989</v>
       </c>
       <c r="R178" t="n">
-        <v>6770614</v>
+        <v>6770629</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20066,7 +20066,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129962436</v>
+        <v>129959579</v>
       </c>
       <c r="B179" t="n">
         <v>8450</v>
@@ -20106,10 +20106,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>470989</v>
+        <v>470822</v>
       </c>
       <c r="R179" t="n">
-        <v>6770629</v>
+        <v>6770452</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20178,7 +20178,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129962443</v>
+        <v>129958214</v>
       </c>
       <c r="B180" t="n">
         <v>79084</v>
@@ -20213,10 +20213,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>470989</v>
+        <v>470823</v>
       </c>
       <c r="R180" t="n">
-        <v>6770629</v>
+        <v>6770705</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20285,50 +20285,45 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129961109</v>
+        <v>129962443</v>
       </c>
       <c r="B181" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
-      <c r="M181" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P181" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471175</v>
+        <v>470989</v>
       </c>
       <c r="R181" t="n">
-        <v>6770631</v>
+        <v>6770629</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20397,7 +20392,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129958214</v>
+        <v>129961937</v>
       </c>
       <c r="B182" t="n">
         <v>79084</v>
@@ -20432,10 +20427,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>470823</v>
+        <v>471216</v>
       </c>
       <c r="R182" t="n">
-        <v>6770705</v>
+        <v>6770650</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20504,45 +20499,50 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129961937</v>
+        <v>129961109</v>
       </c>
       <c r="B183" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>471216</v>
+        <v>471175</v>
       </c>
       <c r="R183" t="n">
-        <v>6770650</v>
+        <v>6770631</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20611,7 +20611,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129958694</v>
+        <v>129962447</v>
       </c>
       <c r="B184" t="n">
         <v>79084</v>
@@ -20646,10 +20646,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>470844</v>
+        <v>470993</v>
       </c>
       <c r="R184" t="n">
-        <v>6770699</v>
+        <v>6770643</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20718,10 +20718,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129958228</v>
+        <v>129959667</v>
       </c>
       <c r="B185" t="n">
-        <v>79084</v>
+        <v>91623</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20729,34 +20729,38 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P185" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>470813</v>
+        <v>470864</v>
       </c>
       <c r="R185" t="n">
-        <v>6770681</v>
+        <v>6770438</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20932,7 +20936,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129956859</v>
+        <v>129958228</v>
       </c>
       <c r="B187" t="n">
         <v>79084</v>
@@ -20967,10 +20971,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>470936</v>
+        <v>470813</v>
       </c>
       <c r="R187" t="n">
-        <v>6770721</v>
+        <v>6770681</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21039,7 +21043,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129962447</v>
+        <v>129960864</v>
       </c>
       <c r="B188" t="n">
         <v>79084</v>
@@ -21074,10 +21078,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>470993</v>
+        <v>471116</v>
       </c>
       <c r="R188" t="n">
-        <v>6770643</v>
+        <v>6770565</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21146,7 +21150,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129960864</v>
+        <v>129958694</v>
       </c>
       <c r="B189" t="n">
         <v>79084</v>
@@ -21181,10 +21185,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>471116</v>
+        <v>470844</v>
       </c>
       <c r="R189" t="n">
-        <v>6770565</v>
+        <v>6770699</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21253,10 +21257,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129959870</v>
+        <v>129956859</v>
       </c>
       <c r="B190" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21264,39 +21268,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>470952</v>
+        <v>470936</v>
       </c>
       <c r="R190" t="n">
-        <v>6770464</v>
+        <v>6770721</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21365,10 +21364,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129959667</v>
+        <v>129959870</v>
       </c>
       <c r="B191" t="n">
-        <v>91623</v>
+        <v>57734</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21376,26 +21375,27 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -21404,10 +21404,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>470864</v>
+        <v>470952</v>
       </c>
       <c r="R191" t="n">
-        <v>6770438</v>
+        <v>6770464</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21476,50 +21476,45 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129958199</v>
+        <v>129954590</v>
       </c>
       <c r="B192" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>470823</v>
+        <v>471013</v>
       </c>
       <c r="R192" t="n">
-        <v>6770705</v>
+        <v>6770715</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21700,45 +21695,50 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129954590</v>
+        <v>129958199</v>
       </c>
       <c r="B194" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>471013</v>
+        <v>470823</v>
       </c>
       <c r="R194" t="n">
-        <v>6770715</v>
+        <v>6770705</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21919,7 +21919,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129956851</v>
+        <v>129959375</v>
       </c>
       <c r="B196" t="n">
         <v>79084</v>
@@ -21954,10 +21954,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>470928</v>
+        <v>470851</v>
       </c>
       <c r="R196" t="n">
-        <v>6770695</v>
+        <v>6770520</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22026,50 +22026,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129962346</v>
+        <v>129960891</v>
       </c>
       <c r="B197" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>471017</v>
+        <v>471147</v>
       </c>
       <c r="R197" t="n">
-        <v>6770613</v>
+        <v>6770575</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22138,7 +22133,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129960891</v>
+        <v>129956851</v>
       </c>
       <c r="B198" t="n">
         <v>79084</v>
@@ -22173,10 +22168,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>471147</v>
+        <v>470928</v>
       </c>
       <c r="R198" t="n">
-        <v>6770575</v>
+        <v>6770695</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22469,45 +22464,50 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129959375</v>
+        <v>129962346</v>
       </c>
       <c r="B201" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>470851</v>
+        <v>471017</v>
       </c>
       <c r="R201" t="n">
-        <v>6770520</v>
+        <v>6770613</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22790,7 +22790,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129962379</v>
+        <v>129962224</v>
       </c>
       <c r="B204" t="n">
         <v>79084</v>
@@ -22825,10 +22825,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>470996</v>
+        <v>471098</v>
       </c>
       <c r="R204" t="n">
-        <v>6770611</v>
+        <v>6770634</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22897,10 +22897,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129962224</v>
+        <v>129958691</v>
       </c>
       <c r="B205" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22908,34 +22908,39 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>471098</v>
+        <v>470844</v>
       </c>
       <c r="R205" t="n">
-        <v>6770634</v>
+        <v>6770699</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23116,38 +23121,38 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129958691</v>
+        <v>129959223</v>
       </c>
       <c r="B207" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -23156,10 +23161,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470844</v>
+        <v>470921</v>
       </c>
       <c r="R207" t="n">
-        <v>6770699</v>
+        <v>6770579</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23228,50 +23233,45 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129959223</v>
+        <v>129962379</v>
       </c>
       <c r="B208" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470921</v>
+        <v>470996</v>
       </c>
       <c r="R208" t="n">
-        <v>6770579</v>
+        <v>6770611</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23340,7 +23340,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129960884</v>
+        <v>129958706</v>
       </c>
       <c r="B209" t="n">
         <v>79084</v>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>471129</v>
+        <v>470816</v>
       </c>
       <c r="R209" t="n">
-        <v>6770567</v>
+        <v>6770646</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23447,7 +23447,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129958706</v>
+        <v>129962417</v>
       </c>
       <c r="B210" t="n">
         <v>79084</v>
@@ -23482,10 +23482,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>470816</v>
+        <v>471002</v>
       </c>
       <c r="R210" t="n">
-        <v>6770646</v>
+        <v>6770618</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23554,7 +23554,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129962417</v>
+        <v>129960884</v>
       </c>
       <c r="B211" t="n">
         <v>79084</v>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>471002</v>
+        <v>471129</v>
       </c>
       <c r="R211" t="n">
-        <v>6770618</v>
+        <v>6770567</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23661,7 +23661,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129956843</v>
+        <v>129962119</v>
       </c>
       <c r="B212" t="n">
         <v>79084</v>
@@ -23696,10 +23696,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>470953</v>
+        <v>471156</v>
       </c>
       <c r="R212" t="n">
-        <v>6770692</v>
+        <v>6770665</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23768,7 +23768,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129962119</v>
+        <v>129954584</v>
       </c>
       <c r="B213" t="n">
         <v>79084</v>
@@ -23803,10 +23803,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>471156</v>
+        <v>471062</v>
       </c>
       <c r="R213" t="n">
-        <v>6770665</v>
+        <v>6770731</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23875,7 +23875,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129954584</v>
+        <v>129956843</v>
       </c>
       <c r="B214" t="n">
         <v>79084</v>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471062</v>
+        <v>470953</v>
       </c>
       <c r="R214" t="n">
-        <v>6770731</v>
+        <v>6770692</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23982,7 +23982,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129960790</v>
+        <v>129958133</v>
       </c>
       <c r="B215" t="n">
         <v>79084</v>
@@ -24017,10 +24017,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471073</v>
+        <v>470869</v>
       </c>
       <c r="R215" t="n">
-        <v>6770551</v>
+        <v>6770702</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24089,50 +24089,45 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129959735</v>
+        <v>129960790</v>
       </c>
       <c r="B216" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>470868</v>
+        <v>471073</v>
       </c>
       <c r="R216" t="n">
-        <v>6770431</v>
+        <v>6770551</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24201,45 +24196,50 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129958133</v>
+        <v>129959735</v>
       </c>
       <c r="B217" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>470869</v>
+        <v>470868</v>
       </c>
       <c r="R217" t="n">
-        <v>6770702</v>
+        <v>6770431</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24527,53 +24527,48 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129960514</v>
+        <v>129960823</v>
       </c>
       <c r="B220" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
-      <c r="M220" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P220" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>470976</v>
+        <v>471078</v>
       </c>
       <c r="R220" t="n">
-        <v>6770536</v>
+        <v>6770561</v>
       </c>
       <c r="S220" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T220" t="inlineStr">
         <is>
@@ -24613,6 +24608,11 @@
       <c r="AB220" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24639,48 +24639,53 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129960823</v>
+        <v>129960514</v>
       </c>
       <c r="B221" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>471078</v>
+        <v>470976</v>
       </c>
       <c r="R221" t="n">
-        <v>6770561</v>
+        <v>6770536</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24720,11 +24725,6 @@
       <c r="AB221" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24751,10 +24751,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129957253</v>
+        <v>129957969</v>
       </c>
       <c r="B222" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24762,39 +24762,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470916</v>
+        <v>470911</v>
       </c>
       <c r="R222" t="n">
-        <v>6770721</v>
+        <v>6770707</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24863,7 +24858,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129960657</v>
+        <v>129959441</v>
       </c>
       <c r="B223" t="n">
         <v>8450</v>
@@ -24903,10 +24898,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>471025</v>
+        <v>470824</v>
       </c>
       <c r="R223" t="n">
-        <v>6770488</v>
+        <v>6770523</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24975,7 +24970,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129959710</v>
+        <v>129958131</v>
       </c>
       <c r="B224" t="n">
         <v>8450</v>
@@ -25015,10 +25010,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470864</v>
+        <v>470869</v>
       </c>
       <c r="R224" t="n">
-        <v>6770438</v>
+        <v>6770702</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25087,45 +25082,50 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129959250</v>
+        <v>129959710</v>
       </c>
       <c r="B225" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470943</v>
+        <v>470864</v>
       </c>
       <c r="R225" t="n">
-        <v>6770559</v>
+        <v>6770438</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25194,7 +25194,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129959441</v>
+        <v>129960657</v>
       </c>
       <c r="B226" t="n">
         <v>8450</v>
@@ -25234,10 +25234,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>470824</v>
+        <v>471025</v>
       </c>
       <c r="R226" t="n">
-        <v>6770523</v>
+        <v>6770488</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25306,50 +25306,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129958131</v>
+        <v>129961818</v>
       </c>
       <c r="B227" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>470869</v>
+        <v>471228</v>
       </c>
       <c r="R227" t="n">
-        <v>6770702</v>
+        <v>6770667</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25418,7 +25413,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129957969</v>
+        <v>129959250</v>
       </c>
       <c r="B228" t="n">
         <v>79084</v>
@@ -25453,10 +25448,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470911</v>
+        <v>470943</v>
       </c>
       <c r="R228" t="n">
-        <v>6770707</v>
+        <v>6770559</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25525,10 +25520,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129961818</v>
+        <v>129957253</v>
       </c>
       <c r="B229" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25536,34 +25531,39 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>471228</v>
+        <v>470916</v>
       </c>
       <c r="R229" t="n">
-        <v>6770667</v>
+        <v>6770721</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25632,10 +25632,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129960437</v>
+        <v>129959730</v>
       </c>
       <c r="B230" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25643,34 +25643,39 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>470948</v>
+        <v>470868</v>
       </c>
       <c r="R230" t="n">
-        <v>6770533</v>
+        <v>6770431</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25739,10 +25744,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129959730</v>
+        <v>129960437</v>
       </c>
       <c r="B231" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25750,39 +25755,34 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>470868</v>
+        <v>470948</v>
       </c>
       <c r="R231" t="n">
-        <v>6770431</v>
+        <v>6770533</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25851,7 +25851,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129960691</v>
+        <v>129958795</v>
       </c>
       <c r="B232" t="n">
         <v>79084</v>
@@ -25886,10 +25886,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>471056</v>
+        <v>470822</v>
       </c>
       <c r="R232" t="n">
-        <v>6770494</v>
+        <v>6770615</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25932,6 +25932,11 @@
       <c r="AB232" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25958,7 +25963,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129958795</v>
+        <v>129958151</v>
       </c>
       <c r="B233" t="n">
         <v>79084</v>
@@ -25993,10 +25998,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>470822</v>
+        <v>470842</v>
       </c>
       <c r="R233" t="n">
-        <v>6770615</v>
+        <v>6770709</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26039,11 +26044,6 @@
       <c r="AB233" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26070,7 +26070,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129958151</v>
+        <v>129960691</v>
       </c>
       <c r="B234" t="n">
         <v>79084</v>
@@ -26105,10 +26105,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>470842</v>
+        <v>471056</v>
       </c>
       <c r="R234" t="n">
-        <v>6770709</v>
+        <v>6770494</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -8056,7 +8056,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129944495</v>
+        <v>129944817</v>
       </c>
       <c r="B68" t="n">
         <v>79084</v>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471288</v>
+        <v>471247</v>
       </c>
       <c r="R68" t="n">
-        <v>6770728</v>
+        <v>6770726</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8163,7 +8163,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129946062</v>
+        <v>129944495</v>
       </c>
       <c r="B69" t="n">
         <v>79084</v>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471161</v>
+        <v>471288</v>
       </c>
       <c r="R69" t="n">
-        <v>6770705</v>
+        <v>6770728</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129946408</v>
+        <v>129946062</v>
       </c>
       <c r="B70" t="n">
         <v>79084</v>
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>470921</v>
+        <v>471161</v>
       </c>
       <c r="R70" t="n">
-        <v>6770579</v>
+        <v>6770705</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8377,7 +8377,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129944164</v>
+        <v>129946408</v>
       </c>
       <c r="B71" t="n">
         <v>79084</v>
@@ -8412,10 +8412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471363</v>
+        <v>470921</v>
       </c>
       <c r="R71" t="n">
-        <v>6770736</v>
+        <v>6770579</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8484,7 +8484,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129944817</v>
+        <v>129944164</v>
       </c>
       <c r="B72" t="n">
         <v>79084</v>
@@ -8519,10 +8519,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471247</v>
+        <v>471363</v>
       </c>
       <c r="R72" t="n">
-        <v>6770726</v>
+        <v>6770736</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9676,32 +9676,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129946047</v>
+        <v>129944037</v>
       </c>
       <c r="B83" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471161</v>
+        <v>471417</v>
       </c>
       <c r="R83" t="n">
-        <v>6770705</v>
+        <v>6770738</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9783,7 +9783,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944037</v>
+        <v>129944210</v>
       </c>
       <c r="B84" t="n">
         <v>79084</v>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471417</v>
+        <v>471390</v>
       </c>
       <c r="R84" t="n">
-        <v>6770738</v>
+        <v>6770705</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9890,32 +9890,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129944210</v>
+        <v>129946047</v>
       </c>
       <c r="B85" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471390</v>
+        <v>471161</v>
       </c>
       <c r="R85" t="n">
         <v>6770705</v>
@@ -9997,7 +9997,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129946029</v>
+        <v>129945509</v>
       </c>
       <c r="B86" t="n">
         <v>79084</v>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471185</v>
+        <v>471198</v>
       </c>
       <c r="R86" t="n">
-        <v>6770690</v>
+        <v>6770689</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10078,6 +10078,11 @@
       <c r="AB86" t="inlineStr">
         <is>
           <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10104,7 +10109,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129944466</v>
+        <v>129946029</v>
       </c>
       <c r="B87" t="n">
         <v>79084</v>
@@ -10139,10 +10144,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471322</v>
+        <v>471185</v>
       </c>
       <c r="R87" t="n">
-        <v>6770702</v>
+        <v>6770690</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10211,7 +10216,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129945509</v>
+        <v>129944466</v>
       </c>
       <c r="B88" t="n">
         <v>79084</v>
@@ -10246,10 +10251,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471198</v>
+        <v>471322</v>
       </c>
       <c r="R88" t="n">
-        <v>6770689</v>
+        <v>6770702</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10292,11 +10297,6 @@
       <c r="AB88" t="inlineStr">
         <is>
           <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10430,50 +10430,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129945161</v>
+        <v>129944975</v>
       </c>
       <c r="B90" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471198</v>
+        <v>471242</v>
       </c>
       <c r="R90" t="n">
-        <v>6770725</v>
+        <v>6770682</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10542,7 +10537,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129944975</v>
+        <v>129946708</v>
       </c>
       <c r="B91" t="n">
         <v>79084</v>
@@ -10577,10 +10572,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471242</v>
+        <v>471171</v>
       </c>
       <c r="R91" t="n">
-        <v>6770682</v>
+        <v>6770660</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10649,45 +10644,50 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129946708</v>
+        <v>129945161</v>
       </c>
       <c r="B92" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471171</v>
+        <v>471198</v>
       </c>
       <c r="R92" t="n">
-        <v>6770660</v>
+        <v>6770725</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10872,45 +10872,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129943855</v>
+        <v>129946444</v>
       </c>
       <c r="B94" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471451</v>
+        <v>470971</v>
       </c>
       <c r="R94" t="n">
-        <v>6770706</v>
+        <v>6770603</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10979,7 +10984,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129945066</v>
+        <v>129943855</v>
       </c>
       <c r="B95" t="n">
         <v>79084</v>
@@ -11014,10 +11019,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471239</v>
+        <v>471451</v>
       </c>
       <c r="R95" t="n">
-        <v>6770732</v>
+        <v>6770706</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11086,7 +11091,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129944756</v>
+        <v>129945066</v>
       </c>
       <c r="B96" t="n">
         <v>79084</v>
@@ -11121,10 +11126,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471288</v>
+        <v>471239</v>
       </c>
       <c r="R96" t="n">
-        <v>6770685</v>
+        <v>6770732</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11193,10 +11198,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129946391</v>
+        <v>129944756</v>
       </c>
       <c r="B97" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11204,39 +11209,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>470921</v>
+        <v>471288</v>
       </c>
       <c r="R97" t="n">
-        <v>6770579</v>
+        <v>6770685</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11305,38 +11305,38 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129946444</v>
+        <v>129946391</v>
       </c>
       <c r="B98" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>470971</v>
+        <v>470921</v>
       </c>
       <c r="R98" t="n">
-        <v>6770603</v>
+        <v>6770579</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11743,50 +11743,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129944062</v>
+        <v>129945457</v>
       </c>
       <c r="B102" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471432</v>
+        <v>471189</v>
       </c>
       <c r="R102" t="n">
-        <v>6770716</v>
+        <v>6770706</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11855,7 +11850,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129945457</v>
+        <v>129943809</v>
       </c>
       <c r="B103" t="n">
         <v>79084</v>
@@ -11890,10 +11885,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471189</v>
+        <v>471447</v>
       </c>
       <c r="R103" t="n">
-        <v>6770706</v>
+        <v>6770716</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11962,42 +11957,47 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129943809</v>
+        <v>129944062</v>
       </c>
       <c r="B104" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471447</v>
+        <v>471432</v>
       </c>
       <c r="R104" t="n">
         <v>6770716</v>
@@ -12069,7 +12069,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129944178</v>
+        <v>129943914</v>
       </c>
       <c r="B105" t="n">
         <v>79084</v>
@@ -12104,10 +12104,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471372</v>
+        <v>471432</v>
       </c>
       <c r="R105" t="n">
-        <v>6770719</v>
+        <v>6770701</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129943914</v>
+        <v>129943849</v>
       </c>
       <c r="B106" t="n">
-        <v>79084</v>
+        <v>91623</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12187,34 +12187,38 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471432</v>
+        <v>471451</v>
       </c>
       <c r="R106" t="n">
-        <v>6770701</v>
+        <v>6770706</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12390,7 +12394,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129943541</v>
+        <v>129944178</v>
       </c>
       <c r="B108" t="n">
         <v>79084</v>
@@ -12425,10 +12429,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471478</v>
+        <v>471372</v>
       </c>
       <c r="R108" t="n">
-        <v>6770707</v>
+        <v>6770719</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12497,7 +12501,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129944592</v>
+        <v>129943541</v>
       </c>
       <c r="B109" t="n">
         <v>79084</v>
@@ -12532,10 +12536,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471313</v>
+        <v>471478</v>
       </c>
       <c r="R109" t="n">
-        <v>6770688</v>
+        <v>6770707</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12604,10 +12608,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129943849</v>
+        <v>129944592</v>
       </c>
       <c r="B110" t="n">
-        <v>91623</v>
+        <v>79084</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12615,38 +12619,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471451</v>
+        <v>471313</v>
       </c>
       <c r="R110" t="n">
-        <v>6770706</v>
+        <v>6770688</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12822,45 +12822,50 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129944804</v>
+        <v>129946334</v>
       </c>
       <c r="B112" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471271</v>
+        <v>470871</v>
       </c>
       <c r="R112" t="n">
-        <v>6770733</v>
+        <v>6770635</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12929,50 +12934,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129946334</v>
+        <v>129944804</v>
       </c>
       <c r="B113" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>470871</v>
+        <v>471271</v>
       </c>
       <c r="R113" t="n">
-        <v>6770635</v>
+        <v>6770733</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13581,50 +13581,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129944158</v>
+        <v>129944523</v>
       </c>
       <c r="B119" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471363</v>
+        <v>471303</v>
       </c>
       <c r="R119" t="n">
-        <v>6770736</v>
+        <v>6770699</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13693,45 +13688,50 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129944523</v>
+        <v>129945444</v>
       </c>
       <c r="B120" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471303</v>
+        <v>471189</v>
       </c>
       <c r="R120" t="n">
-        <v>6770699</v>
+        <v>6770706</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13800,7 +13800,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129945444</v>
+        <v>129944158</v>
       </c>
       <c r="B121" t="n">
         <v>8450</v>
@@ -13840,10 +13840,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471189</v>
+        <v>471363</v>
       </c>
       <c r="R121" t="n">
-        <v>6770706</v>
+        <v>6770736</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129960901</v>
+        <v>129962374</v>
       </c>
       <c r="B123" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14035,34 +14035,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471185</v>
+        <v>470996</v>
       </c>
       <c r="R123" t="n">
-        <v>6770590</v>
+        <v>6770611</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14131,7 +14136,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129959787</v>
+        <v>129960901</v>
       </c>
       <c r="B124" t="n">
         <v>79084</v>
@@ -14166,10 +14171,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>470900</v>
+        <v>471185</v>
       </c>
       <c r="R124" t="n">
-        <v>6770473</v>
+        <v>6770590</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14238,7 +14243,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129957713</v>
+        <v>129960002</v>
       </c>
       <c r="B125" t="n">
         <v>79084</v>
@@ -14273,10 +14278,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470904</v>
+        <v>470932</v>
       </c>
       <c r="R125" t="n">
-        <v>6770718</v>
+        <v>6770480</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14345,7 +14350,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129958842</v>
+        <v>129957713</v>
       </c>
       <c r="B126" t="n">
         <v>79084</v>
@@ -14380,10 +14385,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470820</v>
+        <v>470904</v>
       </c>
       <c r="R126" t="n">
-        <v>6770624</v>
+        <v>6770718</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14452,7 +14457,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129959479</v>
+        <v>129958464</v>
       </c>
       <c r="B127" t="n">
         <v>79084</v>
@@ -14487,10 +14492,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470837</v>
+        <v>470822</v>
       </c>
       <c r="R127" t="n">
-        <v>6770498</v>
+        <v>6770673</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14559,7 +14564,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129954413</v>
+        <v>129959479</v>
       </c>
       <c r="B128" t="n">
         <v>79084</v>
@@ -14594,10 +14599,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>471028</v>
+        <v>470837</v>
       </c>
       <c r="R128" t="n">
-        <v>6770675</v>
+        <v>6770498</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14666,7 +14671,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129959122</v>
+        <v>129959787</v>
       </c>
       <c r="B129" t="n">
         <v>79084</v>
@@ -14701,10 +14706,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470926</v>
+        <v>470900</v>
       </c>
       <c r="R129" t="n">
-        <v>6770613</v>
+        <v>6770473</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14880,7 +14885,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129960002</v>
+        <v>129959122</v>
       </c>
       <c r="B131" t="n">
         <v>79084</v>
@@ -14915,10 +14920,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470932</v>
+        <v>470926</v>
       </c>
       <c r="R131" t="n">
-        <v>6770480</v>
+        <v>6770613</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14987,7 +14992,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129958464</v>
+        <v>129958842</v>
       </c>
       <c r="B132" t="n">
         <v>79084</v>
@@ -15022,10 +15027,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470822</v>
+        <v>470820</v>
       </c>
       <c r="R132" t="n">
-        <v>6770673</v>
+        <v>6770624</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15094,10 +15099,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129962374</v>
+        <v>129954413</v>
       </c>
       <c r="B133" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15105,39 +15110,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>470996</v>
+        <v>471028</v>
       </c>
       <c r="R133" t="n">
-        <v>6770611</v>
+        <v>6770675</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15318,50 +15318,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129959110</v>
+        <v>129961622</v>
       </c>
       <c r="B135" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470926</v>
+        <v>471262</v>
       </c>
       <c r="R135" t="n">
-        <v>6770613</v>
+        <v>6770622</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15430,7 +15425,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129959501</v>
+        <v>129959047</v>
       </c>
       <c r="B136" t="n">
         <v>79084</v>
@@ -15465,10 +15460,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470807</v>
+        <v>470908</v>
       </c>
       <c r="R136" t="n">
-        <v>6770491</v>
+        <v>6770622</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15537,7 +15532,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129954531</v>
+        <v>129959501</v>
       </c>
       <c r="B137" t="n">
         <v>79084</v>
@@ -15572,10 +15567,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>471106</v>
+        <v>470807</v>
       </c>
       <c r="R137" t="n">
-        <v>6770683</v>
+        <v>6770491</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15644,7 +15639,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129958010</v>
+        <v>129955100</v>
       </c>
       <c r="B138" t="n">
         <v>79084</v>
@@ -15679,10 +15674,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470894</v>
+        <v>470981</v>
       </c>
       <c r="R138" t="n">
-        <v>6770713</v>
+        <v>6770691</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15751,7 +15746,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129958895</v>
+        <v>129954531</v>
       </c>
       <c r="B139" t="n">
         <v>79084</v>
@@ -15786,10 +15781,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470887</v>
+        <v>471106</v>
       </c>
       <c r="R139" t="n">
-        <v>6770658</v>
+        <v>6770683</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15858,7 +15853,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129959047</v>
+        <v>129958010</v>
       </c>
       <c r="B140" t="n">
         <v>79084</v>
@@ -15893,10 +15888,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470908</v>
+        <v>470894</v>
       </c>
       <c r="R140" t="n">
-        <v>6770622</v>
+        <v>6770713</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15965,7 +15960,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129961622</v>
+        <v>129958895</v>
       </c>
       <c r="B141" t="n">
         <v>79084</v>
@@ -16000,10 +15995,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>471262</v>
+        <v>470887</v>
       </c>
       <c r="R141" t="n">
-        <v>6770622</v>
+        <v>6770658</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16179,45 +16174,50 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129955100</v>
+        <v>129959110</v>
       </c>
       <c r="B143" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>470981</v>
+        <v>470926</v>
       </c>
       <c r="R143" t="n">
-        <v>6770691</v>
+        <v>6770613</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16286,50 +16286,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129960827</v>
+        <v>129962073</v>
       </c>
       <c r="B144" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471078</v>
+        <v>471222</v>
       </c>
       <c r="R144" t="n">
-        <v>6770561</v>
+        <v>6770635</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16398,7 +16393,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129958802</v>
+        <v>129962260</v>
       </c>
       <c r="B145" t="n">
         <v>79084</v>
@@ -16433,10 +16428,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>470858</v>
+        <v>471044</v>
       </c>
       <c r="R145" t="n">
-        <v>6770602</v>
+        <v>6770615</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16505,7 +16500,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129962260</v>
+        <v>129959352</v>
       </c>
       <c r="B146" t="n">
         <v>79084</v>
@@ -16540,10 +16535,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>471044</v>
+        <v>470879</v>
       </c>
       <c r="R146" t="n">
-        <v>6770615</v>
+        <v>6770545</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16612,7 +16607,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129959352</v>
+        <v>129958937</v>
       </c>
       <c r="B147" t="n">
         <v>79084</v>
@@ -16647,10 +16642,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470879</v>
+        <v>470897</v>
       </c>
       <c r="R147" t="n">
-        <v>6770545</v>
+        <v>6770647</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16719,7 +16714,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129958937</v>
+        <v>129958802</v>
       </c>
       <c r="B148" t="n">
         <v>79084</v>
@@ -16754,10 +16749,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470897</v>
+        <v>470858</v>
       </c>
       <c r="R148" t="n">
-        <v>6770647</v>
+        <v>6770602</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16826,45 +16821,50 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129962073</v>
+        <v>129960827</v>
       </c>
       <c r="B149" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>471222</v>
+        <v>471078</v>
       </c>
       <c r="R149" t="n">
-        <v>6770635</v>
+        <v>6770561</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17157,7 +17157,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129954534</v>
+        <v>129954803</v>
       </c>
       <c r="B152" t="n">
         <v>79084</v>
@@ -17192,10 +17192,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>471086</v>
+        <v>470938</v>
       </c>
       <c r="R152" t="n">
-        <v>6770684</v>
+        <v>6770693</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17264,7 +17264,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129954803</v>
+        <v>129954534</v>
       </c>
       <c r="B153" t="n">
         <v>79084</v>
@@ -17299,10 +17299,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>470938</v>
+        <v>471086</v>
       </c>
       <c r="R153" t="n">
-        <v>6770693</v>
+        <v>6770684</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17371,7 +17371,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129954408</v>
+        <v>129959294</v>
       </c>
       <c r="B154" t="n">
         <v>79084</v>
@@ -17406,10 +17406,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>471019</v>
+        <v>470904</v>
       </c>
       <c r="R154" t="n">
-        <v>6770666</v>
+        <v>6770537</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17478,7 +17478,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129959294</v>
+        <v>129958545</v>
       </c>
       <c r="B155" t="n">
         <v>79084</v>
@@ -17513,10 +17513,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470904</v>
+        <v>470877</v>
       </c>
       <c r="R155" t="n">
-        <v>6770537</v>
+        <v>6770687</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17585,7 +17585,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129958545</v>
+        <v>129954408</v>
       </c>
       <c r="B156" t="n">
         <v>79084</v>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>470877</v>
+        <v>471019</v>
       </c>
       <c r="R156" t="n">
-        <v>6770687</v>
+        <v>6770666</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17692,10 +17692,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129959389</v>
+        <v>129960642</v>
       </c>
       <c r="B157" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17703,34 +17703,39 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>470824</v>
+        <v>471025</v>
       </c>
       <c r="R157" t="n">
-        <v>6770523</v>
+        <v>6770488</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17799,7 +17804,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129959519</v>
+        <v>129959389</v>
       </c>
       <c r="B158" t="n">
         <v>79084</v>
@@ -17834,10 +17839,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470822</v>
+        <v>470824</v>
       </c>
       <c r="R158" t="n">
-        <v>6770452</v>
+        <v>6770523</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17906,7 +17911,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129954452</v>
+        <v>129954442</v>
       </c>
       <c r="B159" t="n">
         <v>79084</v>
@@ -17941,10 +17946,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>471058</v>
+        <v>471053</v>
       </c>
       <c r="R159" t="n">
-        <v>6770677</v>
+        <v>6770682</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18013,7 +18018,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129954442</v>
+        <v>129958754</v>
       </c>
       <c r="B160" t="n">
         <v>79084</v>
@@ -18048,10 +18053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>471053</v>
+        <v>470817</v>
       </c>
       <c r="R160" t="n">
-        <v>6770682</v>
+        <v>6770608</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18227,10 +18232,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129960642</v>
+        <v>129954452</v>
       </c>
       <c r="B162" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18238,39 +18243,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>471025</v>
+        <v>471058</v>
       </c>
       <c r="R162" t="n">
-        <v>6770488</v>
+        <v>6770677</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18339,7 +18339,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129958754</v>
+        <v>129959519</v>
       </c>
       <c r="B163" t="n">
         <v>79084</v>
@@ -18374,10 +18374,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>470817</v>
+        <v>470822</v>
       </c>
       <c r="R163" t="n">
-        <v>6770608</v>
+        <v>6770452</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18446,10 +18446,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129955313</v>
+        <v>129954441</v>
       </c>
       <c r="B164" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18457,34 +18457,39 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>470992</v>
+        <v>471052</v>
       </c>
       <c r="R164" t="n">
-        <v>6770702</v>
+        <v>6770696</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18553,7 +18558,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129960929</v>
+        <v>129958775</v>
       </c>
       <c r="B165" t="n">
         <v>79084</v>
@@ -18588,10 +18593,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>471159</v>
+        <v>470803</v>
       </c>
       <c r="R165" t="n">
-        <v>6770613</v>
+        <v>6770595</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18660,7 +18665,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129958775</v>
+        <v>129960929</v>
       </c>
       <c r="B166" t="n">
         <v>79084</v>
@@ -18695,10 +18700,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470803</v>
+        <v>471159</v>
       </c>
       <c r="R166" t="n">
-        <v>6770595</v>
+        <v>6770613</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18767,7 +18772,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129958466</v>
+        <v>129955313</v>
       </c>
       <c r="B167" t="n">
         <v>79084</v>
@@ -18802,10 +18807,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470812</v>
+        <v>470992</v>
       </c>
       <c r="R167" t="n">
-        <v>6770670</v>
+        <v>6770702</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18874,7 +18879,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129958841</v>
+        <v>129959994</v>
       </c>
       <c r="B168" t="n">
         <v>79084</v>
@@ -18909,10 +18914,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>470828</v>
+        <v>470954</v>
       </c>
       <c r="R168" t="n">
-        <v>6770636</v>
+        <v>6770475</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18981,7 +18986,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129959994</v>
+        <v>129958841</v>
       </c>
       <c r="B169" t="n">
         <v>79084</v>
@@ -19016,10 +19021,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>470954</v>
+        <v>470828</v>
       </c>
       <c r="R169" t="n">
-        <v>6770475</v>
+        <v>6770636</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19195,10 +19200,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129954441</v>
+        <v>129958466</v>
       </c>
       <c r="B171" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19206,39 +19211,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>471052</v>
+        <v>470812</v>
       </c>
       <c r="R171" t="n">
-        <v>6770696</v>
+        <v>6770670</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19307,7 +19307,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129959717</v>
+        <v>129959740</v>
       </c>
       <c r="B172" t="n">
         <v>79084</v>
@@ -19342,10 +19342,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>470864</v>
+        <v>470905</v>
       </c>
       <c r="R172" t="n">
-        <v>6770438</v>
+        <v>6770435</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19414,7 +19414,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129959740</v>
+        <v>129962243</v>
       </c>
       <c r="B173" t="n">
         <v>79084</v>
@@ -19449,10 +19449,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>470905</v>
+        <v>471074</v>
       </c>
       <c r="R173" t="n">
-        <v>6770435</v>
+        <v>6770617</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19521,7 +19521,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129962243</v>
+        <v>129959717</v>
       </c>
       <c r="B174" t="n">
         <v>79084</v>
@@ -19556,10 +19556,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>471074</v>
+        <v>470864</v>
       </c>
       <c r="R174" t="n">
-        <v>6770617</v>
+        <v>6770438</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -20178,7 +20178,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129958214</v>
+        <v>129962443</v>
       </c>
       <c r="B180" t="n">
         <v>79084</v>
@@ -20213,10 +20213,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>470823</v>
+        <v>470989</v>
       </c>
       <c r="R180" t="n">
-        <v>6770705</v>
+        <v>6770629</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20285,7 +20285,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129962443</v>
+        <v>129961937</v>
       </c>
       <c r="B181" t="n">
         <v>79084</v>
@@ -20320,10 +20320,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>470989</v>
+        <v>471216</v>
       </c>
       <c r="R181" t="n">
-        <v>6770629</v>
+        <v>6770650</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20392,7 +20392,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129961937</v>
+        <v>129958214</v>
       </c>
       <c r="B182" t="n">
         <v>79084</v>
@@ -20427,10 +20427,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471216</v>
+        <v>470823</v>
       </c>
       <c r="R182" t="n">
-        <v>6770650</v>
+        <v>6770705</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20611,10 +20611,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129962447</v>
+        <v>129959870</v>
       </c>
       <c r="B184" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20622,34 +20622,39 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>470993</v>
+        <v>470952</v>
       </c>
       <c r="R184" t="n">
-        <v>6770643</v>
+        <v>6770464</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20718,10 +20723,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129959667</v>
+        <v>129962447</v>
       </c>
       <c r="B185" t="n">
-        <v>91623</v>
+        <v>79084</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20729,38 +20734,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I185" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>470864</v>
+        <v>470993</v>
       </c>
       <c r="R185" t="n">
-        <v>6770438</v>
+        <v>6770643</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20829,7 +20830,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129959256</v>
+        <v>129960864</v>
       </c>
       <c r="B186" t="n">
         <v>79084</v>
@@ -20864,10 +20865,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>470922</v>
+        <v>471116</v>
       </c>
       <c r="R186" t="n">
-        <v>6770556</v>
+        <v>6770565</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20936,7 +20937,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129958228</v>
+        <v>129959256</v>
       </c>
       <c r="B187" t="n">
         <v>79084</v>
@@ -20971,10 +20972,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>470813</v>
+        <v>470922</v>
       </c>
       <c r="R187" t="n">
-        <v>6770681</v>
+        <v>6770556</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21043,7 +21044,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129960864</v>
+        <v>129956859</v>
       </c>
       <c r="B188" t="n">
         <v>79084</v>
@@ -21078,10 +21079,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>471116</v>
+        <v>470936</v>
       </c>
       <c r="R188" t="n">
-        <v>6770565</v>
+        <v>6770721</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21257,10 +21258,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129956859</v>
+        <v>129959667</v>
       </c>
       <c r="B190" t="n">
-        <v>79084</v>
+        <v>91623</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21268,34 +21269,38 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>470936</v>
+        <v>470864</v>
       </c>
       <c r="R190" t="n">
-        <v>6770721</v>
+        <v>6770438</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21364,10 +21369,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129959870</v>
+        <v>129958228</v>
       </c>
       <c r="B191" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21375,39 +21380,34 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>470952</v>
+        <v>470813</v>
       </c>
       <c r="R191" t="n">
-        <v>6770464</v>
+        <v>6770681</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21476,10 +21476,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129954590</v>
+        <v>129959434</v>
       </c>
       <c r="B192" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21487,34 +21487,39 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>471013</v>
+        <v>470824</v>
       </c>
       <c r="R192" t="n">
-        <v>6770715</v>
+        <v>6770523</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21583,38 +21588,38 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129959434</v>
+        <v>129958199</v>
       </c>
       <c r="B193" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -21623,10 +21628,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>470824</v>
+        <v>470823</v>
       </c>
       <c r="R193" t="n">
-        <v>6770523</v>
+        <v>6770705</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21695,7 +21700,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129958199</v>
+        <v>129960746</v>
       </c>
       <c r="B194" t="n">
         <v>8450</v>
@@ -21735,10 +21740,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>470823</v>
+        <v>471053</v>
       </c>
       <c r="R194" t="n">
-        <v>6770705</v>
+        <v>6770528</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21807,50 +21812,45 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129960746</v>
+        <v>129954590</v>
       </c>
       <c r="B195" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>471053</v>
+        <v>471013</v>
       </c>
       <c r="R195" t="n">
-        <v>6770528</v>
+        <v>6770715</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21919,10 +21919,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129959375</v>
+        <v>129959567</v>
       </c>
       <c r="B196" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21930,34 +21930,39 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>470851</v>
+        <v>470822</v>
       </c>
       <c r="R196" t="n">
-        <v>6770520</v>
+        <v>6770452</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22026,7 +22031,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129960891</v>
+        <v>129956851</v>
       </c>
       <c r="B197" t="n">
         <v>79084</v>
@@ -22061,10 +22066,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>471147</v>
+        <v>470928</v>
       </c>
       <c r="R197" t="n">
-        <v>6770575</v>
+        <v>6770695</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22133,7 +22138,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129956851</v>
+        <v>129959375</v>
       </c>
       <c r="B198" t="n">
         <v>79084</v>
@@ -22168,10 +22173,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>470928</v>
+        <v>470851</v>
       </c>
       <c r="R198" t="n">
-        <v>6770695</v>
+        <v>6770520</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22240,10 +22245,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129959567</v>
+        <v>129960891</v>
       </c>
       <c r="B199" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22251,39 +22256,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>470822</v>
+        <v>471147</v>
       </c>
       <c r="R199" t="n">
-        <v>6770452</v>
+        <v>6770575</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22576,7 +22576,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129960843</v>
+        <v>129958828</v>
       </c>
       <c r="B202" t="n">
         <v>79084</v>
@@ -22611,10 +22611,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>471097</v>
+        <v>470871</v>
       </c>
       <c r="R202" t="n">
-        <v>6770561</v>
+        <v>6770635</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22683,7 +22683,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129958828</v>
+        <v>129960843</v>
       </c>
       <c r="B203" t="n">
         <v>79084</v>
@@ -22718,10 +22718,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>470871</v>
+        <v>471097</v>
       </c>
       <c r="R203" t="n">
-        <v>6770635</v>
+        <v>6770561</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22790,7 +22790,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129962224</v>
+        <v>129962379</v>
       </c>
       <c r="B204" t="n">
         <v>79084</v>
@@ -22825,10 +22825,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>471098</v>
+        <v>470996</v>
       </c>
       <c r="R204" t="n">
-        <v>6770634</v>
+        <v>6770611</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22897,10 +22897,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129958691</v>
+        <v>129962224</v>
       </c>
       <c r="B205" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22908,39 +22908,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>470844</v>
+        <v>471098</v>
       </c>
       <c r="R205" t="n">
-        <v>6770699</v>
+        <v>6770634</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23009,38 +23004,38 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129954662</v>
+        <v>129958691</v>
       </c>
       <c r="B206" t="n">
-        <v>8450</v>
+        <v>57734</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="M206" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -23049,10 +23044,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470941</v>
+        <v>470844</v>
       </c>
       <c r="R206" t="n">
-        <v>6770708</v>
+        <v>6770699</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23121,7 +23116,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129959223</v>
+        <v>129954662</v>
       </c>
       <c r="B207" t="n">
         <v>8450</v>
@@ -23161,10 +23156,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470921</v>
+        <v>470941</v>
       </c>
       <c r="R207" t="n">
-        <v>6770579</v>
+        <v>6770708</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23233,45 +23228,50 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129962379</v>
+        <v>129959223</v>
       </c>
       <c r="B208" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470996</v>
+        <v>470921</v>
       </c>
       <c r="R208" t="n">
-        <v>6770611</v>
+        <v>6770579</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23340,7 +23340,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129958706</v>
+        <v>129962417</v>
       </c>
       <c r="B209" t="n">
         <v>79084</v>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>470816</v>
+        <v>471002</v>
       </c>
       <c r="R209" t="n">
-        <v>6770646</v>
+        <v>6770618</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23447,7 +23447,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129962417</v>
+        <v>129960884</v>
       </c>
       <c r="B210" t="n">
         <v>79084</v>
@@ -23482,10 +23482,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>471002</v>
+        <v>471129</v>
       </c>
       <c r="R210" t="n">
-        <v>6770618</v>
+        <v>6770567</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23554,7 +23554,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129960884</v>
+        <v>129958706</v>
       </c>
       <c r="B211" t="n">
         <v>79084</v>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>471129</v>
+        <v>470816</v>
       </c>
       <c r="R211" t="n">
-        <v>6770567</v>
+        <v>6770646</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23661,45 +23661,50 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129962119</v>
+        <v>129959735</v>
       </c>
       <c r="B212" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>471156</v>
+        <v>470868</v>
       </c>
       <c r="R212" t="n">
-        <v>6770665</v>
+        <v>6770431</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23768,7 +23773,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129954584</v>
+        <v>129956843</v>
       </c>
       <c r="B213" t="n">
         <v>79084</v>
@@ -23803,10 +23808,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>471062</v>
+        <v>470953</v>
       </c>
       <c r="R213" t="n">
-        <v>6770731</v>
+        <v>6770692</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23875,7 +23880,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129956843</v>
+        <v>129954584</v>
       </c>
       <c r="B214" t="n">
         <v>79084</v>
@@ -23910,10 +23915,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>470953</v>
+        <v>471062</v>
       </c>
       <c r="R214" t="n">
-        <v>6770692</v>
+        <v>6770731</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23982,7 +23987,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129958133</v>
+        <v>129960790</v>
       </c>
       <c r="B215" t="n">
         <v>79084</v>
@@ -24017,10 +24022,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>470869</v>
+        <v>471073</v>
       </c>
       <c r="R215" t="n">
-        <v>6770702</v>
+        <v>6770551</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24089,7 +24094,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129960790</v>
+        <v>129962119</v>
       </c>
       <c r="B216" t="n">
         <v>79084</v>
@@ -24124,10 +24129,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471073</v>
+        <v>471156</v>
       </c>
       <c r="R216" t="n">
-        <v>6770551</v>
+        <v>6770665</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24196,50 +24201,45 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129959735</v>
+        <v>129958133</v>
       </c>
       <c r="B217" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>470868</v>
+        <v>470869</v>
       </c>
       <c r="R217" t="n">
-        <v>6770431</v>
+        <v>6770702</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24420,48 +24420,53 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129962320</v>
+        <v>129960514</v>
       </c>
       <c r="B219" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471024</v>
+        <v>470976</v>
       </c>
       <c r="R219" t="n">
-        <v>6770624</v>
+        <v>6770536</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24527,7 +24532,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129960823</v>
+        <v>129962320</v>
       </c>
       <c r="B220" t="n">
         <v>79084</v>
@@ -24562,10 +24567,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>471078</v>
+        <v>471024</v>
       </c>
       <c r="R220" t="n">
-        <v>6770561</v>
+        <v>6770624</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24608,11 +24613,6 @@
       <c r="AB220" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24639,53 +24639,48 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129960514</v>
+        <v>129960823</v>
       </c>
       <c r="B221" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>470976</v>
+        <v>471078</v>
       </c>
       <c r="R221" t="n">
-        <v>6770536</v>
+        <v>6770561</v>
       </c>
       <c r="S221" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24725,6 +24720,11 @@
       <c r="AB221" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24751,10 +24751,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129957969</v>
+        <v>129957253</v>
       </c>
       <c r="B222" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24762,34 +24762,39 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470911</v>
+        <v>470916</v>
       </c>
       <c r="R222" t="n">
-        <v>6770707</v>
+        <v>6770721</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24858,50 +24863,45 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129959441</v>
+        <v>129959250</v>
       </c>
       <c r="B223" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>470824</v>
+        <v>470943</v>
       </c>
       <c r="R223" t="n">
-        <v>6770523</v>
+        <v>6770559</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24970,50 +24970,45 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129958131</v>
+        <v>129961818</v>
       </c>
       <c r="B224" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470869</v>
+        <v>471228</v>
       </c>
       <c r="R224" t="n">
-        <v>6770702</v>
+        <v>6770667</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25082,50 +25077,45 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129959710</v>
+        <v>129957969</v>
       </c>
       <c r="B225" t="n">
-        <v>8450</v>
+        <v>79084</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470864</v>
+        <v>470911</v>
       </c>
       <c r="R225" t="n">
-        <v>6770438</v>
+        <v>6770707</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25194,7 +25184,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129960657</v>
+        <v>129959441</v>
       </c>
       <c r="B226" t="n">
         <v>8450</v>
@@ -25234,10 +25224,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>471025</v>
+        <v>470824</v>
       </c>
       <c r="R226" t="n">
-        <v>6770488</v>
+        <v>6770523</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25306,45 +25296,50 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129961818</v>
+        <v>129958131</v>
       </c>
       <c r="B227" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>471228</v>
+        <v>470869</v>
       </c>
       <c r="R227" t="n">
-        <v>6770667</v>
+        <v>6770702</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25413,45 +25408,50 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129959250</v>
+        <v>129959710</v>
       </c>
       <c r="B228" t="n">
-        <v>79084</v>
+        <v>8450</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470943</v>
+        <v>470864</v>
       </c>
       <c r="R228" t="n">
-        <v>6770559</v>
+        <v>6770438</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25520,38 +25520,38 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129957253</v>
+        <v>129960657</v>
       </c>
       <c r="B229" t="n">
-        <v>57734</v>
+        <v>8450</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25560,10 +25560,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>470916</v>
+        <v>471025</v>
       </c>
       <c r="R229" t="n">
-        <v>6770721</v>
+        <v>6770488</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25851,7 +25851,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129958795</v>
+        <v>129960691</v>
       </c>
       <c r="B232" t="n">
         <v>79084</v>
@@ -25886,10 +25886,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>470822</v>
+        <v>471056</v>
       </c>
       <c r="R232" t="n">
-        <v>6770615</v>
+        <v>6770494</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25932,11 +25932,6 @@
       <c r="AB232" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC232" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -26070,7 +26065,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129960691</v>
+        <v>129958795</v>
       </c>
       <c r="B234" t="n">
         <v>79084</v>
@@ -26105,10 +26100,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>471056</v>
+        <v>470822</v>
       </c>
       <c r="R234" t="n">
-        <v>6770494</v>
+        <v>6770615</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26151,6 +26146,11 @@
       <c r="AB234" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC234" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD234" t="b">

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -8056,10 +8056,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129944817</v>
+        <v>129946408</v>
       </c>
       <c r="B68" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471247</v>
+        <v>470921</v>
       </c>
       <c r="R68" t="n">
-        <v>6770726</v>
+        <v>6770579</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8163,10 +8163,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129944495</v>
+        <v>129944164</v>
       </c>
       <c r="B69" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471288</v>
+        <v>471363</v>
       </c>
       <c r="R69" t="n">
-        <v>6770728</v>
+        <v>6770736</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,10 +8270,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129946062</v>
+        <v>129944495</v>
       </c>
       <c r="B70" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471161</v>
+        <v>471288</v>
       </c>
       <c r="R70" t="n">
-        <v>6770705</v>
+        <v>6770728</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8377,10 +8377,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129946408</v>
+        <v>129944452</v>
       </c>
       <c r="B71" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8388,34 +8388,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470921</v>
+        <v>471330</v>
       </c>
       <c r="R71" t="n">
-        <v>6770579</v>
+        <v>6770712</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8484,32 +8489,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129944164</v>
+        <v>129944454</v>
       </c>
       <c r="B72" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8519,10 +8524,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471363</v>
+        <v>471330</v>
       </c>
       <c r="R72" t="n">
-        <v>6770736</v>
+        <v>6770712</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8591,10 +8596,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129944452</v>
+        <v>129944817</v>
       </c>
       <c r="B73" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8602,39 +8607,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471330</v>
+        <v>471247</v>
       </c>
       <c r="R73" t="n">
-        <v>6770712</v>
+        <v>6770726</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8703,32 +8703,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129944454</v>
+        <v>129946062</v>
       </c>
       <c r="B74" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471330</v>
+        <v>471161</v>
       </c>
       <c r="R74" t="n">
-        <v>6770712</v>
+        <v>6770705</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8813,7 +8813,7 @@
         <v>129946170</v>
       </c>
       <c r="B75" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>129946586</v>
       </c>
       <c r="B76" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>129944813</v>
       </c>
       <c r="B77" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>129944762</v>
       </c>
       <c r="B78" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>129946436</v>
       </c>
       <c r="B79" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>129945104</v>
       </c>
       <c r="B80" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>129946182</v>
       </c>
       <c r="B81" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9567,7 +9567,7 @@
         <v>129946321</v>
       </c>
       <c r="B82" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9676,32 +9676,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944037</v>
+        <v>129946047</v>
       </c>
       <c r="B83" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471417</v>
+        <v>471161</v>
       </c>
       <c r="R83" t="n">
-        <v>6770738</v>
+        <v>6770705</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944210</v>
+        <v>129944037</v>
       </c>
       <c r="B84" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471390</v>
+        <v>471417</v>
       </c>
       <c r="R84" t="n">
-        <v>6770705</v>
+        <v>6770738</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9890,32 +9890,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129946047</v>
+        <v>129944210</v>
       </c>
       <c r="B85" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471161</v>
+        <v>471390</v>
       </c>
       <c r="R85" t="n">
         <v>6770705</v>
@@ -10000,7 +10000,7 @@
         <v>129945509</v>
       </c>
       <c r="B86" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>129946029</v>
       </c>
       <c r="B87" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>129944466</v>
       </c>
       <c r="B88" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>129944473</v>
       </c>
       <c r="B89" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10430,10 +10430,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129944975</v>
+        <v>129946708</v>
       </c>
       <c r="B90" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471242</v>
+        <v>471171</v>
       </c>
       <c r="R90" t="n">
-        <v>6770682</v>
+        <v>6770660</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10537,45 +10537,50 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129946708</v>
+        <v>129945161</v>
       </c>
       <c r="B91" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471171</v>
+        <v>471198</v>
       </c>
       <c r="R91" t="n">
-        <v>6770660</v>
+        <v>6770725</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10644,50 +10649,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129945161</v>
+        <v>129944975</v>
       </c>
       <c r="B92" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471198</v>
+        <v>471242</v>
       </c>
       <c r="R92" t="n">
-        <v>6770725</v>
+        <v>6770682</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129944878</v>
+        <v>129945066</v>
       </c>
       <c r="B93" t="n">
-        <v>57895</v>
+        <v>79087</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10767,46 +10767,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471258</v>
+        <v>471239</v>
       </c>
       <c r="R93" t="n">
-        <v>6770712</v>
+        <v>6770732</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10872,50 +10863,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129946444</v>
+        <v>129944756</v>
       </c>
       <c r="B94" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>470971</v>
+        <v>471288</v>
       </c>
       <c r="R94" t="n">
-        <v>6770603</v>
+        <v>6770685</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10984,45 +10970,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129943855</v>
+        <v>129946444</v>
       </c>
       <c r="B95" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471451</v>
+        <v>470971</v>
       </c>
       <c r="R95" t="n">
-        <v>6770706</v>
+        <v>6770603</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11091,10 +11082,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129945066</v>
+        <v>129943855</v>
       </c>
       <c r="B96" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11126,10 +11117,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471239</v>
+        <v>471451</v>
       </c>
       <c r="R96" t="n">
-        <v>6770732</v>
+        <v>6770706</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11198,10 +11189,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129944756</v>
+        <v>129946391</v>
       </c>
       <c r="B97" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11209,34 +11200,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471288</v>
+        <v>470921</v>
       </c>
       <c r="R97" t="n">
-        <v>6770685</v>
+        <v>6770579</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11305,10 +11301,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129946391</v>
+        <v>129944878</v>
       </c>
       <c r="B98" t="n">
-        <v>57734</v>
+        <v>57898</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11316,27 +11312,31 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11345,13 +11345,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>470921</v>
+        <v>471258</v>
       </c>
       <c r="R98" t="n">
-        <v>6770579</v>
+        <v>6770712</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>129944926</v>
       </c>
       <c r="B99" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11527,7 +11527,7 @@
         <v>129944544</v>
       </c>
       <c r="B100" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>129945156</v>
       </c>
       <c r="B101" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11746,7 +11746,7 @@
         <v>129945457</v>
       </c>
       <c r="B102" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>129943809</v>
       </c>
       <c r="B103" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11960,7 +11960,7 @@
         <v>129944062</v>
       </c>
       <c r="B104" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12069,10 +12069,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129943914</v>
+        <v>129944488</v>
       </c>
       <c r="B105" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12104,10 +12104,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471432</v>
+        <v>471318</v>
       </c>
       <c r="R105" t="n">
-        <v>6770701</v>
+        <v>6770729</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129943849</v>
+        <v>129944178</v>
       </c>
       <c r="B106" t="n">
-        <v>91623</v>
+        <v>79087</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12187,38 +12187,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471451</v>
+        <v>471372</v>
       </c>
       <c r="R106" t="n">
-        <v>6770706</v>
+        <v>6770719</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12287,10 +12283,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129944488</v>
+        <v>129943849</v>
       </c>
       <c r="B107" t="n">
-        <v>79084</v>
+        <v>91626</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12298,34 +12294,38 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471318</v>
+        <v>471451</v>
       </c>
       <c r="R107" t="n">
-        <v>6770729</v>
+        <v>6770706</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12394,10 +12394,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129944178</v>
+        <v>129943914</v>
       </c>
       <c r="B108" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12429,10 +12429,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471372</v>
+        <v>471432</v>
       </c>
       <c r="R108" t="n">
-        <v>6770719</v>
+        <v>6770701</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12501,10 +12501,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129943541</v>
+        <v>129944592</v>
       </c>
       <c r="B109" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12536,10 +12536,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471478</v>
+        <v>471313</v>
       </c>
       <c r="R109" t="n">
-        <v>6770707</v>
+        <v>6770688</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12608,10 +12608,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129944592</v>
+        <v>129943541</v>
       </c>
       <c r="B110" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471313</v>
+        <v>471478</v>
       </c>
       <c r="R110" t="n">
-        <v>6770688</v>
+        <v>6770707</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12718,7 +12718,7 @@
         <v>129943763</v>
       </c>
       <c r="B111" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12822,50 +12822,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129946334</v>
+        <v>129944804</v>
       </c>
       <c r="B112" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>470871</v>
+        <v>471271</v>
       </c>
       <c r="R112" t="n">
-        <v>6770635</v>
+        <v>6770733</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12934,45 +12929,50 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129944804</v>
+        <v>129946334</v>
       </c>
       <c r="B113" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471271</v>
+        <v>470871</v>
       </c>
       <c r="R113" t="n">
-        <v>6770733</v>
+        <v>6770635</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13044,7 +13044,7 @@
         <v>129946117</v>
       </c>
       <c r="B114" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>129943529</v>
       </c>
       <c r="B115" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>129946197</v>
       </c>
       <c r="B116" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>129945078</v>
       </c>
       <c r="B117" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>129946365</v>
       </c>
       <c r="B118" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>129944523</v>
       </c>
       <c r="B119" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>129945444</v>
       </c>
       <c r="B120" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>129944158</v>
       </c>
       <c r="B121" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>129945440</v>
       </c>
       <c r="B122" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129962374</v>
+        <v>129960901</v>
       </c>
       <c r="B123" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14035,39 +14035,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>470996</v>
+        <v>471185</v>
       </c>
       <c r="R123" t="n">
-        <v>6770611</v>
+        <v>6770590</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14136,10 +14131,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129960901</v>
+        <v>129957713</v>
       </c>
       <c r="B124" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14171,10 +14166,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471185</v>
+        <v>470904</v>
       </c>
       <c r="R124" t="n">
-        <v>6770590</v>
+        <v>6770718</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14243,10 +14238,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129960002</v>
+        <v>129958464</v>
       </c>
       <c r="B125" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14278,10 +14273,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470932</v>
+        <v>470822</v>
       </c>
       <c r="R125" t="n">
-        <v>6770480</v>
+        <v>6770673</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14350,10 +14345,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129957713</v>
+        <v>129959479</v>
       </c>
       <c r="B126" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14385,10 +14380,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470904</v>
+        <v>470837</v>
       </c>
       <c r="R126" t="n">
-        <v>6770718</v>
+        <v>6770498</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14457,10 +14452,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129958464</v>
+        <v>129958842</v>
       </c>
       <c r="B127" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14492,10 +14487,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470822</v>
+        <v>470820</v>
       </c>
       <c r="R127" t="n">
-        <v>6770673</v>
+        <v>6770624</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14564,10 +14559,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129959479</v>
+        <v>129954413</v>
       </c>
       <c r="B128" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14599,10 +14594,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470837</v>
+        <v>471028</v>
       </c>
       <c r="R128" t="n">
-        <v>6770498</v>
+        <v>6770675</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14671,10 +14666,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129959787</v>
+        <v>129960002</v>
       </c>
       <c r="B129" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14706,10 +14701,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470900</v>
+        <v>470932</v>
       </c>
       <c r="R129" t="n">
-        <v>6770473</v>
+        <v>6770480</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14778,10 +14773,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129959813</v>
+        <v>129959787</v>
       </c>
       <c r="B130" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14813,10 +14808,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470942</v>
+        <v>470900</v>
       </c>
       <c r="R130" t="n">
-        <v>6770455</v>
+        <v>6770473</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14885,10 +14880,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129959122</v>
+        <v>129959813</v>
       </c>
       <c r="B131" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14920,10 +14915,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470926</v>
+        <v>470942</v>
       </c>
       <c r="R131" t="n">
-        <v>6770613</v>
+        <v>6770455</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14992,10 +14987,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129958842</v>
+        <v>129959122</v>
       </c>
       <c r="B132" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15027,10 +15022,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470820</v>
+        <v>470926</v>
       </c>
       <c r="R132" t="n">
-        <v>6770624</v>
+        <v>6770613</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15099,10 +15094,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129954413</v>
+        <v>129962374</v>
       </c>
       <c r="B133" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15110,34 +15105,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>471028</v>
+        <v>470996</v>
       </c>
       <c r="R133" t="n">
-        <v>6770675</v>
+        <v>6770611</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15209,7 +15209,7 @@
         <v>129962376</v>
       </c>
       <c r="B134" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15318,10 +15318,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129961622</v>
+        <v>129958499</v>
       </c>
       <c r="B135" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15353,10 +15353,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>471262</v>
+        <v>470850</v>
       </c>
       <c r="R135" t="n">
-        <v>6770622</v>
+        <v>6770690</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15425,10 +15425,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129959047</v>
+        <v>129959501</v>
       </c>
       <c r="B136" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15460,10 +15460,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470908</v>
+        <v>470807</v>
       </c>
       <c r="R136" t="n">
-        <v>6770622</v>
+        <v>6770491</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15532,10 +15532,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129959501</v>
+        <v>129955100</v>
       </c>
       <c r="B137" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15567,10 +15567,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470807</v>
+        <v>470981</v>
       </c>
       <c r="R137" t="n">
-        <v>6770491</v>
+        <v>6770691</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15639,10 +15639,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129955100</v>
+        <v>129961622</v>
       </c>
       <c r="B138" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15674,10 +15674,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470981</v>
+        <v>471262</v>
       </c>
       <c r="R138" t="n">
-        <v>6770691</v>
+        <v>6770622</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15746,10 +15746,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129954531</v>
+        <v>129958010</v>
       </c>
       <c r="B139" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15781,10 +15781,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>471106</v>
+        <v>470894</v>
       </c>
       <c r="R139" t="n">
-        <v>6770683</v>
+        <v>6770713</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15853,10 +15853,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129958010</v>
+        <v>129958895</v>
       </c>
       <c r="B140" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470894</v>
+        <v>470887</v>
       </c>
       <c r="R140" t="n">
-        <v>6770713</v>
+        <v>6770658</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15960,10 +15960,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129958895</v>
+        <v>129959047</v>
       </c>
       <c r="B141" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15995,10 +15995,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>470887</v>
+        <v>470908</v>
       </c>
       <c r="R141" t="n">
-        <v>6770658</v>
+        <v>6770622</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16067,10 +16067,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129958499</v>
+        <v>129954531</v>
       </c>
       <c r="B142" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16102,10 +16102,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>470850</v>
+        <v>471106</v>
       </c>
       <c r="R142" t="n">
-        <v>6770690</v>
+        <v>6770683</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16177,7 +16177,7 @@
         <v>129959110</v>
       </c>
       <c r="B143" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16286,45 +16286,50 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129962073</v>
+        <v>129960827</v>
       </c>
       <c r="B144" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471222</v>
+        <v>471078</v>
       </c>
       <c r="R144" t="n">
-        <v>6770635</v>
+        <v>6770561</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16393,10 +16398,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129962260</v>
+        <v>129958802</v>
       </c>
       <c r="B145" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16428,10 +16433,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>471044</v>
+        <v>470858</v>
       </c>
       <c r="R145" t="n">
-        <v>6770615</v>
+        <v>6770602</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16500,10 +16505,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129959352</v>
+        <v>129962430</v>
       </c>
       <c r="B146" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16511,34 +16516,39 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>470879</v>
+        <v>470989</v>
       </c>
       <c r="R146" t="n">
-        <v>6770545</v>
+        <v>6770629</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16607,10 +16617,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129958937</v>
+        <v>129962343</v>
       </c>
       <c r="B147" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16618,34 +16628,39 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470897</v>
+        <v>471017</v>
       </c>
       <c r="R147" t="n">
-        <v>6770647</v>
+        <v>6770613</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16714,10 +16729,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129958802</v>
+        <v>129962073</v>
       </c>
       <c r="B148" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16749,10 +16764,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470858</v>
+        <v>471222</v>
       </c>
       <c r="R148" t="n">
-        <v>6770602</v>
+        <v>6770635</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16821,50 +16836,45 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129960827</v>
+        <v>129962260</v>
       </c>
       <c r="B149" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>471078</v>
+        <v>471044</v>
       </c>
       <c r="R149" t="n">
-        <v>6770561</v>
+        <v>6770615</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16933,10 +16943,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129962430</v>
+        <v>129959352</v>
       </c>
       <c r="B150" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16944,39 +16954,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>470989</v>
+        <v>470879</v>
       </c>
       <c r="R150" t="n">
-        <v>6770629</v>
+        <v>6770545</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17045,10 +17050,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129962343</v>
+        <v>129958937</v>
       </c>
       <c r="B151" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17056,39 +17061,34 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>471017</v>
+        <v>470897</v>
       </c>
       <c r="R151" t="n">
-        <v>6770613</v>
+        <v>6770647</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17160,7 +17160,7 @@
         <v>129954803</v>
       </c>
       <c r="B152" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>129954534</v>
       </c>
       <c r="B153" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>129959294</v>
       </c>
       <c r="B154" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17478,10 +17478,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129958545</v>
+        <v>129954408</v>
       </c>
       <c r="B155" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17513,10 +17513,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470877</v>
+        <v>471019</v>
       </c>
       <c r="R155" t="n">
-        <v>6770687</v>
+        <v>6770666</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17585,10 +17585,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129954408</v>
+        <v>129958545</v>
       </c>
       <c r="B156" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>471019</v>
+        <v>470877</v>
       </c>
       <c r="R156" t="n">
-        <v>6770666</v>
+        <v>6770687</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17692,10 +17692,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129960642</v>
+        <v>129954445</v>
       </c>
       <c r="B157" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17703,39 +17703,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>471025</v>
+        <v>471053</v>
       </c>
       <c r="R157" t="n">
-        <v>6770488</v>
+        <v>6770682</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17804,10 +17799,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129959389</v>
+        <v>129959519</v>
       </c>
       <c r="B158" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17839,10 +17834,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470824</v>
+        <v>470822</v>
       </c>
       <c r="R158" t="n">
-        <v>6770523</v>
+        <v>6770452</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17911,10 +17906,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129954442</v>
+        <v>129958754</v>
       </c>
       <c r="B159" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17946,10 +17941,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>471053</v>
+        <v>470817</v>
       </c>
       <c r="R159" t="n">
-        <v>6770682</v>
+        <v>6770608</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18018,10 +18013,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129958754</v>
+        <v>129959389</v>
       </c>
       <c r="B160" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18053,10 +18048,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>470817</v>
+        <v>470824</v>
       </c>
       <c r="R160" t="n">
-        <v>6770608</v>
+        <v>6770523</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18128,7 +18123,7 @@
         <v>129960763</v>
       </c>
       <c r="B161" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18235,7 +18230,7 @@
         <v>129954452</v>
       </c>
       <c r="B162" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18339,10 +18334,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129959519</v>
+        <v>129960642</v>
       </c>
       <c r="B163" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18350,34 +18345,39 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>470822</v>
+        <v>471025</v>
       </c>
       <c r="R163" t="n">
-        <v>6770452</v>
+        <v>6770488</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18446,10 +18446,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129954441</v>
+        <v>129958841</v>
       </c>
       <c r="B164" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18457,39 +18457,34 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
-      <c r="M164" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>471052</v>
+        <v>470828</v>
       </c>
       <c r="R164" t="n">
-        <v>6770696</v>
+        <v>6770636</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18561,7 +18556,7 @@
         <v>129958775</v>
       </c>
       <c r="B165" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18668,7 +18663,7 @@
         <v>129960929</v>
       </c>
       <c r="B166" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18775,7 +18770,7 @@
         <v>129955313</v>
       </c>
       <c r="B167" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18882,7 +18877,7 @@
         <v>129959994</v>
       </c>
       <c r="B168" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18986,10 +18981,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129958841</v>
+        <v>129962390</v>
       </c>
       <c r="B169" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19021,10 +19016,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>470828</v>
+        <v>471004</v>
       </c>
       <c r="R169" t="n">
-        <v>6770636</v>
+        <v>6770581</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19093,10 +19088,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129962390</v>
+        <v>129958466</v>
       </c>
       <c r="B170" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19128,10 +19123,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>471004</v>
+        <v>470812</v>
       </c>
       <c r="R170" t="n">
-        <v>6770581</v>
+        <v>6770670</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19200,10 +19195,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129958466</v>
+        <v>129954441</v>
       </c>
       <c r="B171" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19211,34 +19206,39 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>470812</v>
+        <v>471052</v>
       </c>
       <c r="R171" t="n">
-        <v>6770670</v>
+        <v>6770696</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19310,7 +19310,7 @@
         <v>129959740</v>
       </c>
       <c r="B172" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19414,45 +19414,50 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129962243</v>
+        <v>129959285</v>
       </c>
       <c r="B173" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471074</v>
+        <v>470922</v>
       </c>
       <c r="R173" t="n">
-        <v>6770617</v>
+        <v>6770556</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19521,45 +19526,50 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129959717</v>
+        <v>129962436</v>
       </c>
       <c r="B174" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>470864</v>
+        <v>470989</v>
       </c>
       <c r="R174" t="n">
-        <v>6770438</v>
+        <v>6770629</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19628,45 +19638,50 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129962351</v>
+        <v>129959579</v>
       </c>
       <c r="B175" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471017</v>
+        <v>470822</v>
       </c>
       <c r="R175" t="n">
-        <v>6770613</v>
+        <v>6770452</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19735,10 +19750,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129962290</v>
+        <v>129962243</v>
       </c>
       <c r="B176" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19770,10 +19785,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471033</v>
+        <v>471074</v>
       </c>
       <c r="R176" t="n">
-        <v>6770614</v>
+        <v>6770617</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19842,50 +19857,45 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129959285</v>
+        <v>129959717</v>
       </c>
       <c r="B177" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>470922</v>
+        <v>470864</v>
       </c>
       <c r="R177" t="n">
-        <v>6770556</v>
+        <v>6770438</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19954,50 +19964,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129962436</v>
+        <v>129962351</v>
       </c>
       <c r="B178" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>470989</v>
+        <v>471017</v>
       </c>
       <c r="R178" t="n">
-        <v>6770629</v>
+        <v>6770613</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20066,50 +20071,45 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129959579</v>
+        <v>129962290</v>
       </c>
       <c r="B179" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
-      <c r="M179" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>470822</v>
+        <v>471033</v>
       </c>
       <c r="R179" t="n">
-        <v>6770452</v>
+        <v>6770614</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20178,10 +20178,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129962443</v>
+        <v>129961937</v>
       </c>
       <c r="B180" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20213,10 +20213,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>470989</v>
+        <v>471216</v>
       </c>
       <c r="R180" t="n">
-        <v>6770629</v>
+        <v>6770650</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20285,10 +20285,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129961937</v>
+        <v>129958214</v>
       </c>
       <c r="B181" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20320,10 +20320,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471216</v>
+        <v>470823</v>
       </c>
       <c r="R181" t="n">
-        <v>6770650</v>
+        <v>6770705</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20392,10 +20392,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129958214</v>
+        <v>129962443</v>
       </c>
       <c r="B182" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20427,10 +20427,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>470823</v>
+        <v>470989</v>
       </c>
       <c r="R182" t="n">
-        <v>6770705</v>
+        <v>6770629</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20502,7 +20502,7 @@
         <v>129961109</v>
       </c>
       <c r="B183" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20611,10 +20611,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129959870</v>
+        <v>129962447</v>
       </c>
       <c r="B184" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20622,39 +20622,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>470952</v>
+        <v>470993</v>
       </c>
       <c r="R184" t="n">
-        <v>6770464</v>
+        <v>6770643</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20723,10 +20718,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129962447</v>
+        <v>129959256</v>
       </c>
       <c r="B185" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20758,10 +20753,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>470993</v>
+        <v>470922</v>
       </c>
       <c r="R185" t="n">
-        <v>6770643</v>
+        <v>6770556</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20830,10 +20825,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129960864</v>
+        <v>129958694</v>
       </c>
       <c r="B186" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20865,10 +20860,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>471116</v>
+        <v>470844</v>
       </c>
       <c r="R186" t="n">
-        <v>6770565</v>
+        <v>6770699</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20937,10 +20932,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129959256</v>
+        <v>129960864</v>
       </c>
       <c r="B187" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20972,10 +20967,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>470922</v>
+        <v>471116</v>
       </c>
       <c r="R187" t="n">
-        <v>6770556</v>
+        <v>6770565</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21047,7 +21042,7 @@
         <v>129956859</v>
       </c>
       <c r="B188" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21151,10 +21146,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129958694</v>
+        <v>129958228</v>
       </c>
       <c r="B189" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21186,10 +21181,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>470844</v>
+        <v>470813</v>
       </c>
       <c r="R189" t="n">
-        <v>6770699</v>
+        <v>6770681</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21261,7 +21256,7 @@
         <v>129959667</v>
       </c>
       <c r="B190" t="n">
-        <v>91623</v>
+        <v>91626</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21369,10 +21364,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129958228</v>
+        <v>129959870</v>
       </c>
       <c r="B191" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21380,34 +21375,39 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>470813</v>
+        <v>470952</v>
       </c>
       <c r="R191" t="n">
-        <v>6770681</v>
+        <v>6770464</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21476,10 +21476,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129959434</v>
+        <v>129954590</v>
       </c>
       <c r="B192" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21487,39 +21487,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>470824</v>
+        <v>471013</v>
       </c>
       <c r="R192" t="n">
-        <v>6770523</v>
+        <v>6770715</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21588,38 +21583,38 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129958199</v>
+        <v>129959434</v>
       </c>
       <c r="B193" t="n">
-        <v>8450</v>
+        <v>57737</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -21628,10 +21623,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>470823</v>
+        <v>470824</v>
       </c>
       <c r="R193" t="n">
-        <v>6770705</v>
+        <v>6770523</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21700,10 +21695,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129960746</v>
+        <v>129958199</v>
       </c>
       <c r="B194" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21740,10 +21735,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>471053</v>
+        <v>470823</v>
       </c>
       <c r="R194" t="n">
-        <v>6770528</v>
+        <v>6770705</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21812,45 +21807,50 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129954590</v>
+        <v>129960746</v>
       </c>
       <c r="B195" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>471013</v>
+        <v>471053</v>
       </c>
       <c r="R195" t="n">
-        <v>6770715</v>
+        <v>6770528</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21919,10 +21919,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129959567</v>
+        <v>129960891</v>
       </c>
       <c r="B196" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21930,39 +21930,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>470822</v>
+        <v>471147</v>
       </c>
       <c r="R196" t="n">
-        <v>6770452</v>
+        <v>6770575</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22034,7 +22029,7 @@
         <v>129956851</v>
       </c>
       <c r="B197" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22141,7 +22136,7 @@
         <v>129959375</v>
       </c>
       <c r="B198" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22245,10 +22240,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129960891</v>
+        <v>129959567</v>
       </c>
       <c r="B199" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22256,34 +22251,39 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471147</v>
+        <v>470822</v>
       </c>
       <c r="R199" t="n">
-        <v>6770575</v>
+        <v>6770452</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22355,7 +22355,7 @@
         <v>129959924</v>
       </c>
       <c r="B200" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>129962346</v>
       </c>
       <c r="B201" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>129958828</v>
       </c>
       <c r="B202" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>129960843</v>
       </c>
       <c r="B203" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22790,45 +22790,50 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129962379</v>
+        <v>129954662</v>
       </c>
       <c r="B204" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>470996</v>
+        <v>470941</v>
       </c>
       <c r="R204" t="n">
-        <v>6770611</v>
+        <v>6770708</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22897,45 +22902,50 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129962224</v>
+        <v>129959223</v>
       </c>
       <c r="B205" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>471098</v>
+        <v>470921</v>
       </c>
       <c r="R205" t="n">
-        <v>6770634</v>
+        <v>6770579</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23004,10 +23014,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129958691</v>
+        <v>129962379</v>
       </c>
       <c r="B206" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23015,39 +23025,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470844</v>
+        <v>470996</v>
       </c>
       <c r="R206" t="n">
-        <v>6770699</v>
+        <v>6770611</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23116,50 +23121,45 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129954662</v>
+        <v>129962224</v>
       </c>
       <c r="B207" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470941</v>
+        <v>471098</v>
       </c>
       <c r="R207" t="n">
-        <v>6770708</v>
+        <v>6770634</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23228,38 +23228,38 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129959223</v>
+        <v>129958691</v>
       </c>
       <c r="B208" t="n">
-        <v>8450</v>
+        <v>57737</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -23268,10 +23268,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470921</v>
+        <v>470844</v>
       </c>
       <c r="R208" t="n">
-        <v>6770579</v>
+        <v>6770699</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23340,10 +23340,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129962417</v>
+        <v>129958706</v>
       </c>
       <c r="B209" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>471002</v>
+        <v>470816</v>
       </c>
       <c r="R209" t="n">
-        <v>6770618</v>
+        <v>6770646</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23447,10 +23447,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129960884</v>
+        <v>129962417</v>
       </c>
       <c r="B210" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23482,10 +23482,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>471129</v>
+        <v>471002</v>
       </c>
       <c r="R210" t="n">
-        <v>6770567</v>
+        <v>6770618</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23554,10 +23554,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129958706</v>
+        <v>129960884</v>
       </c>
       <c r="B211" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>470816</v>
+        <v>471129</v>
       </c>
       <c r="R211" t="n">
-        <v>6770646</v>
+        <v>6770567</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23661,50 +23661,45 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129959735</v>
+        <v>129960790</v>
       </c>
       <c r="B212" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
-      <c r="M212" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>470868</v>
+        <v>471073</v>
       </c>
       <c r="R212" t="n">
-        <v>6770431</v>
+        <v>6770551</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23773,10 +23768,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129956843</v>
+        <v>129962119</v>
       </c>
       <c r="B213" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23808,10 +23803,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>470953</v>
+        <v>471156</v>
       </c>
       <c r="R213" t="n">
-        <v>6770692</v>
+        <v>6770665</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23880,10 +23875,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129954584</v>
+        <v>129956843</v>
       </c>
       <c r="B214" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23915,10 +23910,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471062</v>
+        <v>470953</v>
       </c>
       <c r="R214" t="n">
-        <v>6770731</v>
+        <v>6770692</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23987,10 +23982,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129960790</v>
+        <v>129954584</v>
       </c>
       <c r="B215" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24022,10 +24017,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471073</v>
+        <v>471062</v>
       </c>
       <c r="R215" t="n">
-        <v>6770551</v>
+        <v>6770731</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24094,10 +24089,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129962119</v>
+        <v>129958133</v>
       </c>
       <c r="B216" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24129,10 +24124,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471156</v>
+        <v>470869</v>
       </c>
       <c r="R216" t="n">
-        <v>6770665</v>
+        <v>6770702</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24201,45 +24196,50 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129958133</v>
+        <v>129959735</v>
       </c>
       <c r="B217" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>470869</v>
+        <v>470868</v>
       </c>
       <c r="R217" t="n">
-        <v>6770702</v>
+        <v>6770431</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24311,7 +24311,7 @@
         <v>129958686</v>
       </c>
       <c r="B218" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24420,53 +24420,48 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129960514</v>
+        <v>129962320</v>
       </c>
       <c r="B219" t="n">
-        <v>8450</v>
+        <v>79087</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>470976</v>
+        <v>471024</v>
       </c>
       <c r="R219" t="n">
-        <v>6770536</v>
+        <v>6770624</v>
       </c>
       <c r="S219" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24532,10 +24527,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129962320</v>
+        <v>129960823</v>
       </c>
       <c r="B220" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24567,10 +24562,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>471024</v>
+        <v>471078</v>
       </c>
       <c r="R220" t="n">
-        <v>6770624</v>
+        <v>6770561</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24613,6 +24608,11 @@
       <c r="AB220" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24639,48 +24639,53 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129960823</v>
+        <v>129960514</v>
       </c>
       <c r="B221" t="n">
-        <v>79084</v>
+        <v>8451</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>471078</v>
+        <v>470976</v>
       </c>
       <c r="R221" t="n">
-        <v>6770561</v>
+        <v>6770536</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24720,11 +24725,6 @@
       <c r="AB221" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24751,10 +24751,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129957253</v>
+        <v>129959250</v>
       </c>
       <c r="B222" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24762,39 +24762,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470916</v>
+        <v>470943</v>
       </c>
       <c r="R222" t="n">
-        <v>6770721</v>
+        <v>6770559</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24863,10 +24858,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129959250</v>
+        <v>129961818</v>
       </c>
       <c r="B223" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24898,10 +24893,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>470943</v>
+        <v>471228</v>
       </c>
       <c r="R223" t="n">
-        <v>6770559</v>
+        <v>6770667</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24970,10 +24965,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129961818</v>
+        <v>129957969</v>
       </c>
       <c r="B224" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25005,10 +25000,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>471228</v>
+        <v>470911</v>
       </c>
       <c r="R224" t="n">
-        <v>6770667</v>
+        <v>6770707</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25077,10 +25072,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129957969</v>
+        <v>129957253</v>
       </c>
       <c r="B225" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25088,34 +25083,39 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470911</v>
+        <v>470916</v>
       </c>
       <c r="R225" t="n">
-        <v>6770707</v>
+        <v>6770721</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25187,7 +25187,7 @@
         <v>129959441</v>
       </c>
       <c r="B226" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25299,7 +25299,7 @@
         <v>129958131</v>
       </c>
       <c r="B227" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25411,7 +25411,7 @@
         <v>129959710</v>
       </c>
       <c r="B228" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -25523,7 +25523,7 @@
         <v>129960657</v>
       </c>
       <c r="B229" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -25635,7 +25635,7 @@
         <v>129959730</v>
       </c>
       <c r="B230" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>129960437</v>
       </c>
       <c r="B231" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>129960691</v>
       </c>
       <c r="B232" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>129958151</v>
       </c>
       <c r="B233" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>129958795</v>
       </c>
       <c r="B234" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -11524,10 +11524,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944544</v>
+        <v>129945156</v>
       </c>
       <c r="B100" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11535,34 +11535,39 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471330</v>
+        <v>471198</v>
       </c>
       <c r="R100" t="n">
-        <v>6770712</v>
+        <v>6770725</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11631,10 +11636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129945156</v>
+        <v>129944544</v>
       </c>
       <c r="B101" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11642,39 +11647,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471198</v>
+        <v>471330</v>
       </c>
       <c r="R101" t="n">
-        <v>6770725</v>
+        <v>6770712</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12283,10 +12283,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129943849</v>
+        <v>129943541</v>
       </c>
       <c r="B107" t="n">
-        <v>91626</v>
+        <v>79087</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12294,38 +12294,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471451</v>
+        <v>471478</v>
       </c>
       <c r="R107" t="n">
-        <v>6770706</v>
+        <v>6770707</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12394,10 +12390,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129943914</v>
+        <v>129943849</v>
       </c>
       <c r="B108" t="n">
-        <v>79087</v>
+        <v>91626</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12405,34 +12401,38 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471432</v>
+        <v>471451</v>
       </c>
       <c r="R108" t="n">
-        <v>6770701</v>
+        <v>6770706</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12501,7 +12501,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129944592</v>
+        <v>129943914</v>
       </c>
       <c r="B109" t="n">
         <v>79087</v>
@@ -12536,10 +12536,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471313</v>
+        <v>471432</v>
       </c>
       <c r="R109" t="n">
-        <v>6770688</v>
+        <v>6770701</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12608,7 +12608,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129943541</v>
+        <v>129944592</v>
       </c>
       <c r="B110" t="n">
         <v>79087</v>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471478</v>
+        <v>471313</v>
       </c>
       <c r="R110" t="n">
-        <v>6770707</v>
+        <v>6770688</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -16286,50 +16286,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129960827</v>
+        <v>129958802</v>
       </c>
       <c r="B144" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471078</v>
+        <v>470858</v>
       </c>
       <c r="R144" t="n">
-        <v>6770561</v>
+        <v>6770602</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16398,7 +16393,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129958802</v>
+        <v>129962073</v>
       </c>
       <c r="B145" t="n">
         <v>79087</v>
@@ -16433,10 +16428,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>470858</v>
+        <v>471222</v>
       </c>
       <c r="R145" t="n">
-        <v>6770602</v>
+        <v>6770635</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16505,10 +16500,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129962430</v>
+        <v>129962260</v>
       </c>
       <c r="B146" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16516,39 +16511,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>470989</v>
+        <v>471044</v>
       </c>
       <c r="R146" t="n">
-        <v>6770629</v>
+        <v>6770615</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16617,10 +16607,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129962343</v>
+        <v>129959352</v>
       </c>
       <c r="B147" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16628,39 +16618,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>471017</v>
+        <v>470879</v>
       </c>
       <c r="R147" t="n">
-        <v>6770613</v>
+        <v>6770545</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16729,7 +16714,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129962073</v>
+        <v>129958937</v>
       </c>
       <c r="B148" t="n">
         <v>79087</v>
@@ -16764,10 +16749,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>471222</v>
+        <v>470897</v>
       </c>
       <c r="R148" t="n">
-        <v>6770635</v>
+        <v>6770647</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16836,10 +16821,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129962260</v>
+        <v>129962430</v>
       </c>
       <c r="B149" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16847,34 +16832,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>471044</v>
+        <v>470989</v>
       </c>
       <c r="R149" t="n">
-        <v>6770615</v>
+        <v>6770629</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16943,10 +16933,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129959352</v>
+        <v>129962343</v>
       </c>
       <c r="B150" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16954,34 +16944,39 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>470879</v>
+        <v>471017</v>
       </c>
       <c r="R150" t="n">
-        <v>6770545</v>
+        <v>6770613</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17050,45 +17045,50 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129958937</v>
+        <v>129960827</v>
       </c>
       <c r="B151" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>470897</v>
+        <v>471078</v>
       </c>
       <c r="R151" t="n">
-        <v>6770647</v>
+        <v>6770561</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -25632,10 +25632,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129959730</v>
+        <v>129960437</v>
       </c>
       <c r="B230" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25643,39 +25643,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>470868</v>
+        <v>470948</v>
       </c>
       <c r="R230" t="n">
-        <v>6770431</v>
+        <v>6770533</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25744,10 +25739,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129960437</v>
+        <v>129959730</v>
       </c>
       <c r="B231" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25755,34 +25750,39 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>470948</v>
+        <v>470868</v>
       </c>
       <c r="R231" t="n">
-        <v>6770533</v>
+        <v>6770431</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -20178,7 +20178,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129961937</v>
+        <v>129962443</v>
       </c>
       <c r="B180" t="n">
         <v>79087</v>
@@ -20213,10 +20213,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>471216</v>
+        <v>470989</v>
       </c>
       <c r="R180" t="n">
-        <v>6770650</v>
+        <v>6770629</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20285,7 +20285,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129958214</v>
+        <v>129961937</v>
       </c>
       <c r="B181" t="n">
         <v>79087</v>
@@ -20320,10 +20320,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>470823</v>
+        <v>471216</v>
       </c>
       <c r="R181" t="n">
-        <v>6770705</v>
+        <v>6770650</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20392,7 +20392,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129962443</v>
+        <v>129958214</v>
       </c>
       <c r="B182" t="n">
         <v>79087</v>
@@ -20427,10 +20427,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>470989</v>
+        <v>470823</v>
       </c>
       <c r="R182" t="n">
-        <v>6770629</v>
+        <v>6770705</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20611,10 +20611,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129962447</v>
+        <v>129959667</v>
       </c>
       <c r="B184" t="n">
-        <v>79087</v>
+        <v>91626</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20622,34 +20622,38 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>470993</v>
+        <v>470864</v>
       </c>
       <c r="R184" t="n">
-        <v>6770643</v>
+        <v>6770438</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20718,7 +20722,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129959256</v>
+        <v>129962447</v>
       </c>
       <c r="B185" t="n">
         <v>79087</v>
@@ -20753,10 +20757,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>470922</v>
+        <v>470993</v>
       </c>
       <c r="R185" t="n">
-        <v>6770556</v>
+        <v>6770643</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20825,7 +20829,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129958694</v>
+        <v>129959256</v>
       </c>
       <c r="B186" t="n">
         <v>79087</v>
@@ -20860,10 +20864,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>470844</v>
+        <v>470922</v>
       </c>
       <c r="R186" t="n">
-        <v>6770699</v>
+        <v>6770556</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20932,7 +20936,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129960864</v>
+        <v>129958694</v>
       </c>
       <c r="B187" t="n">
         <v>79087</v>
@@ -20967,10 +20971,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>471116</v>
+        <v>470844</v>
       </c>
       <c r="R187" t="n">
-        <v>6770565</v>
+        <v>6770699</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21039,7 +21043,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129956859</v>
+        <v>129960864</v>
       </c>
       <c r="B188" t="n">
         <v>79087</v>
@@ -21074,10 +21078,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>470936</v>
+        <v>471116</v>
       </c>
       <c r="R188" t="n">
-        <v>6770721</v>
+        <v>6770565</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21146,7 +21150,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129958228</v>
+        <v>129956859</v>
       </c>
       <c r="B189" t="n">
         <v>79087</v>
@@ -21181,10 +21185,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>470813</v>
+        <v>470936</v>
       </c>
       <c r="R189" t="n">
-        <v>6770681</v>
+        <v>6770721</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21253,10 +21257,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129959667</v>
+        <v>129958228</v>
       </c>
       <c r="B190" t="n">
-        <v>91626</v>
+        <v>79087</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21264,38 +21268,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>470864</v>
+        <v>470813</v>
       </c>
       <c r="R190" t="n">
-        <v>6770438</v>
+        <v>6770681</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -23661,7 +23661,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129960790</v>
+        <v>129956843</v>
       </c>
       <c r="B212" t="n">
         <v>79087</v>
@@ -23696,10 +23696,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>471073</v>
+        <v>470953</v>
       </c>
       <c r="R212" t="n">
-        <v>6770551</v>
+        <v>6770692</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23768,7 +23768,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129962119</v>
+        <v>129954584</v>
       </c>
       <c r="B213" t="n">
         <v>79087</v>
@@ -23803,10 +23803,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>471156</v>
+        <v>471062</v>
       </c>
       <c r="R213" t="n">
-        <v>6770665</v>
+        <v>6770731</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23875,7 +23875,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129956843</v>
+        <v>129958133</v>
       </c>
       <c r="B214" t="n">
         <v>79087</v>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>470953</v>
+        <v>470869</v>
       </c>
       <c r="R214" t="n">
-        <v>6770692</v>
+        <v>6770702</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23982,45 +23982,50 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129954584</v>
+        <v>129959735</v>
       </c>
       <c r="B215" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471062</v>
+        <v>470868</v>
       </c>
       <c r="R215" t="n">
-        <v>6770731</v>
+        <v>6770431</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24089,7 +24094,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129958133</v>
+        <v>129960790</v>
       </c>
       <c r="B216" t="n">
         <v>79087</v>
@@ -24124,10 +24129,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>470869</v>
+        <v>471073</v>
       </c>
       <c r="R216" t="n">
-        <v>6770702</v>
+        <v>6770551</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24196,50 +24201,45 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129959735</v>
+        <v>129962119</v>
       </c>
       <c r="B217" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>470868</v>
+        <v>471156</v>
       </c>
       <c r="R217" t="n">
-        <v>6770431</v>
+        <v>6770665</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24751,45 +24751,50 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129959250</v>
+        <v>129959441</v>
       </c>
       <c r="B222" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470943</v>
+        <v>470824</v>
       </c>
       <c r="R222" t="n">
-        <v>6770559</v>
+        <v>6770523</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24858,45 +24863,50 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129961818</v>
+        <v>129958131</v>
       </c>
       <c r="B223" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>471228</v>
+        <v>470869</v>
       </c>
       <c r="R223" t="n">
-        <v>6770667</v>
+        <v>6770702</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24965,45 +24975,50 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129957969</v>
+        <v>129959710</v>
       </c>
       <c r="B224" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470911</v>
+        <v>470864</v>
       </c>
       <c r="R224" t="n">
-        <v>6770707</v>
+        <v>6770438</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25072,38 +25087,38 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129957253</v>
+        <v>129960657</v>
       </c>
       <c r="B225" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -25112,10 +25127,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470916</v>
+        <v>471025</v>
       </c>
       <c r="R225" t="n">
-        <v>6770721</v>
+        <v>6770488</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25184,50 +25199,45 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129959441</v>
+        <v>129959250</v>
       </c>
       <c r="B226" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>470824</v>
+        <v>470943</v>
       </c>
       <c r="R226" t="n">
-        <v>6770523</v>
+        <v>6770559</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25296,50 +25306,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129958131</v>
+        <v>129961818</v>
       </c>
       <c r="B227" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>470869</v>
+        <v>471228</v>
       </c>
       <c r="R227" t="n">
-        <v>6770702</v>
+        <v>6770667</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25408,50 +25413,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129959710</v>
+        <v>129957969</v>
       </c>
       <c r="B228" t="n">
-        <v>8451</v>
+        <v>79087</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470864</v>
+        <v>470911</v>
       </c>
       <c r="R228" t="n">
-        <v>6770438</v>
+        <v>6770707</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25520,38 +25520,38 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129960657</v>
+        <v>129957253</v>
       </c>
       <c r="B229" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25560,10 +25560,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>471025</v>
+        <v>470916</v>
       </c>
       <c r="R229" t="n">
-        <v>6770488</v>
+        <v>6770721</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25632,10 +25632,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129960437</v>
+        <v>129959730</v>
       </c>
       <c r="B230" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25643,34 +25643,39 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>470948</v>
+        <v>470868</v>
       </c>
       <c r="R230" t="n">
-        <v>6770533</v>
+        <v>6770431</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25739,10 +25744,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129959730</v>
+        <v>129960437</v>
       </c>
       <c r="B231" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25750,39 +25755,34 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>470868</v>
+        <v>470948</v>
       </c>
       <c r="R231" t="n">
-        <v>6770431</v>
+        <v>6770533</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -8056,10 +8056,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129946408</v>
+        <v>129944495</v>
       </c>
       <c r="B68" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>470921</v>
+        <v>471288</v>
       </c>
       <c r="R68" t="n">
-        <v>6770579</v>
+        <v>6770728</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8163,10 +8163,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129944164</v>
+        <v>129946062</v>
       </c>
       <c r="B69" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471363</v>
+        <v>471161</v>
       </c>
       <c r="R69" t="n">
-        <v>6770736</v>
+        <v>6770705</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,10 +8270,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129944495</v>
+        <v>129946408</v>
       </c>
       <c r="B70" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471288</v>
+        <v>470921</v>
       </c>
       <c r="R70" t="n">
-        <v>6770728</v>
+        <v>6770579</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8377,10 +8377,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129944452</v>
+        <v>129944164</v>
       </c>
       <c r="B71" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8388,39 +8388,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471330</v>
+        <v>471363</v>
       </c>
       <c r="R71" t="n">
-        <v>6770712</v>
+        <v>6770736</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8489,35 +8484,40 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129944454</v>
+        <v>129944452</v>
       </c>
       <c r="B72" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
@@ -8596,32 +8596,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129944817</v>
+        <v>129944454</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8631,10 +8631,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471247</v>
+        <v>471330</v>
       </c>
       <c r="R73" t="n">
-        <v>6770726</v>
+        <v>6770712</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8703,10 +8703,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129946062</v>
+        <v>129944817</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471161</v>
+        <v>471247</v>
       </c>
       <c r="R74" t="n">
-        <v>6770705</v>
+        <v>6770726</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8813,7 +8813,7 @@
         <v>129946170</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>129946586</v>
       </c>
       <c r="B76" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>129944813</v>
       </c>
       <c r="B77" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9131,10 +9131,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129944762</v>
+        <v>129946436</v>
       </c>
       <c r="B78" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9142,34 +9142,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471276</v>
+        <v>470971</v>
       </c>
       <c r="R78" t="n">
-        <v>6770703</v>
+        <v>6770603</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9238,10 +9243,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129946436</v>
+        <v>129944762</v>
       </c>
       <c r="B79" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9249,39 +9254,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470971</v>
+        <v>471276</v>
       </c>
       <c r="R79" t="n">
-        <v>6770603</v>
+        <v>6770703</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9353,7 +9353,7 @@
         <v>129945104</v>
       </c>
       <c r="B80" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>129946182</v>
       </c>
       <c r="B81" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9676,32 +9676,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129946047</v>
+        <v>129944037</v>
       </c>
       <c r="B83" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471161</v>
+        <v>471417</v>
       </c>
       <c r="R83" t="n">
-        <v>6770705</v>
+        <v>6770738</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9783,10 +9783,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944037</v>
+        <v>129944210</v>
       </c>
       <c r="B84" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9818,10 +9818,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471417</v>
+        <v>471390</v>
       </c>
       <c r="R84" t="n">
-        <v>6770738</v>
+        <v>6770705</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9890,32 +9890,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129944210</v>
+        <v>129946047</v>
       </c>
       <c r="B85" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471390</v>
+        <v>471161</v>
       </c>
       <c r="R85" t="n">
         <v>6770705</v>
@@ -10000,7 +10000,7 @@
         <v>129945509</v>
       </c>
       <c r="B86" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>129946029</v>
       </c>
       <c r="B87" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>129944466</v>
       </c>
       <c r="B88" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>129944473</v>
       </c>
       <c r="B89" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10430,10 +10430,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129946708</v>
+        <v>129944975</v>
       </c>
       <c r="B90" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10465,10 +10465,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471171</v>
+        <v>471242</v>
       </c>
       <c r="R90" t="n">
-        <v>6770660</v>
+        <v>6770682</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10537,50 +10537,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129945161</v>
+        <v>129946708</v>
       </c>
       <c r="B91" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471198</v>
+        <v>471171</v>
       </c>
       <c r="R91" t="n">
-        <v>6770725</v>
+        <v>6770660</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10649,45 +10644,50 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129944975</v>
+        <v>129945161</v>
       </c>
       <c r="B92" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471242</v>
+        <v>471198</v>
       </c>
       <c r="R92" t="n">
-        <v>6770682</v>
+        <v>6770725</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129945066</v>
+        <v>129943855</v>
       </c>
       <c r="B93" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10791,10 +10791,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471239</v>
+        <v>471451</v>
       </c>
       <c r="R93" t="n">
-        <v>6770732</v>
+        <v>6770706</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10863,10 +10863,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129944756</v>
+        <v>129945066</v>
       </c>
       <c r="B94" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10898,10 +10898,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471288</v>
+        <v>471239</v>
       </c>
       <c r="R94" t="n">
-        <v>6770685</v>
+        <v>6770732</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10970,50 +10970,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129946444</v>
+        <v>129944756</v>
       </c>
       <c r="B95" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>470971</v>
+        <v>471288</v>
       </c>
       <c r="R95" t="n">
-        <v>6770603</v>
+        <v>6770685</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11082,10 +11077,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129943855</v>
+        <v>129946391</v>
       </c>
       <c r="B96" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11093,34 +11088,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471451</v>
+        <v>470921</v>
       </c>
       <c r="R96" t="n">
-        <v>6770706</v>
+        <v>6770579</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11189,38 +11189,38 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129946391</v>
+        <v>129946444</v>
       </c>
       <c r="B97" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11229,10 +11229,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>470921</v>
+        <v>470971</v>
       </c>
       <c r="R97" t="n">
-        <v>6770579</v>
+        <v>6770603</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11420,7 +11420,7 @@
         <v>129944926</v>
       </c>
       <c r="B99" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11524,10 +11524,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129945156</v>
+        <v>129944544</v>
       </c>
       <c r="B100" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11535,39 +11535,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471198</v>
+        <v>471330</v>
       </c>
       <c r="R100" t="n">
-        <v>6770725</v>
+        <v>6770712</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11636,10 +11631,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129944544</v>
+        <v>129945156</v>
       </c>
       <c r="B101" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11647,34 +11642,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471330</v>
+        <v>471198</v>
       </c>
       <c r="R101" t="n">
-        <v>6770712</v>
+        <v>6770725</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11746,7 +11746,7 @@
         <v>129945457</v>
       </c>
       <c r="B102" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>129943809</v>
       </c>
       <c r="B103" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12069,10 +12069,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129944488</v>
+        <v>129943914</v>
       </c>
       <c r="B105" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12104,10 +12104,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>471318</v>
+        <v>471432</v>
       </c>
       <c r="R105" t="n">
-        <v>6770729</v>
+        <v>6770701</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129944178</v>
+        <v>129944488</v>
       </c>
       <c r="B106" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12211,10 +12211,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471372</v>
+        <v>471318</v>
       </c>
       <c r="R106" t="n">
-        <v>6770719</v>
+        <v>6770729</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12283,10 +12283,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129943541</v>
+        <v>129944178</v>
       </c>
       <c r="B107" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12318,10 +12318,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471478</v>
+        <v>471372</v>
       </c>
       <c r="R107" t="n">
-        <v>6770707</v>
+        <v>6770719</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12390,10 +12390,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129943849</v>
+        <v>129943541</v>
       </c>
       <c r="B108" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12401,38 +12401,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471451</v>
+        <v>471478</v>
       </c>
       <c r="R108" t="n">
-        <v>6770706</v>
+        <v>6770707</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12501,10 +12497,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129943914</v>
+        <v>129944592</v>
       </c>
       <c r="B109" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12536,10 +12532,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471432</v>
+        <v>471313</v>
       </c>
       <c r="R109" t="n">
-        <v>6770701</v>
+        <v>6770688</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12608,10 +12604,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129944592</v>
+        <v>129943849</v>
       </c>
       <c r="B110" t="n">
-        <v>79087</v>
+        <v>91627</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12619,34 +12615,38 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471313</v>
+        <v>471451</v>
       </c>
       <c r="R110" t="n">
-        <v>6770688</v>
+        <v>6770706</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12718,7 +12718,7 @@
         <v>129943763</v>
       </c>
       <c r="B111" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>129944804</v>
       </c>
       <c r="B112" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>129946117</v>
       </c>
       <c r="B114" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>129943529</v>
       </c>
       <c r="B115" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>129946197</v>
       </c>
       <c r="B116" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>129945078</v>
       </c>
       <c r="B117" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>129944523</v>
       </c>
       <c r="B119" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14024,45 +14024,50 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129960901</v>
+        <v>129962376</v>
       </c>
       <c r="B123" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471185</v>
+        <v>470996</v>
       </c>
       <c r="R123" t="n">
-        <v>6770590</v>
+        <v>6770611</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14131,10 +14136,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129957713</v>
+        <v>129960901</v>
       </c>
       <c r="B124" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14166,10 +14171,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>470904</v>
+        <v>471185</v>
       </c>
       <c r="R124" t="n">
-        <v>6770718</v>
+        <v>6770590</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14238,10 +14243,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129958464</v>
+        <v>129960002</v>
       </c>
       <c r="B125" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14273,10 +14278,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470822</v>
+        <v>470932</v>
       </c>
       <c r="R125" t="n">
-        <v>6770673</v>
+        <v>6770480</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14345,10 +14350,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129959479</v>
+        <v>129957713</v>
       </c>
       <c r="B126" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14380,10 +14385,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470837</v>
+        <v>470904</v>
       </c>
       <c r="R126" t="n">
-        <v>6770498</v>
+        <v>6770718</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14452,10 +14457,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129958842</v>
+        <v>129958464</v>
       </c>
       <c r="B127" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14487,10 +14492,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470820</v>
+        <v>470822</v>
       </c>
       <c r="R127" t="n">
-        <v>6770624</v>
+        <v>6770673</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14559,10 +14564,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129954413</v>
+        <v>129959479</v>
       </c>
       <c r="B128" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14594,10 +14599,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>471028</v>
+        <v>470837</v>
       </c>
       <c r="R128" t="n">
-        <v>6770675</v>
+        <v>6770498</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14666,10 +14671,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129960002</v>
+        <v>129959787</v>
       </c>
       <c r="B129" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14701,10 +14706,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470932</v>
+        <v>470900</v>
       </c>
       <c r="R129" t="n">
-        <v>6770480</v>
+        <v>6770473</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14773,10 +14778,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129959787</v>
+        <v>129959813</v>
       </c>
       <c r="B130" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14808,10 +14813,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470900</v>
+        <v>470942</v>
       </c>
       <c r="R130" t="n">
-        <v>6770473</v>
+        <v>6770455</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14880,10 +14885,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129959813</v>
+        <v>129959122</v>
       </c>
       <c r="B131" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14915,10 +14920,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470942</v>
+        <v>470926</v>
       </c>
       <c r="R131" t="n">
-        <v>6770455</v>
+        <v>6770613</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14987,10 +14992,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129959122</v>
+        <v>129958842</v>
       </c>
       <c r="B132" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15022,10 +15027,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470926</v>
+        <v>470820</v>
       </c>
       <c r="R132" t="n">
-        <v>6770613</v>
+        <v>6770624</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15094,10 +15099,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129962374</v>
+        <v>129954413</v>
       </c>
       <c r="B133" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15105,39 +15110,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>470996</v>
+        <v>471028</v>
       </c>
       <c r="R133" t="n">
-        <v>6770611</v>
+        <v>6770675</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15206,38 +15206,38 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129962376</v>
+        <v>129962374</v>
       </c>
       <c r="B134" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -15318,10 +15318,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129958499</v>
+        <v>129959047</v>
       </c>
       <c r="B135" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15353,10 +15353,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470850</v>
+        <v>470908</v>
       </c>
       <c r="R135" t="n">
-        <v>6770690</v>
+        <v>6770622</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15428,7 +15428,7 @@
         <v>129959501</v>
       </c>
       <c r="B136" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15535,7 +15535,7 @@
         <v>129955100</v>
       </c>
       <c r="B137" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15639,10 +15639,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129961622</v>
+        <v>129954531</v>
       </c>
       <c r="B138" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15674,10 +15674,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>471262</v>
+        <v>471106</v>
       </c>
       <c r="R138" t="n">
-        <v>6770622</v>
+        <v>6770683</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15746,10 +15746,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129958010</v>
+        <v>129961622</v>
       </c>
       <c r="B139" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15781,10 +15781,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470894</v>
+        <v>471262</v>
       </c>
       <c r="R139" t="n">
-        <v>6770713</v>
+        <v>6770622</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15853,10 +15853,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129958895</v>
+        <v>129958010</v>
       </c>
       <c r="B140" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470887</v>
+        <v>470894</v>
       </c>
       <c r="R140" t="n">
-        <v>6770658</v>
+        <v>6770713</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15960,10 +15960,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129959047</v>
+        <v>129958895</v>
       </c>
       <c r="B141" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15995,10 +15995,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>470908</v>
+        <v>470887</v>
       </c>
       <c r="R141" t="n">
-        <v>6770622</v>
+        <v>6770658</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16067,10 +16067,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129954531</v>
+        <v>129958499</v>
       </c>
       <c r="B142" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16102,10 +16102,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>471106</v>
+        <v>470850</v>
       </c>
       <c r="R142" t="n">
-        <v>6770683</v>
+        <v>6770690</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16286,10 +16286,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129958802</v>
+        <v>129962073</v>
       </c>
       <c r="B144" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16321,10 +16321,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>470858</v>
+        <v>471222</v>
       </c>
       <c r="R144" t="n">
-        <v>6770602</v>
+        <v>6770635</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16393,10 +16393,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129962073</v>
+        <v>129962260</v>
       </c>
       <c r="B145" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16428,10 +16428,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>471222</v>
+        <v>471044</v>
       </c>
       <c r="R145" t="n">
-        <v>6770635</v>
+        <v>6770615</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16500,10 +16500,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129962260</v>
+        <v>129959352</v>
       </c>
       <c r="B146" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16535,10 +16535,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>471044</v>
+        <v>470879</v>
       </c>
       <c r="R146" t="n">
-        <v>6770615</v>
+        <v>6770545</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16607,10 +16607,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129959352</v>
+        <v>129958937</v>
       </c>
       <c r="B147" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16642,10 +16642,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470879</v>
+        <v>470897</v>
       </c>
       <c r="R147" t="n">
-        <v>6770545</v>
+        <v>6770647</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16714,10 +16714,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129958937</v>
+        <v>129958802</v>
       </c>
       <c r="B148" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16749,10 +16749,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470897</v>
+        <v>470858</v>
       </c>
       <c r="R148" t="n">
-        <v>6770647</v>
+        <v>6770602</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17160,7 +17160,7 @@
         <v>129954803</v>
       </c>
       <c r="B152" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>129954534</v>
       </c>
       <c r="B153" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>129959294</v>
       </c>
       <c r="B154" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17478,10 +17478,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129954408</v>
+        <v>129958545</v>
       </c>
       <c r="B155" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17513,10 +17513,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>471019</v>
+        <v>470877</v>
       </c>
       <c r="R155" t="n">
-        <v>6770666</v>
+        <v>6770687</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17585,10 +17585,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129958545</v>
+        <v>129954408</v>
       </c>
       <c r="B156" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>470877</v>
+        <v>471019</v>
       </c>
       <c r="R156" t="n">
-        <v>6770687</v>
+        <v>6770666</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17692,10 +17692,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129954445</v>
+        <v>129954442</v>
       </c>
       <c r="B157" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17799,10 +17799,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129959519</v>
+        <v>129958754</v>
       </c>
       <c r="B158" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17834,10 +17834,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470822</v>
+        <v>470817</v>
       </c>
       <c r="R158" t="n">
-        <v>6770452</v>
+        <v>6770608</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17906,10 +17906,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129958754</v>
+        <v>129959389</v>
       </c>
       <c r="B159" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17941,10 +17941,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>470817</v>
+        <v>470824</v>
       </c>
       <c r="R159" t="n">
-        <v>6770608</v>
+        <v>6770523</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18013,10 +18013,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129959389</v>
+        <v>129960763</v>
       </c>
       <c r="B160" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18048,10 +18048,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>470824</v>
+        <v>471062</v>
       </c>
       <c r="R160" t="n">
-        <v>6770523</v>
+        <v>6770538</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18120,10 +18120,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129960763</v>
+        <v>129954452</v>
       </c>
       <c r="B161" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18155,10 +18155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>471062</v>
+        <v>471058</v>
       </c>
       <c r="R161" t="n">
-        <v>6770538</v>
+        <v>6770677</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18227,10 +18227,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129954452</v>
+        <v>129959519</v>
       </c>
       <c r="B162" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18262,10 +18262,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>471058</v>
+        <v>470822</v>
       </c>
       <c r="R162" t="n">
-        <v>6770677</v>
+        <v>6770452</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18446,10 +18446,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129958841</v>
+        <v>129958775</v>
       </c>
       <c r="B164" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18481,10 +18481,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>470828</v>
+        <v>470803</v>
       </c>
       <c r="R164" t="n">
-        <v>6770636</v>
+        <v>6770595</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18553,10 +18553,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129958775</v>
+        <v>129960929</v>
       </c>
       <c r="B165" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18588,10 +18588,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>470803</v>
+        <v>471159</v>
       </c>
       <c r="R165" t="n">
-        <v>6770595</v>
+        <v>6770613</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18660,10 +18660,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129960929</v>
+        <v>129955313</v>
       </c>
       <c r="B166" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18695,10 +18695,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>471159</v>
+        <v>470992</v>
       </c>
       <c r="R166" t="n">
-        <v>6770613</v>
+        <v>6770702</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18767,10 +18767,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129955313</v>
+        <v>129959994</v>
       </c>
       <c r="B167" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18802,10 +18802,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470992</v>
+        <v>470954</v>
       </c>
       <c r="R167" t="n">
-        <v>6770702</v>
+        <v>6770475</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18874,10 +18874,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129959994</v>
+        <v>129958841</v>
       </c>
       <c r="B168" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18909,10 +18909,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>470954</v>
+        <v>470828</v>
       </c>
       <c r="R168" t="n">
-        <v>6770475</v>
+        <v>6770636</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18984,7 +18984,7 @@
         <v>129962390</v>
       </c>
       <c r="B169" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19091,7 +19091,7 @@
         <v>129958466</v>
       </c>
       <c r="B170" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19307,45 +19307,50 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129959740</v>
+        <v>129959285</v>
       </c>
       <c r="B172" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>470905</v>
+        <v>470922</v>
       </c>
       <c r="R172" t="n">
-        <v>6770435</v>
+        <v>6770556</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19414,7 +19419,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129959285</v>
+        <v>129962436</v>
       </c>
       <c r="B173" t="n">
         <v>8451</v>
@@ -19454,10 +19459,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>470922</v>
+        <v>470989</v>
       </c>
       <c r="R173" t="n">
-        <v>6770556</v>
+        <v>6770629</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19526,7 +19531,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129962436</v>
+        <v>129959579</v>
       </c>
       <c r="B174" t="n">
         <v>8451</v>
@@ -19566,10 +19571,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>470989</v>
+        <v>470822</v>
       </c>
       <c r="R174" t="n">
-        <v>6770629</v>
+        <v>6770452</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19638,50 +19643,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129959579</v>
+        <v>129959740</v>
       </c>
       <c r="B175" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>470822</v>
+        <v>470905</v>
       </c>
       <c r="R175" t="n">
-        <v>6770452</v>
+        <v>6770435</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19753,7 +19753,7 @@
         <v>129962243</v>
       </c>
       <c r="B176" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19860,7 +19860,7 @@
         <v>129959717</v>
       </c>
       <c r="B177" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>129962351</v>
       </c>
       <c r="B178" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20074,7 +20074,7 @@
         <v>129962290</v>
       </c>
       <c r="B179" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>129962443</v>
       </c>
       <c r="B180" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>129961937</v>
       </c>
       <c r="B181" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20395,7 +20395,7 @@
         <v>129958214</v>
       </c>
       <c r="B182" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20611,10 +20611,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129959667</v>
+        <v>129962447</v>
       </c>
       <c r="B184" t="n">
-        <v>91626</v>
+        <v>79088</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20622,38 +20622,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>470864</v>
+        <v>470993</v>
       </c>
       <c r="R184" t="n">
-        <v>6770438</v>
+        <v>6770643</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20722,10 +20718,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129962447</v>
+        <v>129960864</v>
       </c>
       <c r="B185" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20757,10 +20753,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>470993</v>
+        <v>471116</v>
       </c>
       <c r="R185" t="n">
-        <v>6770643</v>
+        <v>6770565</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20832,7 +20828,7 @@
         <v>129959256</v>
       </c>
       <c r="B186" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20936,10 +20932,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129958694</v>
+        <v>129956859</v>
       </c>
       <c r="B187" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20971,10 +20967,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>470844</v>
+        <v>470936</v>
       </c>
       <c r="R187" t="n">
-        <v>6770699</v>
+        <v>6770721</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21043,10 +21039,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129960864</v>
+        <v>129958694</v>
       </c>
       <c r="B188" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21078,10 +21074,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>471116</v>
+        <v>470844</v>
       </c>
       <c r="R188" t="n">
-        <v>6770565</v>
+        <v>6770699</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21150,10 +21146,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129956859</v>
+        <v>129958228</v>
       </c>
       <c r="B189" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21185,10 +21181,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>470936</v>
+        <v>470813</v>
       </c>
       <c r="R189" t="n">
-        <v>6770721</v>
+        <v>6770681</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21257,10 +21253,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129958228</v>
+        <v>129959667</v>
       </c>
       <c r="B190" t="n">
-        <v>79087</v>
+        <v>91627</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21268,34 +21264,38 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>470813</v>
+        <v>470864</v>
       </c>
       <c r="R190" t="n">
-        <v>6770681</v>
+        <v>6770438</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21479,7 +21479,7 @@
         <v>129954590</v>
       </c>
       <c r="B192" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>129960891</v>
       </c>
       <c r="B196" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>129956851</v>
       </c>
       <c r="B197" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22136,7 +22136,7 @@
         <v>129959375</v>
       </c>
       <c r="B198" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>129958828</v>
       </c>
       <c r="B202" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>129960843</v>
       </c>
       <c r="B203" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22790,50 +22790,45 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129954662</v>
+        <v>129962379</v>
       </c>
       <c r="B204" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>470941</v>
+        <v>470996</v>
       </c>
       <c r="R204" t="n">
-        <v>6770708</v>
+        <v>6770611</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22902,50 +22897,45 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129959223</v>
+        <v>129962224</v>
       </c>
       <c r="B205" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>470921</v>
+        <v>471098</v>
       </c>
       <c r="R205" t="n">
-        <v>6770579</v>
+        <v>6770634</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23014,10 +23004,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129962379</v>
+        <v>129958691</v>
       </c>
       <c r="B206" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23025,34 +23015,39 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470996</v>
+        <v>470844</v>
       </c>
       <c r="R206" t="n">
-        <v>6770611</v>
+        <v>6770699</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23121,45 +23116,50 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129962224</v>
+        <v>129954662</v>
       </c>
       <c r="B207" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>471098</v>
+        <v>470941</v>
       </c>
       <c r="R207" t="n">
-        <v>6770634</v>
+        <v>6770708</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23228,38 +23228,38 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129958691</v>
+        <v>129959223</v>
       </c>
       <c r="B208" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -23268,10 +23268,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470844</v>
+        <v>470921</v>
       </c>
       <c r="R208" t="n">
-        <v>6770699</v>
+        <v>6770579</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23340,10 +23340,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129958706</v>
+        <v>129962417</v>
       </c>
       <c r="B209" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>470816</v>
+        <v>471002</v>
       </c>
       <c r="R209" t="n">
-        <v>6770646</v>
+        <v>6770618</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23447,10 +23447,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129962417</v>
+        <v>129958706</v>
       </c>
       <c r="B210" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23482,10 +23482,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>471002</v>
+        <v>470816</v>
       </c>
       <c r="R210" t="n">
-        <v>6770618</v>
+        <v>6770646</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23557,7 +23557,7 @@
         <v>129960884</v>
       </c>
       <c r="B211" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>129956843</v>
       </c>
       <c r="B212" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23771,7 +23771,7 @@
         <v>129954584</v>
       </c>
       <c r="B213" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23875,10 +23875,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129958133</v>
+        <v>129960790</v>
       </c>
       <c r="B214" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>470869</v>
+        <v>471073</v>
       </c>
       <c r="R214" t="n">
-        <v>6770702</v>
+        <v>6770551</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23982,50 +23982,45 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129959735</v>
+        <v>129962119</v>
       </c>
       <c r="B215" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
-      <c r="M215" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P215" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>470868</v>
+        <v>471156</v>
       </c>
       <c r="R215" t="n">
-        <v>6770431</v>
+        <v>6770665</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24094,10 +24089,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129960790</v>
+        <v>129958133</v>
       </c>
       <c r="B216" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24129,10 +24124,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471073</v>
+        <v>470869</v>
       </c>
       <c r="R216" t="n">
-        <v>6770551</v>
+        <v>6770702</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24201,45 +24196,50 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129962119</v>
+        <v>129959735</v>
       </c>
       <c r="B217" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>471156</v>
+        <v>470868</v>
       </c>
       <c r="R217" t="n">
-        <v>6770665</v>
+        <v>6770431</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24420,10 +24420,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129962320</v>
+        <v>129960823</v>
       </c>
       <c r="B219" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24455,10 +24455,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471024</v>
+        <v>471078</v>
       </c>
       <c r="R219" t="n">
-        <v>6770624</v>
+        <v>6770561</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24501,6 +24501,11 @@
       <c r="AB219" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC219" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24527,10 +24532,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129960823</v>
+        <v>129962320</v>
       </c>
       <c r="B220" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24562,10 +24567,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>471078</v>
+        <v>471024</v>
       </c>
       <c r="R220" t="n">
-        <v>6770561</v>
+        <v>6770624</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24608,11 +24613,6 @@
       <c r="AB220" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC220" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24751,38 +24751,38 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129959441</v>
+        <v>129957253</v>
       </c>
       <c r="B222" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
       <c r="M222" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P222" t="inlineStr">
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470824</v>
+        <v>470916</v>
       </c>
       <c r="R222" t="n">
-        <v>6770523</v>
+        <v>6770721</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24863,7 +24863,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129958131</v>
+        <v>129959710</v>
       </c>
       <c r="B223" t="n">
         <v>8451</v>
@@ -24903,10 +24903,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>470869</v>
+        <v>470864</v>
       </c>
       <c r="R223" t="n">
-        <v>6770702</v>
+        <v>6770438</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24975,7 +24975,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129959710</v>
+        <v>129960657</v>
       </c>
       <c r="B224" t="n">
         <v>8451</v>
@@ -25015,10 +25015,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470864</v>
+        <v>471025</v>
       </c>
       <c r="R224" t="n">
-        <v>6770438</v>
+        <v>6770488</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25087,50 +25087,45 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129960657</v>
+        <v>129959250</v>
       </c>
       <c r="B225" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
-      <c r="M225" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>471025</v>
+        <v>470943</v>
       </c>
       <c r="R225" t="n">
-        <v>6770488</v>
+        <v>6770559</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25199,10 +25194,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129959250</v>
+        <v>129961818</v>
       </c>
       <c r="B226" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25234,10 +25229,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>470943</v>
+        <v>471228</v>
       </c>
       <c r="R226" t="n">
-        <v>6770559</v>
+        <v>6770667</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25306,10 +25301,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129961818</v>
+        <v>129957969</v>
       </c>
       <c r="B227" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25341,10 +25336,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>471228</v>
+        <v>470911</v>
       </c>
       <c r="R227" t="n">
-        <v>6770667</v>
+        <v>6770707</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25413,45 +25408,50 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129957969</v>
+        <v>129959441</v>
       </c>
       <c r="B228" t="n">
-        <v>79087</v>
+        <v>8451</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470911</v>
+        <v>470824</v>
       </c>
       <c r="R228" t="n">
-        <v>6770707</v>
+        <v>6770523</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25520,38 +25520,38 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129957253</v>
+        <v>129958131</v>
       </c>
       <c r="B229" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P229" t="inlineStr">
@@ -25560,10 +25560,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>470916</v>
+        <v>470869</v>
       </c>
       <c r="R229" t="n">
-        <v>6770721</v>
+        <v>6770702</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25632,10 +25632,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129959730</v>
+        <v>129960437</v>
       </c>
       <c r="B230" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25643,39 +25643,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>470868</v>
+        <v>470948</v>
       </c>
       <c r="R230" t="n">
-        <v>6770431</v>
+        <v>6770533</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25744,10 +25739,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129960437</v>
+        <v>129959730</v>
       </c>
       <c r="B231" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25755,34 +25750,39 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>470948</v>
+        <v>470868</v>
       </c>
       <c r="R231" t="n">
-        <v>6770533</v>
+        <v>6770431</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25854,7 +25854,7 @@
         <v>129960691</v>
       </c>
       <c r="B232" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>129958151</v>
       </c>
       <c r="B233" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>129958795</v>
       </c>
       <c r="B234" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -11189,38 +11189,42 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129946444</v>
+        <v>129944878</v>
       </c>
       <c r="B97" t="n">
-        <v>8451</v>
+        <v>57898</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11229,13 +11233,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>470971</v>
+        <v>471258</v>
       </c>
       <c r="R97" t="n">
-        <v>6770603</v>
+        <v>6770712</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11301,42 +11305,38 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129944878</v>
+        <v>129946444</v>
       </c>
       <c r="B98" t="n">
-        <v>57898</v>
+        <v>8451</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>103021</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11345,13 +11345,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471258</v>
+        <v>470971</v>
       </c>
       <c r="R98" t="n">
-        <v>6770712</v>
+        <v>6770603</v>
       </c>
       <c r="S98" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11417,10 +11417,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129944926</v>
+        <v>129945156</v>
       </c>
       <c r="B99" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11428,34 +11428,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471263</v>
+        <v>471198</v>
       </c>
       <c r="R99" t="n">
-        <v>6770694</v>
+        <v>6770725</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11524,7 +11529,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944544</v>
+        <v>129944926</v>
       </c>
       <c r="B100" t="n">
         <v>79088</v>
@@ -11559,10 +11564,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471330</v>
+        <v>471263</v>
       </c>
       <c r="R100" t="n">
-        <v>6770712</v>
+        <v>6770694</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11631,10 +11636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129945156</v>
+        <v>129944544</v>
       </c>
       <c r="B101" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11642,39 +11647,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471198</v>
+        <v>471330</v>
       </c>
       <c r="R101" t="n">
-        <v>6770725</v>
+        <v>6770712</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13362,10 +13362,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129945078</v>
+        <v>129946365</v>
       </c>
       <c r="B117" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13373,34 +13373,39 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>471209</v>
+        <v>470910</v>
       </c>
       <c r="R117" t="n">
-        <v>6770731</v>
+        <v>6770605</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13469,10 +13474,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129946365</v>
+        <v>129945078</v>
       </c>
       <c r="B118" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13480,39 +13485,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>470910</v>
+        <v>471209</v>
       </c>
       <c r="R118" t="n">
-        <v>6770605</v>
+        <v>6770731</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -16286,10 +16286,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129962073</v>
+        <v>129962430</v>
       </c>
       <c r="B144" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16297,34 +16297,39 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471222</v>
+        <v>470989</v>
       </c>
       <c r="R144" t="n">
-        <v>6770635</v>
+        <v>6770629</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16393,10 +16398,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129962260</v>
+        <v>129962343</v>
       </c>
       <c r="B145" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16404,34 +16409,39 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>471044</v>
+        <v>471017</v>
       </c>
       <c r="R145" t="n">
-        <v>6770615</v>
+        <v>6770613</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16500,45 +16510,50 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129959352</v>
+        <v>129960827</v>
       </c>
       <c r="B146" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>470879</v>
+        <v>471078</v>
       </c>
       <c r="R146" t="n">
-        <v>6770545</v>
+        <v>6770561</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16607,7 +16622,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129958937</v>
+        <v>129962073</v>
       </c>
       <c r="B147" t="n">
         <v>79088</v>
@@ -16642,10 +16657,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470897</v>
+        <v>471222</v>
       </c>
       <c r="R147" t="n">
-        <v>6770647</v>
+        <v>6770635</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16714,7 +16729,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129958802</v>
+        <v>129962260</v>
       </c>
       <c r="B148" t="n">
         <v>79088</v>
@@ -16749,10 +16764,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470858</v>
+        <v>471044</v>
       </c>
       <c r="R148" t="n">
-        <v>6770602</v>
+        <v>6770615</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16821,10 +16836,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129962430</v>
+        <v>129959352</v>
       </c>
       <c r="B149" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16832,39 +16847,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>470989</v>
+        <v>470879</v>
       </c>
       <c r="R149" t="n">
-        <v>6770629</v>
+        <v>6770545</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16933,10 +16943,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129962343</v>
+        <v>129958937</v>
       </c>
       <c r="B150" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16944,39 +16954,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>471017</v>
+        <v>470897</v>
       </c>
       <c r="R150" t="n">
-        <v>6770613</v>
+        <v>6770647</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17045,50 +17050,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129960827</v>
+        <v>129958802</v>
       </c>
       <c r="B151" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>471078</v>
+        <v>470858</v>
       </c>
       <c r="R151" t="n">
-        <v>6770561</v>
+        <v>6770602</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -8056,7 +8056,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129944495</v>
+        <v>129944817</v>
       </c>
       <c r="B68" t="n">
         <v>79088</v>
@@ -8091,10 +8091,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471288</v>
+        <v>471247</v>
       </c>
       <c r="R68" t="n">
-        <v>6770728</v>
+        <v>6770726</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8163,7 +8163,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129946062</v>
+        <v>129944495</v>
       </c>
       <c r="B69" t="n">
         <v>79088</v>
@@ -8198,10 +8198,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471161</v>
+        <v>471288</v>
       </c>
       <c r="R69" t="n">
-        <v>6770705</v>
+        <v>6770728</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129946408</v>
+        <v>129946062</v>
       </c>
       <c r="B70" t="n">
         <v>79088</v>
@@ -8305,10 +8305,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>470921</v>
+        <v>471161</v>
       </c>
       <c r="R70" t="n">
-        <v>6770579</v>
+        <v>6770705</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8377,7 +8377,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129944164</v>
+        <v>129946408</v>
       </c>
       <c r="B71" t="n">
         <v>79088</v>
@@ -8412,10 +8412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471363</v>
+        <v>470921</v>
       </c>
       <c r="R71" t="n">
-        <v>6770736</v>
+        <v>6770579</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8484,10 +8484,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129944452</v>
+        <v>129944164</v>
       </c>
       <c r="B72" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8495,39 +8495,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471330</v>
+        <v>471363</v>
       </c>
       <c r="R72" t="n">
-        <v>6770712</v>
+        <v>6770736</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8596,35 +8591,40 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129944454</v>
+        <v>129944452</v>
       </c>
       <c r="B73" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
@@ -8703,32 +8703,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129944817</v>
+        <v>129944454</v>
       </c>
       <c r="B74" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471247</v>
+        <v>471330</v>
       </c>
       <c r="R74" t="n">
-        <v>6770726</v>
+        <v>6770712</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9131,10 +9131,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129946436</v>
+        <v>129944762</v>
       </c>
       <c r="B78" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9142,39 +9142,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470971</v>
+        <v>471276</v>
       </c>
       <c r="R78" t="n">
-        <v>6770603</v>
+        <v>6770703</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9243,10 +9238,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129944762</v>
+        <v>129946436</v>
       </c>
       <c r="B79" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9254,34 +9249,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471276</v>
+        <v>470971</v>
       </c>
       <c r="R79" t="n">
-        <v>6770703</v>
+        <v>6770603</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9564,50 +9564,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129946321</v>
+        <v>129946047</v>
       </c>
       <c r="B82" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>470871</v>
+        <v>471161</v>
       </c>
       <c r="R82" t="n">
-        <v>6770635</v>
+        <v>6770705</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9890,45 +9885,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129946047</v>
+        <v>129946321</v>
       </c>
       <c r="B85" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471161</v>
+        <v>470871</v>
       </c>
       <c r="R85" t="n">
-        <v>6770705</v>
+        <v>6770635</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -14024,50 +14024,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129962376</v>
+        <v>129960901</v>
       </c>
       <c r="B123" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>470996</v>
+        <v>471185</v>
       </c>
       <c r="R123" t="n">
-        <v>6770611</v>
+        <v>6770590</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14136,7 +14131,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129960901</v>
+        <v>129960002</v>
       </c>
       <c r="B124" t="n">
         <v>79088</v>
@@ -14171,10 +14166,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>471185</v>
+        <v>470932</v>
       </c>
       <c r="R124" t="n">
-        <v>6770590</v>
+        <v>6770480</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14243,7 +14238,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129960002</v>
+        <v>129957713</v>
       </c>
       <c r="B125" t="n">
         <v>79088</v>
@@ -14278,10 +14273,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470932</v>
+        <v>470904</v>
       </c>
       <c r="R125" t="n">
-        <v>6770480</v>
+        <v>6770718</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14350,7 +14345,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129957713</v>
+        <v>129958464</v>
       </c>
       <c r="B126" t="n">
         <v>79088</v>
@@ -14385,10 +14380,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470904</v>
+        <v>470822</v>
       </c>
       <c r="R126" t="n">
-        <v>6770718</v>
+        <v>6770673</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14457,7 +14452,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129958464</v>
+        <v>129959479</v>
       </c>
       <c r="B127" t="n">
         <v>79088</v>
@@ -14492,10 +14487,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470822</v>
+        <v>470837</v>
       </c>
       <c r="R127" t="n">
-        <v>6770673</v>
+        <v>6770498</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14564,7 +14559,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129959479</v>
+        <v>129959787</v>
       </c>
       <c r="B128" t="n">
         <v>79088</v>
@@ -14599,10 +14594,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470837</v>
+        <v>470900</v>
       </c>
       <c r="R128" t="n">
-        <v>6770498</v>
+        <v>6770473</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14671,7 +14666,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129959787</v>
+        <v>129959813</v>
       </c>
       <c r="B129" t="n">
         <v>79088</v>
@@ -14706,10 +14701,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470900</v>
+        <v>470942</v>
       </c>
       <c r="R129" t="n">
-        <v>6770473</v>
+        <v>6770455</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14778,7 +14773,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129959813</v>
+        <v>129959122</v>
       </c>
       <c r="B130" t="n">
         <v>79088</v>
@@ -14813,10 +14808,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470942</v>
+        <v>470926</v>
       </c>
       <c r="R130" t="n">
-        <v>6770455</v>
+        <v>6770613</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14885,7 +14880,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129959122</v>
+        <v>129958842</v>
       </c>
       <c r="B131" t="n">
         <v>79088</v>
@@ -14920,10 +14915,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470926</v>
+        <v>470820</v>
       </c>
       <c r="R131" t="n">
-        <v>6770613</v>
+        <v>6770624</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14992,7 +14987,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129958842</v>
+        <v>129954413</v>
       </c>
       <c r="B132" t="n">
         <v>79088</v>
@@ -15027,10 +15022,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470820</v>
+        <v>471028</v>
       </c>
       <c r="R132" t="n">
-        <v>6770624</v>
+        <v>6770675</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15099,45 +15094,50 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129954413</v>
+        <v>129962376</v>
       </c>
       <c r="B133" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>471028</v>
+        <v>470996</v>
       </c>
       <c r="R133" t="n">
-        <v>6770675</v>
+        <v>6770611</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -21919,45 +21919,50 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129960891</v>
+        <v>129959924</v>
       </c>
       <c r="B196" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>471147</v>
+        <v>470944</v>
       </c>
       <c r="R196" t="n">
-        <v>6770575</v>
+        <v>6770458</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22026,45 +22031,50 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129956851</v>
+        <v>129962346</v>
       </c>
       <c r="B197" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>470928</v>
+        <v>471017</v>
       </c>
       <c r="R197" t="n">
-        <v>6770695</v>
+        <v>6770613</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22133,10 +22143,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129959375</v>
+        <v>129959567</v>
       </c>
       <c r="B198" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22144,34 +22154,39 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>470851</v>
+        <v>470822</v>
       </c>
       <c r="R198" t="n">
-        <v>6770520</v>
+        <v>6770452</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22240,10 +22255,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129959567</v>
+        <v>129960891</v>
       </c>
       <c r="B199" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22251,39 +22266,34 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
-      <c r="M199" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>470822</v>
+        <v>471147</v>
       </c>
       <c r="R199" t="n">
-        <v>6770452</v>
+        <v>6770575</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22352,50 +22362,45 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129959924</v>
+        <v>129956851</v>
       </c>
       <c r="B200" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>470944</v>
+        <v>470928</v>
       </c>
       <c r="R200" t="n">
-        <v>6770458</v>
+        <v>6770695</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22464,50 +22469,45 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129962346</v>
+        <v>129959375</v>
       </c>
       <c r="B201" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>471017</v>
+        <v>470851</v>
       </c>
       <c r="R201" t="n">
-        <v>6770613</v>
+        <v>6770520</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -23447,7 +23447,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129958706</v>
+        <v>129960884</v>
       </c>
       <c r="B210" t="n">
         <v>79088</v>
@@ -23482,10 +23482,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>470816</v>
+        <v>471129</v>
       </c>
       <c r="R210" t="n">
-        <v>6770646</v>
+        <v>6770567</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23554,7 +23554,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129960884</v>
+        <v>129958706</v>
       </c>
       <c r="B211" t="n">
         <v>79088</v>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>471129</v>
+        <v>470816</v>
       </c>
       <c r="R211" t="n">
-        <v>6770567</v>
+        <v>6770646</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -24751,10 +24751,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129957253</v>
+        <v>129959250</v>
       </c>
       <c r="B222" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24762,39 +24762,34 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470916</v>
+        <v>470943</v>
       </c>
       <c r="R222" t="n">
-        <v>6770721</v>
+        <v>6770559</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24863,50 +24858,45 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129959710</v>
+        <v>129961818</v>
       </c>
       <c r="B223" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>470864</v>
+        <v>471228</v>
       </c>
       <c r="R223" t="n">
-        <v>6770438</v>
+        <v>6770667</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24975,50 +24965,45 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129960657</v>
+        <v>129957969</v>
       </c>
       <c r="B224" t="n">
-        <v>8451</v>
+        <v>79088</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>471025</v>
+        <v>470911</v>
       </c>
       <c r="R224" t="n">
-        <v>6770488</v>
+        <v>6770707</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25087,10 +25072,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129959250</v>
+        <v>129957253</v>
       </c>
       <c r="B225" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25098,34 +25083,39 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470943</v>
+        <v>470916</v>
       </c>
       <c r="R225" t="n">
-        <v>6770559</v>
+        <v>6770721</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25194,45 +25184,50 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129961818</v>
+        <v>129959441</v>
       </c>
       <c r="B226" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P226" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>471228</v>
+        <v>470824</v>
       </c>
       <c r="R226" t="n">
-        <v>6770667</v>
+        <v>6770523</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25301,45 +25296,50 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129957969</v>
+        <v>129958131</v>
       </c>
       <c r="B227" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>470911</v>
+        <v>470869</v>
       </c>
       <c r="R227" t="n">
-        <v>6770707</v>
+        <v>6770702</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25408,7 +25408,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129959441</v>
+        <v>129959710</v>
       </c>
       <c r="B228" t="n">
         <v>8451</v>
@@ -25448,10 +25448,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470824</v>
+        <v>470864</v>
       </c>
       <c r="R228" t="n">
-        <v>6770523</v>
+        <v>6770438</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25520,7 +25520,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129958131</v>
+        <v>129960657</v>
       </c>
       <c r="B229" t="n">
         <v>8451</v>
@@ -25560,10 +25560,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>470869</v>
+        <v>471025</v>
       </c>
       <c r="R229" t="n">
-        <v>6770702</v>
+        <v>6770488</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -8059,7 +8059,7 @@
         <v>129944817</v>
       </c>
       <c r="B68" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>129944495</v>
       </c>
       <c r="B69" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8273,7 +8273,7 @@
         <v>129946062</v>
       </c>
       <c r="B70" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
         <v>129946408</v>
       </c>
       <c r="B71" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8487,7 +8487,7 @@
         <v>129944164</v>
       </c>
       <c r="B72" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>129946170</v>
       </c>
       <c r="B75" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>129946586</v>
       </c>
       <c r="B76" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>129944813</v>
       </c>
       <c r="B77" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9131,10 +9131,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129944762</v>
+        <v>129946436</v>
       </c>
       <c r="B78" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9142,34 +9142,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471276</v>
+        <v>470971</v>
       </c>
       <c r="R78" t="n">
-        <v>6770703</v>
+        <v>6770603</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9238,10 +9243,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129946436</v>
+        <v>129944762</v>
       </c>
       <c r="B79" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9249,39 +9254,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470971</v>
+        <v>471276</v>
       </c>
       <c r="R79" t="n">
-        <v>6770603</v>
+        <v>6770703</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9353,7 +9353,7 @@
         <v>129945104</v>
       </c>
       <c r="B80" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>129946182</v>
       </c>
       <c r="B81" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9564,45 +9564,50 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129946047</v>
+        <v>129946321</v>
       </c>
       <c r="B82" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471161</v>
+        <v>470871</v>
       </c>
       <c r="R82" t="n">
-        <v>6770705</v>
+        <v>6770635</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9671,10 +9676,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944037</v>
+        <v>129944210</v>
       </c>
       <c r="B83" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9706,10 +9711,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471417</v>
+        <v>471390</v>
       </c>
       <c r="R83" t="n">
-        <v>6770738</v>
+        <v>6770705</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9778,32 +9783,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944210</v>
+        <v>129946047</v>
       </c>
       <c r="B84" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9813,7 +9818,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471390</v>
+        <v>471161</v>
       </c>
       <c r="R84" t="n">
         <v>6770705</v>
@@ -9885,10 +9890,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129946321</v>
+        <v>129944037</v>
       </c>
       <c r="B85" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9896,39 +9901,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>470871</v>
+        <v>471417</v>
       </c>
       <c r="R85" t="n">
-        <v>6770635</v>
+        <v>6770738</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10000,7 +10000,7 @@
         <v>129945509</v>
       </c>
       <c r="B86" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>129946029</v>
       </c>
       <c r="B87" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>129944466</v>
       </c>
       <c r="B88" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10326,7 +10326,7 @@
         <v>129944473</v>
       </c>
       <c r="B89" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10433,7 +10433,7 @@
         <v>129944975</v>
       </c>
       <c r="B90" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>129946708</v>
       </c>
       <c r="B91" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         <v>129943855</v>
       </c>
       <c r="B93" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>129945066</v>
       </c>
       <c r="B94" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>129944756</v>
       </c>
       <c r="B95" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11077,10 +11077,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129946391</v>
+        <v>129944878</v>
       </c>
       <c r="B96" t="n">
-        <v>57737</v>
+        <v>57899</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11088,27 +11088,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11117,13 +11121,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>470921</v>
+        <v>471258</v>
       </c>
       <c r="R96" t="n">
-        <v>6770579</v>
+        <v>6770712</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11189,10 +11193,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129944878</v>
+        <v>129946391</v>
       </c>
       <c r="B97" t="n">
-        <v>57898</v>
+        <v>57737</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11200,31 +11204,27 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="M97" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11233,13 +11233,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471258</v>
+        <v>470921</v>
       </c>
       <c r="R97" t="n">
-        <v>6770712</v>
+        <v>6770579</v>
       </c>
       <c r="S97" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11532,7 +11532,7 @@
         <v>129944926</v>
       </c>
       <c r="B100" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
         <v>129944544</v>
       </c>
       <c r="B101" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11743,45 +11743,50 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129945457</v>
+        <v>129944062</v>
       </c>
       <c r="B102" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471189</v>
+        <v>471432</v>
       </c>
       <c r="R102" t="n">
-        <v>6770706</v>
+        <v>6770716</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11850,10 +11855,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129943809</v>
+        <v>129945457</v>
       </c>
       <c r="B103" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11885,10 +11890,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471447</v>
+        <v>471189</v>
       </c>
       <c r="R103" t="n">
-        <v>6770716</v>
+        <v>6770706</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11957,47 +11962,42 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129944062</v>
+        <v>129943809</v>
       </c>
       <c r="B104" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471432</v>
+        <v>471447</v>
       </c>
       <c r="R104" t="n">
         <v>6770716</v>
@@ -12072,7 +12072,7 @@
         <v>129943914</v>
       </c>
       <c r="B105" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
         <v>129944488</v>
       </c>
       <c r="B106" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12286,7 +12286,7 @@
         <v>129944178</v>
       </c>
       <c r="B107" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>129943541</v>
       </c>
       <c r="B108" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12500,7 +12500,7 @@
         <v>129944592</v>
       </c>
       <c r="B109" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>129943849</v>
       </c>
       <c r="B110" t="n">
-        <v>91627</v>
+        <v>91644</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>129943763</v>
       </c>
       <c r="B111" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12822,45 +12822,50 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129944804</v>
+        <v>129946334</v>
       </c>
       <c r="B112" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>471271</v>
+        <v>470871</v>
       </c>
       <c r="R112" t="n">
-        <v>6770733</v>
+        <v>6770635</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12929,50 +12934,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129946334</v>
+        <v>129944804</v>
       </c>
       <c r="B113" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>470871</v>
+        <v>471271</v>
       </c>
       <c r="R113" t="n">
-        <v>6770635</v>
+        <v>6770733</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13044,7 +13044,7 @@
         <v>129946117</v>
       </c>
       <c r="B114" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>129943529</v>
       </c>
       <c r="B115" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>129946197</v>
       </c>
       <c r="B116" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>129945078</v>
       </c>
       <c r="B118" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13581,45 +13581,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129944523</v>
+        <v>129945444</v>
       </c>
       <c r="B119" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471303</v>
+        <v>471189</v>
       </c>
       <c r="R119" t="n">
-        <v>6770699</v>
+        <v>6770706</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13688,7 +13693,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129945444</v>
+        <v>129944158</v>
       </c>
       <c r="B120" t="n">
         <v>8451</v>
@@ -13728,10 +13733,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471189</v>
+        <v>471363</v>
       </c>
       <c r="R120" t="n">
-        <v>6770706</v>
+        <v>6770736</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13800,50 +13805,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129944158</v>
+        <v>129944523</v>
       </c>
       <c r="B121" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471363</v>
+        <v>471303</v>
       </c>
       <c r="R121" t="n">
-        <v>6770736</v>
+        <v>6770699</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14024,10 +14024,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129960901</v>
+        <v>129959787</v>
       </c>
       <c r="B123" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471185</v>
+        <v>470900</v>
       </c>
       <c r="R123" t="n">
-        <v>6770590</v>
+        <v>6770473</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14131,10 +14131,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129960002</v>
+        <v>129957713</v>
       </c>
       <c r="B124" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14166,10 +14166,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>470932</v>
+        <v>470904</v>
       </c>
       <c r="R124" t="n">
-        <v>6770480</v>
+        <v>6770718</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14238,10 +14238,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129957713</v>
+        <v>129959479</v>
       </c>
       <c r="B125" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14273,10 +14273,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470904</v>
+        <v>470837</v>
       </c>
       <c r="R125" t="n">
-        <v>6770718</v>
+        <v>6770498</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14345,10 +14345,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129958464</v>
+        <v>129954413</v>
       </c>
       <c r="B126" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14380,10 +14380,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470822</v>
+        <v>471028</v>
       </c>
       <c r="R126" t="n">
-        <v>6770673</v>
+        <v>6770675</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14452,10 +14452,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129959479</v>
+        <v>129959122</v>
       </c>
       <c r="B127" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14487,10 +14487,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470837</v>
+        <v>470926</v>
       </c>
       <c r="R127" t="n">
-        <v>6770498</v>
+        <v>6770613</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14559,10 +14559,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129959787</v>
+        <v>129958842</v>
       </c>
       <c r="B128" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14594,10 +14594,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470900</v>
+        <v>470820</v>
       </c>
       <c r="R128" t="n">
-        <v>6770473</v>
+        <v>6770624</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14669,7 +14669,7 @@
         <v>129959813</v>
       </c>
       <c r="B129" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14773,10 +14773,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129959122</v>
+        <v>129960002</v>
       </c>
       <c r="B130" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14808,10 +14808,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470926</v>
+        <v>470932</v>
       </c>
       <c r="R130" t="n">
-        <v>6770613</v>
+        <v>6770480</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14880,10 +14880,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129958842</v>
+        <v>129958464</v>
       </c>
       <c r="B131" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14915,10 +14915,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470820</v>
+        <v>470822</v>
       </c>
       <c r="R131" t="n">
-        <v>6770624</v>
+        <v>6770673</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14987,10 +14987,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129954413</v>
+        <v>129960901</v>
       </c>
       <c r="B132" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15022,10 +15022,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>471028</v>
+        <v>471185</v>
       </c>
       <c r="R132" t="n">
-        <v>6770675</v>
+        <v>6770590</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15094,38 +15094,38 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129962376</v>
+        <v>129962374</v>
       </c>
       <c r="B133" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P133" t="inlineStr">
@@ -15206,38 +15206,38 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129962374</v>
+        <v>129962376</v>
       </c>
       <c r="B134" t="n">
-        <v>57737</v>
+        <v>8451</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -15318,10 +15318,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129959047</v>
+        <v>129959501</v>
       </c>
       <c r="B135" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15353,10 +15353,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470908</v>
+        <v>470807</v>
       </c>
       <c r="R135" t="n">
-        <v>6770622</v>
+        <v>6770491</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15425,10 +15425,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129959501</v>
+        <v>129954531</v>
       </c>
       <c r="B136" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15460,10 +15460,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470807</v>
+        <v>471106</v>
       </c>
       <c r="R136" t="n">
-        <v>6770491</v>
+        <v>6770683</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15532,10 +15532,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129955100</v>
+        <v>129958010</v>
       </c>
       <c r="B137" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15567,10 +15567,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470981</v>
+        <v>470894</v>
       </c>
       <c r="R137" t="n">
-        <v>6770691</v>
+        <v>6770713</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15639,10 +15639,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129954531</v>
+        <v>129958895</v>
       </c>
       <c r="B138" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15674,10 +15674,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>471106</v>
+        <v>470887</v>
       </c>
       <c r="R138" t="n">
-        <v>6770683</v>
+        <v>6770658</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15746,10 +15746,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129961622</v>
+        <v>129959047</v>
       </c>
       <c r="B139" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15781,7 +15781,7 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>471262</v>
+        <v>470908</v>
       </c>
       <c r="R139" t="n">
         <v>6770622</v>
@@ -15853,10 +15853,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129958010</v>
+        <v>129961622</v>
       </c>
       <c r="B140" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15888,10 +15888,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470894</v>
+        <v>471262</v>
       </c>
       <c r="R140" t="n">
-        <v>6770713</v>
+        <v>6770622</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15960,10 +15960,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129958895</v>
+        <v>129958499</v>
       </c>
       <c r="B141" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15995,10 +15995,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>470887</v>
+        <v>470850</v>
       </c>
       <c r="R141" t="n">
-        <v>6770658</v>
+        <v>6770690</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16067,10 +16067,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129958499</v>
+        <v>129955100</v>
       </c>
       <c r="B142" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16102,10 +16102,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>470850</v>
+        <v>470981</v>
       </c>
       <c r="R142" t="n">
-        <v>6770690</v>
+        <v>6770691</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16286,10 +16286,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129962430</v>
+        <v>129958802</v>
       </c>
       <c r="B144" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16297,39 +16297,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>470989</v>
+        <v>470858</v>
       </c>
       <c r="R144" t="n">
-        <v>6770629</v>
+        <v>6770602</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16398,10 +16393,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129962343</v>
+        <v>129962260</v>
       </c>
       <c r="B145" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16409,39 +16404,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>471017</v>
+        <v>471044</v>
       </c>
       <c r="R145" t="n">
-        <v>6770613</v>
+        <v>6770615</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16510,50 +16500,45 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129960827</v>
+        <v>129959352</v>
       </c>
       <c r="B146" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>471078</v>
+        <v>470879</v>
       </c>
       <c r="R146" t="n">
-        <v>6770561</v>
+        <v>6770545</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16622,10 +16607,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129962073</v>
+        <v>129958937</v>
       </c>
       <c r="B147" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16657,10 +16642,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>471222</v>
+        <v>470897</v>
       </c>
       <c r="R147" t="n">
-        <v>6770635</v>
+        <v>6770647</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16729,10 +16714,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129962260</v>
+        <v>129962073</v>
       </c>
       <c r="B148" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16764,10 +16749,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>471044</v>
+        <v>471222</v>
       </c>
       <c r="R148" t="n">
-        <v>6770615</v>
+        <v>6770635</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16836,10 +16821,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129959352</v>
+        <v>129962430</v>
       </c>
       <c r="B149" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16847,34 +16832,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>470879</v>
+        <v>470989</v>
       </c>
       <c r="R149" t="n">
-        <v>6770545</v>
+        <v>6770629</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16943,10 +16933,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129958937</v>
+        <v>129962343</v>
       </c>
       <c r="B150" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16954,34 +16944,39 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>470897</v>
+        <v>471017</v>
       </c>
       <c r="R150" t="n">
-        <v>6770647</v>
+        <v>6770613</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17050,45 +17045,50 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129958802</v>
+        <v>129960827</v>
       </c>
       <c r="B151" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>470858</v>
+        <v>471078</v>
       </c>
       <c r="R151" t="n">
-        <v>6770602</v>
+        <v>6770561</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17157,10 +17157,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129954803</v>
+        <v>129954534</v>
       </c>
       <c r="B152" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17192,10 +17192,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>470938</v>
+        <v>471086</v>
       </c>
       <c r="R152" t="n">
-        <v>6770693</v>
+        <v>6770684</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17264,10 +17264,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129954534</v>
+        <v>129954803</v>
       </c>
       <c r="B153" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17299,10 +17299,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>471086</v>
+        <v>470938</v>
       </c>
       <c r="R153" t="n">
-        <v>6770684</v>
+        <v>6770693</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17371,10 +17371,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129959294</v>
+        <v>129954408</v>
       </c>
       <c r="B154" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17406,10 +17406,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>470904</v>
+        <v>471019</v>
       </c>
       <c r="R154" t="n">
-        <v>6770537</v>
+        <v>6770666</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17478,10 +17478,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129958545</v>
+        <v>129959294</v>
       </c>
       <c r="B155" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17513,10 +17513,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470877</v>
+        <v>470904</v>
       </c>
       <c r="R155" t="n">
-        <v>6770687</v>
+        <v>6770537</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17585,10 +17585,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129954408</v>
+        <v>129958545</v>
       </c>
       <c r="B156" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>471019</v>
+        <v>470877</v>
       </c>
       <c r="R156" t="n">
-        <v>6770666</v>
+        <v>6770687</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17692,10 +17692,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129954442</v>
+        <v>129959389</v>
       </c>
       <c r="B157" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17727,10 +17727,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>471053</v>
+        <v>470824</v>
       </c>
       <c r="R157" t="n">
-        <v>6770682</v>
+        <v>6770523</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17799,10 +17799,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129958754</v>
+        <v>129959519</v>
       </c>
       <c r="B158" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17834,10 +17834,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470817</v>
+        <v>470822</v>
       </c>
       <c r="R158" t="n">
-        <v>6770608</v>
+        <v>6770452</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17906,10 +17906,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129959389</v>
+        <v>129954452</v>
       </c>
       <c r="B159" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17941,10 +17941,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>470824</v>
+        <v>471058</v>
       </c>
       <c r="R159" t="n">
-        <v>6770523</v>
+        <v>6770677</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18013,10 +18013,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129960763</v>
+        <v>129954442</v>
       </c>
       <c r="B160" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18048,10 +18048,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>471062</v>
+        <v>471053</v>
       </c>
       <c r="R160" t="n">
-        <v>6770538</v>
+        <v>6770682</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18120,10 +18120,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129954452</v>
+        <v>129960763</v>
       </c>
       <c r="B161" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18155,10 +18155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>471058</v>
+        <v>471062</v>
       </c>
       <c r="R161" t="n">
-        <v>6770677</v>
+        <v>6770538</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18227,10 +18227,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129959519</v>
+        <v>129958754</v>
       </c>
       <c r="B162" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18262,10 +18262,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>470822</v>
+        <v>470817</v>
       </c>
       <c r="R162" t="n">
-        <v>6770452</v>
+        <v>6770608</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18446,10 +18446,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129958775</v>
+        <v>129955313</v>
       </c>
       <c r="B164" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18481,10 +18481,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>470803</v>
+        <v>470992</v>
       </c>
       <c r="R164" t="n">
-        <v>6770595</v>
+        <v>6770702</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18556,7 +18556,7 @@
         <v>129960929</v>
       </c>
       <c r="B165" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18660,10 +18660,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129955313</v>
+        <v>129958466</v>
       </c>
       <c r="B166" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18695,10 +18695,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470992</v>
+        <v>470812</v>
       </c>
       <c r="R166" t="n">
-        <v>6770702</v>
+        <v>6770670</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18767,10 +18767,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129959994</v>
+        <v>129958775</v>
       </c>
       <c r="B167" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18802,10 +18802,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470954</v>
+        <v>470803</v>
       </c>
       <c r="R167" t="n">
-        <v>6770475</v>
+        <v>6770595</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18877,7 +18877,7 @@
         <v>129958841</v>
       </c>
       <c r="B168" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18981,10 +18981,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129962390</v>
+        <v>129959994</v>
       </c>
       <c r="B169" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19016,10 +19016,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>471004</v>
+        <v>470954</v>
       </c>
       <c r="R169" t="n">
-        <v>6770581</v>
+        <v>6770475</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19088,10 +19088,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129958466</v>
+        <v>129962390</v>
       </c>
       <c r="B170" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19123,10 +19123,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>470812</v>
+        <v>471004</v>
       </c>
       <c r="R170" t="n">
-        <v>6770670</v>
+        <v>6770581</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19307,50 +19307,45 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129959285</v>
+        <v>129959717</v>
       </c>
       <c r="B172" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>470922</v>
+        <v>470864</v>
       </c>
       <c r="R172" t="n">
-        <v>6770556</v>
+        <v>6770438</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19419,50 +19414,45 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129962436</v>
+        <v>129959740</v>
       </c>
       <c r="B173" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>470989</v>
+        <v>470905</v>
       </c>
       <c r="R173" t="n">
-        <v>6770629</v>
+        <v>6770435</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19531,50 +19521,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129959579</v>
+        <v>129962290</v>
       </c>
       <c r="B174" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>470822</v>
+        <v>471033</v>
       </c>
       <c r="R174" t="n">
-        <v>6770452</v>
+        <v>6770614</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19643,10 +19628,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129959740</v>
+        <v>129962243</v>
       </c>
       <c r="B175" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19678,10 +19663,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>470905</v>
+        <v>471074</v>
       </c>
       <c r="R175" t="n">
-        <v>6770435</v>
+        <v>6770617</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19750,10 +19735,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129962243</v>
+        <v>129962351</v>
       </c>
       <c r="B176" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19785,10 +19770,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471074</v>
+        <v>471017</v>
       </c>
       <c r="R176" t="n">
-        <v>6770617</v>
+        <v>6770613</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19857,45 +19842,50 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129959717</v>
+        <v>129959285</v>
       </c>
       <c r="B177" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>470864</v>
+        <v>470922</v>
       </c>
       <c r="R177" t="n">
-        <v>6770438</v>
+        <v>6770556</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19964,45 +19954,50 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129962351</v>
+        <v>129962436</v>
       </c>
       <c r="B178" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>471017</v>
+        <v>470989</v>
       </c>
       <c r="R178" t="n">
-        <v>6770613</v>
+        <v>6770629</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20071,45 +20066,50 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129962290</v>
+        <v>129959579</v>
       </c>
       <c r="B179" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>471033</v>
+        <v>470822</v>
       </c>
       <c r="R179" t="n">
-        <v>6770614</v>
+        <v>6770452</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20181,7 +20181,7 @@
         <v>129962443</v>
       </c>
       <c r="B180" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20285,10 +20285,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129961937</v>
+        <v>129958214</v>
       </c>
       <c r="B181" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20320,10 +20320,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471216</v>
+        <v>470823</v>
       </c>
       <c r="R181" t="n">
-        <v>6770650</v>
+        <v>6770705</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20392,10 +20392,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129958214</v>
+        <v>129961937</v>
       </c>
       <c r="B182" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20427,10 +20427,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>470823</v>
+        <v>471216</v>
       </c>
       <c r="R182" t="n">
-        <v>6770705</v>
+        <v>6770650</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20611,10 +20611,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129962447</v>
+        <v>129959667</v>
       </c>
       <c r="B184" t="n">
-        <v>79088</v>
+        <v>91644</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20622,34 +20622,38 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>470993</v>
+        <v>470864</v>
       </c>
       <c r="R184" t="n">
-        <v>6770643</v>
+        <v>6770438</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20718,10 +20722,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129960864</v>
+        <v>129962447</v>
       </c>
       <c r="B185" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20753,10 +20757,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>471116</v>
+        <v>470993</v>
       </c>
       <c r="R185" t="n">
-        <v>6770565</v>
+        <v>6770643</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20825,10 +20829,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129959256</v>
+        <v>129958694</v>
       </c>
       <c r="B186" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20860,10 +20864,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>470922</v>
+        <v>470844</v>
       </c>
       <c r="R186" t="n">
-        <v>6770556</v>
+        <v>6770699</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20932,10 +20936,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129956859</v>
+        <v>129959256</v>
       </c>
       <c r="B187" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20967,10 +20971,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>470936</v>
+        <v>470922</v>
       </c>
       <c r="R187" t="n">
-        <v>6770721</v>
+        <v>6770556</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21039,10 +21043,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129958694</v>
+        <v>129956859</v>
       </c>
       <c r="B188" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21074,10 +21078,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>470844</v>
+        <v>470936</v>
       </c>
       <c r="R188" t="n">
-        <v>6770699</v>
+        <v>6770721</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21149,7 +21153,7 @@
         <v>129958228</v>
       </c>
       <c r="B189" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21253,10 +21257,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129959667</v>
+        <v>129960864</v>
       </c>
       <c r="B190" t="n">
-        <v>91627</v>
+        <v>79089</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21264,38 +21268,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>470864</v>
+        <v>471116</v>
       </c>
       <c r="R190" t="n">
-        <v>6770438</v>
+        <v>6770565</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21479,7 +21479,7 @@
         <v>129954590</v>
       </c>
       <c r="B192" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21919,50 +21919,45 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129959924</v>
+        <v>129959375</v>
       </c>
       <c r="B196" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>470944</v>
+        <v>470851</v>
       </c>
       <c r="R196" t="n">
-        <v>6770458</v>
+        <v>6770520</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22031,50 +22026,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129962346</v>
+        <v>129956851</v>
       </c>
       <c r="B197" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>471017</v>
+        <v>470928</v>
       </c>
       <c r="R197" t="n">
-        <v>6770613</v>
+        <v>6770695</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22143,10 +22133,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129959567</v>
+        <v>129960891</v>
       </c>
       <c r="B198" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22154,39 +22144,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>470822</v>
+        <v>471147</v>
       </c>
       <c r="R198" t="n">
-        <v>6770452</v>
+        <v>6770575</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22255,10 +22240,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129960891</v>
+        <v>129959567</v>
       </c>
       <c r="B199" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22266,34 +22251,39 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471147</v>
+        <v>470822</v>
       </c>
       <c r="R199" t="n">
-        <v>6770575</v>
+        <v>6770452</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22362,45 +22352,50 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129956851</v>
+        <v>129959924</v>
       </c>
       <c r="B200" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>470928</v>
+        <v>470944</v>
       </c>
       <c r="R200" t="n">
-        <v>6770695</v>
+        <v>6770458</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22469,45 +22464,50 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129959375</v>
+        <v>129962346</v>
       </c>
       <c r="B201" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>470851</v>
+        <v>471017</v>
       </c>
       <c r="R201" t="n">
-        <v>6770520</v>
+        <v>6770613</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22576,10 +22576,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129958828</v>
+        <v>129960843</v>
       </c>
       <c r="B202" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22611,10 +22611,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>470871</v>
+        <v>471097</v>
       </c>
       <c r="R202" t="n">
-        <v>6770635</v>
+        <v>6770561</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22683,10 +22683,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129960843</v>
+        <v>129958828</v>
       </c>
       <c r="B203" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22718,10 +22718,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>471097</v>
+        <v>470871</v>
       </c>
       <c r="R203" t="n">
-        <v>6770561</v>
+        <v>6770635</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22790,45 +22790,50 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129962379</v>
+        <v>129954662</v>
       </c>
       <c r="B204" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>470996</v>
+        <v>470941</v>
       </c>
       <c r="R204" t="n">
-        <v>6770611</v>
+        <v>6770708</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22897,45 +22902,50 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129962224</v>
+        <v>129959223</v>
       </c>
       <c r="B205" t="n">
-        <v>79088</v>
+        <v>8451</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>471098</v>
+        <v>470921</v>
       </c>
       <c r="R205" t="n">
-        <v>6770634</v>
+        <v>6770579</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23004,10 +23014,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129958691</v>
+        <v>129962379</v>
       </c>
       <c r="B206" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23015,39 +23025,34 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470844</v>
+        <v>470996</v>
       </c>
       <c r="R206" t="n">
-        <v>6770699</v>
+        <v>6770611</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23116,50 +23121,45 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129954662</v>
+        <v>129962224</v>
       </c>
       <c r="B207" t="n">
-        <v>8451</v>
+        <v>79089</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470941</v>
+        <v>471098</v>
       </c>
       <c r="R207" t="n">
-        <v>6770708</v>
+        <v>6770634</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23228,38 +23228,38 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129959223</v>
+        <v>129958691</v>
       </c>
       <c r="B208" t="n">
-        <v>8451</v>
+        <v>57737</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -23268,10 +23268,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470921</v>
+        <v>470844</v>
       </c>
       <c r="R208" t="n">
-        <v>6770579</v>
+        <v>6770699</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23340,10 +23340,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129962417</v>
+        <v>129958706</v>
       </c>
       <c r="B209" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>471002</v>
+        <v>470816</v>
       </c>
       <c r="R209" t="n">
-        <v>6770618</v>
+        <v>6770646</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23447,10 +23447,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129960884</v>
+        <v>129962417</v>
       </c>
       <c r="B210" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23482,10 +23482,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>471129</v>
+        <v>471002</v>
       </c>
       <c r="R210" t="n">
-        <v>6770567</v>
+        <v>6770618</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23554,10 +23554,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129958706</v>
+        <v>129960884</v>
       </c>
       <c r="B211" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>470816</v>
+        <v>471129</v>
       </c>
       <c r="R211" t="n">
-        <v>6770646</v>
+        <v>6770567</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23661,10 +23661,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129956843</v>
+        <v>129962119</v>
       </c>
       <c r="B212" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23696,10 +23696,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>470953</v>
+        <v>471156</v>
       </c>
       <c r="R212" t="n">
-        <v>6770692</v>
+        <v>6770665</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23771,7 +23771,7 @@
         <v>129954584</v>
       </c>
       <c r="B213" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23875,10 +23875,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129960790</v>
+        <v>129956843</v>
       </c>
       <c r="B214" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471073</v>
+        <v>470953</v>
       </c>
       <c r="R214" t="n">
-        <v>6770551</v>
+        <v>6770692</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23982,10 +23982,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129962119</v>
+        <v>129958133</v>
       </c>
       <c r="B215" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24017,10 +24017,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471156</v>
+        <v>470869</v>
       </c>
       <c r="R215" t="n">
-        <v>6770665</v>
+        <v>6770702</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24089,10 +24089,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129958133</v>
+        <v>129960790</v>
       </c>
       <c r="B216" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24124,10 +24124,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>470869</v>
+        <v>471073</v>
       </c>
       <c r="R216" t="n">
-        <v>6770702</v>
+        <v>6770551</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24420,10 +24420,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129960823</v>
+        <v>129962320</v>
       </c>
       <c r="B219" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -24455,10 +24455,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471078</v>
+        <v>471024</v>
       </c>
       <c r="R219" t="n">
-        <v>6770561</v>
+        <v>6770624</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24501,11 +24501,6 @@
       <c r="AB219" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24532,10 +24527,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129962320</v>
+        <v>129960823</v>
       </c>
       <c r="B220" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24567,10 +24562,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>471024</v>
+        <v>471078</v>
       </c>
       <c r="R220" t="n">
-        <v>6770624</v>
+        <v>6770561</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24613,6 +24608,11 @@
       <c r="AB220" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24751,10 +24751,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129959250</v>
+        <v>129961818</v>
       </c>
       <c r="B222" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24786,10 +24786,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470943</v>
+        <v>471228</v>
       </c>
       <c r="R222" t="n">
-        <v>6770559</v>
+        <v>6770667</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24858,10 +24858,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129961818</v>
+        <v>129957969</v>
       </c>
       <c r="B223" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24893,10 +24893,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>471228</v>
+        <v>470911</v>
       </c>
       <c r="R223" t="n">
-        <v>6770667</v>
+        <v>6770707</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24965,10 +24965,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129957969</v>
+        <v>129959250</v>
       </c>
       <c r="B224" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -25000,10 +25000,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470911</v>
+        <v>470943</v>
       </c>
       <c r="R224" t="n">
-        <v>6770707</v>
+        <v>6770559</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25635,7 +25635,7 @@
         <v>129960437</v>
       </c>
       <c r="B230" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25851,10 +25851,10 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129960691</v>
+        <v>129958795</v>
       </c>
       <c r="B232" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25886,10 +25886,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>471056</v>
+        <v>470822</v>
       </c>
       <c r="R232" t="n">
-        <v>6770494</v>
+        <v>6770615</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25932,6 +25932,11 @@
       <c r="AB232" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25961,7 +25966,7 @@
         <v>129958151</v>
       </c>
       <c r="B233" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26065,10 +26070,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129958795</v>
+        <v>129960691</v>
       </c>
       <c r="B234" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26100,10 +26105,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>470822</v>
+        <v>471056</v>
       </c>
       <c r="R234" t="n">
-        <v>6770615</v>
+        <v>6770494</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26146,11 +26151,6 @@
       <c r="AB234" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD234" t="b">

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -10756,10 +10756,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129944878</v>
+        <v>129943855</v>
       </c>
       <c r="B93" t="n">
-        <v>57900</v>
+        <v>79095</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10767,46 +10767,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471258</v>
+        <v>471451</v>
       </c>
       <c r="R93" t="n">
-        <v>6770712</v>
+        <v>6770706</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10872,50 +10863,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129946444</v>
+        <v>129945066</v>
       </c>
       <c r="B94" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>470971</v>
+        <v>471239</v>
       </c>
       <c r="R94" t="n">
-        <v>6770603</v>
+        <v>6770732</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10984,7 +10970,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129943855</v>
+        <v>129944756</v>
       </c>
       <c r="B95" t="n">
         <v>79095</v>
@@ -11019,10 +11005,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471451</v>
+        <v>471288</v>
       </c>
       <c r="R95" t="n">
-        <v>6770706</v>
+        <v>6770685</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11091,10 +11077,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129945066</v>
+        <v>129946391</v>
       </c>
       <c r="B96" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11102,34 +11088,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471239</v>
+        <v>470921</v>
       </c>
       <c r="R96" t="n">
-        <v>6770732</v>
+        <v>6770579</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11198,10 +11189,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129944756</v>
+        <v>129944878</v>
       </c>
       <c r="B97" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11209,37 +11200,46 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471288</v>
+        <v>471258</v>
       </c>
       <c r="R97" t="n">
-        <v>6770685</v>
+        <v>6770712</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11305,38 +11305,38 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129946391</v>
+        <v>129946444</v>
       </c>
       <c r="B98" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>470921</v>
+        <v>470971</v>
       </c>
       <c r="R98" t="n">
-        <v>6770579</v>
+        <v>6770603</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -15318,50 +15318,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129959110</v>
+        <v>129959501</v>
       </c>
       <c r="B135" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470926</v>
+        <v>470807</v>
       </c>
       <c r="R135" t="n">
-        <v>6770613</v>
+        <v>6770491</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15430,7 +15425,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129959501</v>
+        <v>129958895</v>
       </c>
       <c r="B136" t="n">
         <v>79095</v>
@@ -15465,10 +15460,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470807</v>
+        <v>470887</v>
       </c>
       <c r="R136" t="n">
-        <v>6770491</v>
+        <v>6770658</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15537,7 +15532,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129958895</v>
+        <v>129958499</v>
       </c>
       <c r="B137" t="n">
         <v>79095</v>
@@ -15572,10 +15567,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470887</v>
+        <v>470850</v>
       </c>
       <c r="R137" t="n">
-        <v>6770658</v>
+        <v>6770690</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15644,45 +15639,50 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129958499</v>
+        <v>129959110</v>
       </c>
       <c r="B138" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470850</v>
+        <v>470926</v>
       </c>
       <c r="R138" t="n">
-        <v>6770690</v>
+        <v>6770613</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -17692,10 +17692,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129960642</v>
+        <v>129958754</v>
       </c>
       <c r="B157" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17703,39 +17703,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P157" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>471025</v>
+        <v>470817</v>
       </c>
       <c r="R157" t="n">
-        <v>6770488</v>
+        <v>6770608</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17804,7 +17799,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129954442</v>
+        <v>129959389</v>
       </c>
       <c r="B158" t="n">
         <v>79095</v>
@@ -17839,10 +17834,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>471053</v>
+        <v>470824</v>
       </c>
       <c r="R158" t="n">
-        <v>6770682</v>
+        <v>6770523</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17911,10 +17906,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129960763</v>
+        <v>129960642</v>
       </c>
       <c r="B159" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17922,34 +17917,39 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>471062</v>
+        <v>471025</v>
       </c>
       <c r="R159" t="n">
-        <v>6770538</v>
+        <v>6770488</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18018,7 +18018,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129954452</v>
+        <v>129954442</v>
       </c>
       <c r="B160" t="n">
         <v>79095</v>
@@ -18053,10 +18053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>471058</v>
+        <v>471053</v>
       </c>
       <c r="R160" t="n">
-        <v>6770677</v>
+        <v>6770682</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18125,7 +18125,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129959519</v>
+        <v>129960763</v>
       </c>
       <c r="B161" t="n">
         <v>79095</v>
@@ -18160,10 +18160,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>470822</v>
+        <v>471062</v>
       </c>
       <c r="R161" t="n">
-        <v>6770452</v>
+        <v>6770538</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18232,7 +18232,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129958754</v>
+        <v>129954452</v>
       </c>
       <c r="B162" t="n">
         <v>79095</v>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>470817</v>
+        <v>471058</v>
       </c>
       <c r="R162" t="n">
-        <v>6770608</v>
+        <v>6770677</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18339,7 +18339,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129959389</v>
+        <v>129959519</v>
       </c>
       <c r="B163" t="n">
         <v>79095</v>
@@ -18374,10 +18374,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>470824</v>
+        <v>470822</v>
       </c>
       <c r="R163" t="n">
-        <v>6770523</v>
+        <v>6770452</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18446,7 +18446,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129960929</v>
+        <v>129958775</v>
       </c>
       <c r="B164" t="n">
         <v>79095</v>
@@ -18481,10 +18481,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>471159</v>
+        <v>470803</v>
       </c>
       <c r="R164" t="n">
-        <v>6770613</v>
+        <v>6770595</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18553,7 +18553,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129955313</v>
+        <v>129959994</v>
       </c>
       <c r="B165" t="n">
         <v>79095</v>
@@ -18588,10 +18588,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>470992</v>
+        <v>470954</v>
       </c>
       <c r="R165" t="n">
-        <v>6770702</v>
+        <v>6770475</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18660,7 +18660,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129958841</v>
+        <v>129962390</v>
       </c>
       <c r="B166" t="n">
         <v>79095</v>
@@ -18695,10 +18695,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470828</v>
+        <v>471004</v>
       </c>
       <c r="R166" t="n">
-        <v>6770636</v>
+        <v>6770581</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18767,10 +18767,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129958466</v>
+        <v>129954441</v>
       </c>
       <c r="B167" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18778,34 +18778,39 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470812</v>
+        <v>471052</v>
       </c>
       <c r="R167" t="n">
-        <v>6770670</v>
+        <v>6770696</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18874,7 +18879,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129958775</v>
+        <v>129960929</v>
       </c>
       <c r="B168" t="n">
         <v>79095</v>
@@ -18909,10 +18914,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>470803</v>
+        <v>471159</v>
       </c>
       <c r="R168" t="n">
-        <v>6770595</v>
+        <v>6770613</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18981,7 +18986,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129959994</v>
+        <v>129955313</v>
       </c>
       <c r="B169" t="n">
         <v>79095</v>
@@ -19016,10 +19021,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>470954</v>
+        <v>470992</v>
       </c>
       <c r="R169" t="n">
-        <v>6770475</v>
+        <v>6770702</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19088,7 +19093,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129962390</v>
+        <v>129958841</v>
       </c>
       <c r="B170" t="n">
         <v>79095</v>
@@ -19123,10 +19128,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>471004</v>
+        <v>470828</v>
       </c>
       <c r="R170" t="n">
-        <v>6770581</v>
+        <v>6770636</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19195,10 +19200,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129954441</v>
+        <v>129958466</v>
       </c>
       <c r="B171" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19206,39 +19211,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>471052</v>
+        <v>470812</v>
       </c>
       <c r="R171" t="n">
-        <v>6770696</v>
+        <v>6770670</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -20178,7 +20178,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129961937</v>
+        <v>129962443</v>
       </c>
       <c r="B180" t="n">
         <v>79095</v>
@@ -20213,10 +20213,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>471216</v>
+        <v>470989</v>
       </c>
       <c r="R180" t="n">
-        <v>6770650</v>
+        <v>6770629</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20285,7 +20285,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129958214</v>
+        <v>129961937</v>
       </c>
       <c r="B181" t="n">
         <v>79095</v>
@@ -20320,10 +20320,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>470823</v>
+        <v>471216</v>
       </c>
       <c r="R181" t="n">
-        <v>6770705</v>
+        <v>6770650</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20392,50 +20392,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129961109</v>
+        <v>129958214</v>
       </c>
       <c r="B182" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471175</v>
+        <v>470823</v>
       </c>
       <c r="R182" t="n">
-        <v>6770631</v>
+        <v>6770705</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20504,45 +20499,50 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129962443</v>
+        <v>129961109</v>
       </c>
       <c r="B183" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>470989</v>
+        <v>471175</v>
       </c>
       <c r="R183" t="n">
-        <v>6770629</v>
+        <v>6770631</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21476,38 +21476,38 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129959434</v>
+        <v>129958199</v>
       </c>
       <c r="B192" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="M192" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -21516,10 +21516,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>470824</v>
+        <v>470823</v>
       </c>
       <c r="R192" t="n">
-        <v>6770523</v>
+        <v>6770705</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21588,38 +21588,38 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129958199</v>
+        <v>129959434</v>
       </c>
       <c r="B193" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -21628,10 +21628,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>470823</v>
+        <v>470824</v>
       </c>
       <c r="R193" t="n">
-        <v>6770705</v>
+        <v>6770523</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -22790,10 +22790,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129962379</v>
+        <v>129958691</v>
       </c>
       <c r="B204" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22801,34 +22801,39 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>470996</v>
+        <v>470844</v>
       </c>
       <c r="R204" t="n">
-        <v>6770611</v>
+        <v>6770699</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22897,7 +22902,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129962224</v>
+        <v>129962379</v>
       </c>
       <c r="B205" t="n">
         <v>79095</v>
@@ -22932,10 +22937,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>471098</v>
+        <v>470996</v>
       </c>
       <c r="R205" t="n">
-        <v>6770634</v>
+        <v>6770611</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23004,50 +23009,45 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129954662</v>
+        <v>129962224</v>
       </c>
       <c r="B206" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470941</v>
+        <v>471098</v>
       </c>
       <c r="R206" t="n">
-        <v>6770708</v>
+        <v>6770634</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23116,7 +23116,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129959223</v>
+        <v>129954662</v>
       </c>
       <c r="B207" t="n">
         <v>8451</v>
@@ -23156,10 +23156,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470921</v>
+        <v>470941</v>
       </c>
       <c r="R207" t="n">
-        <v>6770579</v>
+        <v>6770708</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23228,38 +23228,38 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129958691</v>
+        <v>129959223</v>
       </c>
       <c r="B208" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="M208" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P208" t="inlineStr">
@@ -23268,10 +23268,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470844</v>
+        <v>470921</v>
       </c>
       <c r="R208" t="n">
-        <v>6770699</v>
+        <v>6770579</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23340,7 +23340,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129960884</v>
+        <v>129962417</v>
       </c>
       <c r="B209" t="n">
         <v>79095</v>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>471129</v>
+        <v>471002</v>
       </c>
       <c r="R209" t="n">
-        <v>6770567</v>
+        <v>6770618</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23447,7 +23447,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129958706</v>
+        <v>129960884</v>
       </c>
       <c r="B210" t="n">
         <v>79095</v>
@@ -23482,10 +23482,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>470816</v>
+        <v>471129</v>
       </c>
       <c r="R210" t="n">
-        <v>6770646</v>
+        <v>6770567</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23554,7 +23554,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129962417</v>
+        <v>129958706</v>
       </c>
       <c r="B211" t="n">
         <v>79095</v>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>471002</v>
+        <v>470816</v>
       </c>
       <c r="R211" t="n">
-        <v>6770618</v>
+        <v>6770646</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -9131,10 +9131,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129946436</v>
+        <v>129944762</v>
       </c>
       <c r="B78" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9142,39 +9142,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470971</v>
+        <v>471276</v>
       </c>
       <c r="R78" t="n">
-        <v>6770603</v>
+        <v>6770703</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9243,10 +9238,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129944762</v>
+        <v>129946436</v>
       </c>
       <c r="B79" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9254,34 +9249,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471276</v>
+        <v>470971</v>
       </c>
       <c r="R79" t="n">
-        <v>6770703</v>
+        <v>6770603</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9564,32 +9564,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129946047</v>
+        <v>129944037</v>
       </c>
       <c r="B82" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471161</v>
+        <v>471417</v>
       </c>
       <c r="R82" t="n">
-        <v>6770705</v>
+        <v>6770738</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9671,7 +9671,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944037</v>
+        <v>129944210</v>
       </c>
       <c r="B83" t="n">
         <v>79095</v>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471417</v>
+        <v>471390</v>
       </c>
       <c r="R83" t="n">
-        <v>6770738</v>
+        <v>6770705</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9778,10 +9778,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944210</v>
+        <v>129946321</v>
       </c>
       <c r="B84" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9789,34 +9789,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471390</v>
+        <v>470871</v>
       </c>
       <c r="R84" t="n">
-        <v>6770705</v>
+        <v>6770635</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9885,50 +9890,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129946321</v>
+        <v>129946047</v>
       </c>
       <c r="B85" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>470871</v>
+        <v>471161</v>
       </c>
       <c r="R85" t="n">
-        <v>6770635</v>
+        <v>6770705</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129943855</v>
+        <v>129944878</v>
       </c>
       <c r="B93" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10767,37 +10767,46 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471451</v>
+        <v>471258</v>
       </c>
       <c r="R93" t="n">
-        <v>6770706</v>
+        <v>6770712</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10863,45 +10872,50 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129945066</v>
+        <v>129946444</v>
       </c>
       <c r="B94" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471239</v>
+        <v>470971</v>
       </c>
       <c r="R94" t="n">
-        <v>6770732</v>
+        <v>6770603</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10970,7 +10984,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129944756</v>
+        <v>129943855</v>
       </c>
       <c r="B95" t="n">
         <v>79095</v>
@@ -11005,10 +11019,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471288</v>
+        <v>471451</v>
       </c>
       <c r="R95" t="n">
-        <v>6770685</v>
+        <v>6770706</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11077,10 +11091,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129946391</v>
+        <v>129945066</v>
       </c>
       <c r="B96" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11088,39 +11102,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>470921</v>
+        <v>471239</v>
       </c>
       <c r="R96" t="n">
-        <v>6770579</v>
+        <v>6770732</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11189,10 +11198,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129944878</v>
+        <v>129944756</v>
       </c>
       <c r="B97" t="n">
-        <v>57900</v>
+        <v>79095</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11200,46 +11209,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471258</v>
+        <v>471288</v>
       </c>
       <c r="R97" t="n">
-        <v>6770712</v>
+        <v>6770685</v>
       </c>
       <c r="S97" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11305,38 +11305,38 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129946444</v>
+        <v>129946391</v>
       </c>
       <c r="B98" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>470971</v>
+        <v>470921</v>
       </c>
       <c r="R98" t="n">
-        <v>6770603</v>
+        <v>6770579</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11417,10 +11417,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129944926</v>
+        <v>129945156</v>
       </c>
       <c r="B99" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11428,34 +11428,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471263</v>
+        <v>471198</v>
       </c>
       <c r="R99" t="n">
-        <v>6770694</v>
+        <v>6770725</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11524,7 +11529,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944544</v>
+        <v>129944926</v>
       </c>
       <c r="B100" t="n">
         <v>79095</v>
@@ -11559,10 +11564,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471330</v>
+        <v>471263</v>
       </c>
       <c r="R100" t="n">
-        <v>6770712</v>
+        <v>6770694</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11631,10 +11636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129945156</v>
+        <v>129944544</v>
       </c>
       <c r="B101" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11642,39 +11647,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471198</v>
+        <v>471330</v>
       </c>
       <c r="R101" t="n">
-        <v>6770725</v>
+        <v>6770712</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -16286,7 +16286,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129958802</v>
+        <v>129962260</v>
       </c>
       <c r="B144" t="n">
         <v>79095</v>
@@ -16321,10 +16321,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>470858</v>
+        <v>471044</v>
       </c>
       <c r="R144" t="n">
-        <v>6770602</v>
+        <v>6770615</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16393,10 +16393,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129962430</v>
+        <v>129959352</v>
       </c>
       <c r="B145" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16404,39 +16404,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="M145" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P145" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>470989</v>
+        <v>470879</v>
       </c>
       <c r="R145" t="n">
-        <v>6770629</v>
+        <v>6770545</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16505,10 +16500,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129962343</v>
+        <v>129958937</v>
       </c>
       <c r="B146" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16516,39 +16511,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>471017</v>
+        <v>470897</v>
       </c>
       <c r="R146" t="n">
-        <v>6770613</v>
+        <v>6770647</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16617,45 +16607,50 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129962073</v>
+        <v>129960827</v>
       </c>
       <c r="B147" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>471222</v>
+        <v>471078</v>
       </c>
       <c r="R147" t="n">
-        <v>6770635</v>
+        <v>6770561</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16724,7 +16719,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129962260</v>
+        <v>129958802</v>
       </c>
       <c r="B148" t="n">
         <v>79095</v>
@@ -16759,10 +16754,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>471044</v>
+        <v>470858</v>
       </c>
       <c r="R148" t="n">
-        <v>6770615</v>
+        <v>6770602</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16831,10 +16826,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129959352</v>
+        <v>129962430</v>
       </c>
       <c r="B149" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16842,34 +16837,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>470879</v>
+        <v>470989</v>
       </c>
       <c r="R149" t="n">
-        <v>6770545</v>
+        <v>6770629</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16938,10 +16938,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129958937</v>
+        <v>129962343</v>
       </c>
       <c r="B150" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16949,34 +16949,39 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>470897</v>
+        <v>471017</v>
       </c>
       <c r="R150" t="n">
-        <v>6770647</v>
+        <v>6770613</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17045,50 +17050,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129960827</v>
+        <v>129962073</v>
       </c>
       <c r="B151" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>471078</v>
+        <v>471222</v>
       </c>
       <c r="R151" t="n">
-        <v>6770561</v>
+        <v>6770635</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17157,7 +17157,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129954803</v>
+        <v>129954534</v>
       </c>
       <c r="B152" t="n">
         <v>79095</v>
@@ -17192,10 +17192,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>470938</v>
+        <v>471086</v>
       </c>
       <c r="R152" t="n">
-        <v>6770693</v>
+        <v>6770684</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17264,7 +17264,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129954534</v>
+        <v>129959294</v>
       </c>
       <c r="B153" t="n">
         <v>79095</v>
@@ -17299,10 +17299,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>471086</v>
+        <v>470904</v>
       </c>
       <c r="R153" t="n">
-        <v>6770684</v>
+        <v>6770537</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17371,7 +17371,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129959294</v>
+        <v>129958545</v>
       </c>
       <c r="B154" t="n">
         <v>79095</v>
@@ -17406,10 +17406,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>470904</v>
+        <v>470877</v>
       </c>
       <c r="R154" t="n">
-        <v>6770537</v>
+        <v>6770687</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17478,7 +17478,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129958545</v>
+        <v>129954408</v>
       </c>
       <c r="B155" t="n">
         <v>79095</v>
@@ -17513,10 +17513,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470877</v>
+        <v>471019</v>
       </c>
       <c r="R155" t="n">
-        <v>6770687</v>
+        <v>6770666</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17585,7 +17585,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129954408</v>
+        <v>129954803</v>
       </c>
       <c r="B156" t="n">
         <v>79095</v>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>471019</v>
+        <v>470938</v>
       </c>
       <c r="R156" t="n">
-        <v>6770666</v>
+        <v>6770693</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -20178,7 +20178,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129962443</v>
+        <v>129961937</v>
       </c>
       <c r="B180" t="n">
         <v>79095</v>
@@ -20213,10 +20213,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>470989</v>
+        <v>471216</v>
       </c>
       <c r="R180" t="n">
-        <v>6770629</v>
+        <v>6770650</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20285,7 +20285,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129961937</v>
+        <v>129958214</v>
       </c>
       <c r="B181" t="n">
         <v>79095</v>
@@ -20320,10 +20320,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471216</v>
+        <v>470823</v>
       </c>
       <c r="R181" t="n">
-        <v>6770650</v>
+        <v>6770705</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20392,45 +20392,50 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129958214</v>
+        <v>129961109</v>
       </c>
       <c r="B182" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>470823</v>
+        <v>471175</v>
       </c>
       <c r="R182" t="n">
-        <v>6770705</v>
+        <v>6770631</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20499,50 +20504,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129961109</v>
+        <v>129962443</v>
       </c>
       <c r="B183" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>471175</v>
+        <v>470989</v>
       </c>
       <c r="R183" t="n">
-        <v>6770631</v>
+        <v>6770629</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21476,50 +21476,45 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129958199</v>
+        <v>129954590</v>
       </c>
       <c r="B192" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>470823</v>
+        <v>471013</v>
       </c>
       <c r="R192" t="n">
-        <v>6770705</v>
+        <v>6770715</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21588,38 +21583,38 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129959434</v>
+        <v>129958199</v>
       </c>
       <c r="B193" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -21628,10 +21623,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>470824</v>
+        <v>470823</v>
       </c>
       <c r="R193" t="n">
-        <v>6770523</v>
+        <v>6770705</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21700,45 +21695,50 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129954590</v>
+        <v>129960746</v>
       </c>
       <c r="B194" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>471013</v>
+        <v>471053</v>
       </c>
       <c r="R194" t="n">
-        <v>6770715</v>
+        <v>6770528</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21807,38 +21807,38 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129960746</v>
+        <v>129959434</v>
       </c>
       <c r="B195" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
       <c r="M195" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P195" t="inlineStr">
@@ -21847,10 +21847,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>471053</v>
+        <v>470824</v>
       </c>
       <c r="R195" t="n">
-        <v>6770528</v>
+        <v>6770523</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -25632,10 +25632,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129960437</v>
+        <v>129959730</v>
       </c>
       <c r="B230" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25643,34 +25643,39 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>470948</v>
+        <v>470868</v>
       </c>
       <c r="R230" t="n">
-        <v>6770533</v>
+        <v>6770431</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25739,10 +25744,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129959730</v>
+        <v>129960437</v>
       </c>
       <c r="B231" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25750,39 +25755,34 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>470868</v>
+        <v>470948</v>
       </c>
       <c r="R231" t="n">
-        <v>6770431</v>
+        <v>6770533</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -8056,35 +8056,40 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129944454</v>
+        <v>129944452</v>
       </c>
       <c r="B68" t="n">
-        <v>8451</v>
+        <v>57738</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
@@ -8163,32 +8168,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129944817</v>
+        <v>129944454</v>
       </c>
       <c r="B69" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8198,10 +8203,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471247</v>
+        <v>471330</v>
       </c>
       <c r="R69" t="n">
-        <v>6770726</v>
+        <v>6770712</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,7 +8275,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129944495</v>
+        <v>129944817</v>
       </c>
       <c r="B70" t="n">
         <v>79095</v>
@@ -8305,10 +8310,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471288</v>
+        <v>471247</v>
       </c>
       <c r="R70" t="n">
-        <v>6770728</v>
+        <v>6770726</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8377,7 +8382,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129946062</v>
+        <v>129944495</v>
       </c>
       <c r="B71" t="n">
         <v>79095</v>
@@ -8412,10 +8417,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471161</v>
+        <v>471288</v>
       </c>
       <c r="R71" t="n">
-        <v>6770705</v>
+        <v>6770728</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8484,7 +8489,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129946408</v>
+        <v>129946062</v>
       </c>
       <c r="B72" t="n">
         <v>79095</v>
@@ -8519,10 +8524,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470921</v>
+        <v>471161</v>
       </c>
       <c r="R72" t="n">
-        <v>6770579</v>
+        <v>6770705</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8591,7 +8596,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129944164</v>
+        <v>129946408</v>
       </c>
       <c r="B73" t="n">
         <v>79095</v>
@@ -8626,10 +8631,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471363</v>
+        <v>470921</v>
       </c>
       <c r="R73" t="n">
-        <v>6770736</v>
+        <v>6770579</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8698,10 +8703,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129944452</v>
+        <v>129944164</v>
       </c>
       <c r="B74" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8709,39 +8714,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471330</v>
+        <v>471363</v>
       </c>
       <c r="R74" t="n">
-        <v>6770712</v>
+        <v>6770736</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9997,7 +9997,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129945509</v>
+        <v>129944466</v>
       </c>
       <c r="B86" t="n">
         <v>79095</v>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471198</v>
+        <v>471322</v>
       </c>
       <c r="R86" t="n">
-        <v>6770689</v>
+        <v>6770702</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10078,11 +10078,6 @@
       <c r="AB86" t="inlineStr">
         <is>
           <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10109,7 +10104,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129946029</v>
+        <v>129945509</v>
       </c>
       <c r="B87" t="n">
         <v>79095</v>
@@ -10144,10 +10139,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471185</v>
+        <v>471198</v>
       </c>
       <c r="R87" t="n">
-        <v>6770690</v>
+        <v>6770689</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10190,6 +10185,11 @@
       <c r="AB87" t="inlineStr">
         <is>
           <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10216,7 +10216,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129944466</v>
+        <v>129946029</v>
       </c>
       <c r="B88" t="n">
         <v>79095</v>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471322</v>
+        <v>471185</v>
       </c>
       <c r="R88" t="n">
-        <v>6770702</v>
+        <v>6770690</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129944878</v>
+        <v>129946391</v>
       </c>
       <c r="B93" t="n">
-        <v>57900</v>
+        <v>57738</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10767,31 +10767,27 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P93" t="inlineStr">
@@ -10800,13 +10796,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471258</v>
+        <v>470921</v>
       </c>
       <c r="R93" t="n">
-        <v>6770712</v>
+        <v>6770579</v>
       </c>
       <c r="S93" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10872,50 +10868,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129946444</v>
+        <v>129943855</v>
       </c>
       <c r="B94" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>470971</v>
+        <v>471451</v>
       </c>
       <c r="R94" t="n">
-        <v>6770603</v>
+        <v>6770706</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10984,7 +10975,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129943855</v>
+        <v>129945066</v>
       </c>
       <c r="B95" t="n">
         <v>79095</v>
@@ -11019,10 +11010,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471451</v>
+        <v>471239</v>
       </c>
       <c r="R95" t="n">
-        <v>6770706</v>
+        <v>6770732</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11091,7 +11082,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129945066</v>
+        <v>129944756</v>
       </c>
       <c r="B96" t="n">
         <v>79095</v>
@@ -11126,10 +11117,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471239</v>
+        <v>471288</v>
       </c>
       <c r="R96" t="n">
-        <v>6770732</v>
+        <v>6770685</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11198,10 +11189,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129944756</v>
+        <v>129944878</v>
       </c>
       <c r="B97" t="n">
-        <v>79095</v>
+        <v>57900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11209,37 +11200,46 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471288</v>
+        <v>471258</v>
       </c>
       <c r="R97" t="n">
-        <v>6770685</v>
+        <v>6770712</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11305,38 +11305,38 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129946391</v>
+        <v>129946444</v>
       </c>
       <c r="B98" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>470921</v>
+        <v>470971</v>
       </c>
       <c r="R98" t="n">
-        <v>6770579</v>
+        <v>6770603</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11743,45 +11743,50 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129945457</v>
+        <v>129944062</v>
       </c>
       <c r="B102" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471189</v>
+        <v>471432</v>
       </c>
       <c r="R102" t="n">
-        <v>6770706</v>
+        <v>6770716</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11850,7 +11855,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129943809</v>
+        <v>129945457</v>
       </c>
       <c r="B103" t="n">
         <v>79095</v>
@@ -11885,10 +11890,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471447</v>
+        <v>471189</v>
       </c>
       <c r="R103" t="n">
-        <v>6770716</v>
+        <v>6770706</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11957,47 +11962,42 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129944062</v>
+        <v>129943809</v>
       </c>
       <c r="B104" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471432</v>
+        <v>471447</v>
       </c>
       <c r="R104" t="n">
         <v>6770716</v>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129943849</v>
+        <v>129944178</v>
       </c>
       <c r="B106" t="n">
-        <v>91660</v>
+        <v>79095</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12187,38 +12187,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471451</v>
+        <v>471372</v>
       </c>
       <c r="R106" t="n">
-        <v>6770706</v>
+        <v>6770719</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12287,7 +12283,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129944488</v>
+        <v>129943541</v>
       </c>
       <c r="B107" t="n">
         <v>79095</v>
@@ -12322,10 +12318,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471318</v>
+        <v>471478</v>
       </c>
       <c r="R107" t="n">
-        <v>6770729</v>
+        <v>6770707</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12394,7 +12390,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129944178</v>
+        <v>129944592</v>
       </c>
       <c r="B108" t="n">
         <v>79095</v>
@@ -12429,10 +12425,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471372</v>
+        <v>471313</v>
       </c>
       <c r="R108" t="n">
-        <v>6770719</v>
+        <v>6770688</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12501,10 +12497,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129943541</v>
+        <v>129943849</v>
       </c>
       <c r="B109" t="n">
-        <v>79095</v>
+        <v>91662</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12512,34 +12508,38 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471478</v>
+        <v>471451</v>
       </c>
       <c r="R109" t="n">
-        <v>6770707</v>
+        <v>6770706</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12608,7 +12608,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129944592</v>
+        <v>129944488</v>
       </c>
       <c r="B110" t="n">
         <v>79095</v>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471313</v>
+        <v>471318</v>
       </c>
       <c r="R110" t="n">
-        <v>6770688</v>
+        <v>6770729</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12822,50 +12822,45 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129946334</v>
+        <v>129944804</v>
       </c>
       <c r="B112" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P112" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>470871</v>
+        <v>471271</v>
       </c>
       <c r="R112" t="n">
-        <v>6770635</v>
+        <v>6770733</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12934,45 +12929,50 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129944804</v>
+        <v>129946334</v>
       </c>
       <c r="B113" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>471271</v>
+        <v>470871</v>
       </c>
       <c r="R113" t="n">
-        <v>6770733</v>
+        <v>6770635</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -14024,50 +14024,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129962376</v>
+        <v>129960901</v>
       </c>
       <c r="B123" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>470996</v>
+        <v>471185</v>
       </c>
       <c r="R123" t="n">
-        <v>6770611</v>
+        <v>6770590</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14136,7 +14131,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129958842</v>
+        <v>129960002</v>
       </c>
       <c r="B124" t="n">
         <v>79095</v>
@@ -14171,10 +14166,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>470820</v>
+        <v>470932</v>
       </c>
       <c r="R124" t="n">
-        <v>6770624</v>
+        <v>6770480</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14243,7 +14238,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129954413</v>
+        <v>129957713</v>
       </c>
       <c r="B125" t="n">
         <v>79095</v>
@@ -14278,10 +14273,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>471028</v>
+        <v>470904</v>
       </c>
       <c r="R125" t="n">
-        <v>6770675</v>
+        <v>6770718</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14350,10 +14345,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129962374</v>
+        <v>129959479</v>
       </c>
       <c r="B126" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14361,39 +14356,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="M126" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P126" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470996</v>
+        <v>470837</v>
       </c>
       <c r="R126" t="n">
-        <v>6770611</v>
+        <v>6770498</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14462,7 +14452,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129960901</v>
+        <v>129959813</v>
       </c>
       <c r="B127" t="n">
         <v>79095</v>
@@ -14497,10 +14487,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>471185</v>
+        <v>470942</v>
       </c>
       <c r="R127" t="n">
-        <v>6770590</v>
+        <v>6770455</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14569,7 +14559,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129960002</v>
+        <v>129959122</v>
       </c>
       <c r="B128" t="n">
         <v>79095</v>
@@ -14604,10 +14594,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470932</v>
+        <v>470926</v>
       </c>
       <c r="R128" t="n">
-        <v>6770480</v>
+        <v>6770613</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14676,7 +14666,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129957713</v>
+        <v>129958842</v>
       </c>
       <c r="B129" t="n">
         <v>79095</v>
@@ -14711,10 +14701,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470904</v>
+        <v>470820</v>
       </c>
       <c r="R129" t="n">
-        <v>6770718</v>
+        <v>6770624</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14783,7 +14773,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129958464</v>
+        <v>129954413</v>
       </c>
       <c r="B130" t="n">
         <v>79095</v>
@@ -14818,10 +14808,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470822</v>
+        <v>471028</v>
       </c>
       <c r="R130" t="n">
-        <v>6770673</v>
+        <v>6770675</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14890,7 +14880,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129959479</v>
+        <v>129958464</v>
       </c>
       <c r="B131" t="n">
         <v>79095</v>
@@ -14925,10 +14915,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470837</v>
+        <v>470822</v>
       </c>
       <c r="R131" t="n">
-        <v>6770498</v>
+        <v>6770673</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15104,10 +15094,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129959813</v>
+        <v>129962374</v>
       </c>
       <c r="B133" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15115,34 +15105,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>470942</v>
+        <v>470996</v>
       </c>
       <c r="R133" t="n">
-        <v>6770455</v>
+        <v>6770611</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15211,45 +15206,50 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129959122</v>
+        <v>129962376</v>
       </c>
       <c r="B134" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>470926</v>
+        <v>470996</v>
       </c>
       <c r="R134" t="n">
-        <v>6770613</v>
+        <v>6770611</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15425,7 +15425,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129958895</v>
+        <v>129954531</v>
       </c>
       <c r="B136" t="n">
         <v>79095</v>
@@ -15460,10 +15460,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470887</v>
+        <v>471106</v>
       </c>
       <c r="R136" t="n">
-        <v>6770658</v>
+        <v>6770683</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15532,7 +15532,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129958499</v>
+        <v>129958895</v>
       </c>
       <c r="B137" t="n">
         <v>79095</v>
@@ -15567,10 +15567,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470850</v>
+        <v>470887</v>
       </c>
       <c r="R137" t="n">
-        <v>6770690</v>
+        <v>6770658</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15639,50 +15639,45 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129959110</v>
+        <v>129958499</v>
       </c>
       <c r="B138" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="M138" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470926</v>
+        <v>470850</v>
       </c>
       <c r="R138" t="n">
-        <v>6770613</v>
+        <v>6770690</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15965,7 +15960,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129954531</v>
+        <v>129961622</v>
       </c>
       <c r="B141" t="n">
         <v>79095</v>
@@ -16000,10 +15995,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>471106</v>
+        <v>471262</v>
       </c>
       <c r="R141" t="n">
-        <v>6770683</v>
+        <v>6770622</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16072,7 +16067,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129961622</v>
+        <v>129958010</v>
       </c>
       <c r="B142" t="n">
         <v>79095</v>
@@ -16107,10 +16102,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>471262</v>
+        <v>470894</v>
       </c>
       <c r="R142" t="n">
-        <v>6770622</v>
+        <v>6770713</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16179,45 +16174,50 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129958010</v>
+        <v>129959110</v>
       </c>
       <c r="B143" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>470894</v>
+        <v>470926</v>
       </c>
       <c r="R143" t="n">
-        <v>6770713</v>
+        <v>6770613</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16607,50 +16607,45 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129960827</v>
+        <v>129958802</v>
       </c>
       <c r="B147" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P147" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>471078</v>
+        <v>470858</v>
       </c>
       <c r="R147" t="n">
-        <v>6770561</v>
+        <v>6770602</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16719,7 +16714,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129958802</v>
+        <v>129962073</v>
       </c>
       <c r="B148" t="n">
         <v>79095</v>
@@ -16754,10 +16749,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470858</v>
+        <v>471222</v>
       </c>
       <c r="R148" t="n">
-        <v>6770602</v>
+        <v>6770635</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17050,45 +17045,50 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129962073</v>
+        <v>129960827</v>
       </c>
       <c r="B151" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>471222</v>
+        <v>471078</v>
       </c>
       <c r="R151" t="n">
-        <v>6770635</v>
+        <v>6770561</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17264,7 +17264,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129959294</v>
+        <v>129958545</v>
       </c>
       <c r="B153" t="n">
         <v>79095</v>
@@ -17299,10 +17299,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>470904</v>
+        <v>470877</v>
       </c>
       <c r="R153" t="n">
-        <v>6770537</v>
+        <v>6770687</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17371,7 +17371,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129958545</v>
+        <v>129954408</v>
       </c>
       <c r="B154" t="n">
         <v>79095</v>
@@ -17406,10 +17406,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>470877</v>
+        <v>471019</v>
       </c>
       <c r="R154" t="n">
-        <v>6770687</v>
+        <v>6770666</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17478,7 +17478,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129954408</v>
+        <v>129954803</v>
       </c>
       <c r="B155" t="n">
         <v>79095</v>
@@ -17513,10 +17513,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>471019</v>
+        <v>470938</v>
       </c>
       <c r="R155" t="n">
-        <v>6770666</v>
+        <v>6770693</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17585,7 +17585,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129954803</v>
+        <v>129959294</v>
       </c>
       <c r="B156" t="n">
         <v>79095</v>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>470938</v>
+        <v>470904</v>
       </c>
       <c r="R156" t="n">
-        <v>6770693</v>
+        <v>6770537</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17692,7 +17692,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129958754</v>
+        <v>129954442</v>
       </c>
       <c r="B157" t="n">
         <v>79095</v>
@@ -17727,10 +17727,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>470817</v>
+        <v>471053</v>
       </c>
       <c r="R157" t="n">
-        <v>6770608</v>
+        <v>6770682</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17799,7 +17799,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129959389</v>
+        <v>129960763</v>
       </c>
       <c r="B158" t="n">
         <v>79095</v>
@@ -17834,10 +17834,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470824</v>
+        <v>471062</v>
       </c>
       <c r="R158" t="n">
-        <v>6770523</v>
+        <v>6770538</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18018,7 +18018,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129954442</v>
+        <v>129958754</v>
       </c>
       <c r="B160" t="n">
         <v>79095</v>
@@ -18053,10 +18053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>471053</v>
+        <v>470817</v>
       </c>
       <c r="R160" t="n">
-        <v>6770682</v>
+        <v>6770608</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18125,7 +18125,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129960763</v>
+        <v>129959389</v>
       </c>
       <c r="B161" t="n">
         <v>79095</v>
@@ -18160,10 +18160,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>471062</v>
+        <v>470824</v>
       </c>
       <c r="R161" t="n">
-        <v>6770538</v>
+        <v>6770523</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18553,7 +18553,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129959994</v>
+        <v>129955313</v>
       </c>
       <c r="B165" t="n">
         <v>79095</v>
@@ -18588,10 +18588,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>470954</v>
+        <v>470992</v>
       </c>
       <c r="R165" t="n">
-        <v>6770475</v>
+        <v>6770702</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18660,7 +18660,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129962390</v>
+        <v>129959994</v>
       </c>
       <c r="B166" t="n">
         <v>79095</v>
@@ -18695,10 +18695,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>471004</v>
+        <v>470954</v>
       </c>
       <c r="R166" t="n">
-        <v>6770581</v>
+        <v>6770475</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18767,10 +18767,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129954441</v>
+        <v>129958841</v>
       </c>
       <c r="B167" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18778,39 +18778,34 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
-      <c r="M167" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P167" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>471052</v>
+        <v>470828</v>
       </c>
       <c r="R167" t="n">
-        <v>6770696</v>
+        <v>6770636</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18879,7 +18874,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129960929</v>
+        <v>129962390</v>
       </c>
       <c r="B168" t="n">
         <v>79095</v>
@@ -18914,10 +18909,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>471159</v>
+        <v>471004</v>
       </c>
       <c r="R168" t="n">
-        <v>6770613</v>
+        <v>6770581</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18986,7 +18981,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129955313</v>
+        <v>129958466</v>
       </c>
       <c r="B169" t="n">
         <v>79095</v>
@@ -19021,10 +19016,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>470992</v>
+        <v>470812</v>
       </c>
       <c r="R169" t="n">
-        <v>6770702</v>
+        <v>6770670</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19093,10 +19088,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129958841</v>
+        <v>129954441</v>
       </c>
       <c r="B170" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19104,34 +19099,39 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>470828</v>
+        <v>471052</v>
       </c>
       <c r="R170" t="n">
-        <v>6770636</v>
+        <v>6770696</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19200,7 +19200,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129958466</v>
+        <v>129960929</v>
       </c>
       <c r="B171" t="n">
         <v>79095</v>
@@ -19235,10 +19235,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>470812</v>
+        <v>471159</v>
       </c>
       <c r="R171" t="n">
-        <v>6770670</v>
+        <v>6770613</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19307,50 +19307,45 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129959285</v>
+        <v>129962243</v>
       </c>
       <c r="B172" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>470922</v>
+        <v>471074</v>
       </c>
       <c r="R172" t="n">
-        <v>6770556</v>
+        <v>6770617</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19419,50 +19414,45 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129962436</v>
+        <v>129959717</v>
       </c>
       <c r="B173" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
-      <c r="M173" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P173" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>470989</v>
+        <v>470864</v>
       </c>
       <c r="R173" t="n">
-        <v>6770629</v>
+        <v>6770438</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19531,50 +19521,45 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129959579</v>
+        <v>129962351</v>
       </c>
       <c r="B174" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
-      <c r="M174" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P174" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>470822</v>
+        <v>471017</v>
       </c>
       <c r="R174" t="n">
-        <v>6770452</v>
+        <v>6770613</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19643,45 +19628,50 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129959740</v>
+        <v>129959579</v>
       </c>
       <c r="B175" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>470905</v>
+        <v>470822</v>
       </c>
       <c r="R175" t="n">
-        <v>6770435</v>
+        <v>6770452</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19750,45 +19740,50 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129962243</v>
+        <v>129962436</v>
       </c>
       <c r="B176" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471074</v>
+        <v>470989</v>
       </c>
       <c r="R176" t="n">
-        <v>6770617</v>
+        <v>6770629</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19857,45 +19852,50 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129959717</v>
+        <v>129959285</v>
       </c>
       <c r="B177" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>470864</v>
+        <v>470922</v>
       </c>
       <c r="R177" t="n">
-        <v>6770438</v>
+        <v>6770556</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19964,7 +19964,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129962351</v>
+        <v>129959740</v>
       </c>
       <c r="B178" t="n">
         <v>79095</v>
@@ -19999,10 +19999,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>471017</v>
+        <v>470905</v>
       </c>
       <c r="R178" t="n">
-        <v>6770613</v>
+        <v>6770435</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20178,7 +20178,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129961937</v>
+        <v>129962443</v>
       </c>
       <c r="B180" t="n">
         <v>79095</v>
@@ -20213,10 +20213,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>471216</v>
+        <v>470989</v>
       </c>
       <c r="R180" t="n">
-        <v>6770650</v>
+        <v>6770629</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20392,50 +20392,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129961109</v>
+        <v>129961937</v>
       </c>
       <c r="B182" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471175</v>
+        <v>471216</v>
       </c>
       <c r="R182" t="n">
-        <v>6770631</v>
+        <v>6770650</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20504,45 +20499,50 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129962443</v>
+        <v>129961109</v>
       </c>
       <c r="B183" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>470989</v>
+        <v>471175</v>
       </c>
       <c r="R183" t="n">
-        <v>6770629</v>
+        <v>6770631</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20611,7 +20611,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129962447</v>
+        <v>129960864</v>
       </c>
       <c r="B184" t="n">
         <v>79095</v>
@@ -20646,10 +20646,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>470993</v>
+        <v>471116</v>
       </c>
       <c r="R184" t="n">
-        <v>6770643</v>
+        <v>6770565</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20718,7 +20718,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129960864</v>
+        <v>129959256</v>
       </c>
       <c r="B185" t="n">
         <v>79095</v>
@@ -20753,10 +20753,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>471116</v>
+        <v>470922</v>
       </c>
       <c r="R185" t="n">
-        <v>6770565</v>
+        <v>6770556</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20825,10 +20825,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129959667</v>
+        <v>129956859</v>
       </c>
       <c r="B186" t="n">
-        <v>91660</v>
+        <v>79095</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20836,38 +20836,34 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I186" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>470864</v>
+        <v>470936</v>
       </c>
       <c r="R186" t="n">
-        <v>6770438</v>
+        <v>6770721</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20936,10 +20932,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129959870</v>
+        <v>129958694</v>
       </c>
       <c r="B187" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20947,39 +20943,34 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
-      <c r="M187" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P187" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>470952</v>
+        <v>470844</v>
       </c>
       <c r="R187" t="n">
-        <v>6770464</v>
+        <v>6770699</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21048,10 +21039,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129959256</v>
+        <v>129959667</v>
       </c>
       <c r="B188" t="n">
-        <v>79095</v>
+        <v>91662</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21059,34 +21050,38 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>470922</v>
+        <v>470864</v>
       </c>
       <c r="R188" t="n">
-        <v>6770556</v>
+        <v>6770438</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21155,7 +21150,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129956859</v>
+        <v>129958228</v>
       </c>
       <c r="B189" t="n">
         <v>79095</v>
@@ -21190,10 +21185,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>470936</v>
+        <v>470813</v>
       </c>
       <c r="R189" t="n">
-        <v>6770721</v>
+        <v>6770681</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21262,10 +21257,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129958694</v>
+        <v>129959870</v>
       </c>
       <c r="B190" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21273,34 +21268,39 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>470844</v>
+        <v>470952</v>
       </c>
       <c r="R190" t="n">
-        <v>6770699</v>
+        <v>6770464</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21369,7 +21369,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129958228</v>
+        <v>129962447</v>
       </c>
       <c r="B191" t="n">
         <v>79095</v>
@@ -21404,10 +21404,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>470813</v>
+        <v>470993</v>
       </c>
       <c r="R191" t="n">
-        <v>6770681</v>
+        <v>6770643</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21476,45 +21476,50 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129954590</v>
+        <v>129958199</v>
       </c>
       <c r="B192" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>471013</v>
+        <v>470823</v>
       </c>
       <c r="R192" t="n">
-        <v>6770715</v>
+        <v>6770705</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21583,7 +21588,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129958199</v>
+        <v>129960746</v>
       </c>
       <c r="B193" t="n">
         <v>8451</v>
@@ -21623,10 +21628,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>470823</v>
+        <v>471053</v>
       </c>
       <c r="R193" t="n">
-        <v>6770705</v>
+        <v>6770528</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21695,50 +21700,45 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129960746</v>
+        <v>129954590</v>
       </c>
       <c r="B194" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
-      <c r="M194" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>471053</v>
+        <v>471013</v>
       </c>
       <c r="R194" t="n">
-        <v>6770528</v>
+        <v>6770715</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -22255,7 +22255,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129960891</v>
+        <v>129956851</v>
       </c>
       <c r="B199" t="n">
         <v>79095</v>
@@ -22290,10 +22290,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471147</v>
+        <v>470928</v>
       </c>
       <c r="R199" t="n">
-        <v>6770575</v>
+        <v>6770695</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22362,7 +22362,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129956851</v>
+        <v>129959375</v>
       </c>
       <c r="B200" t="n">
         <v>79095</v>
@@ -22397,10 +22397,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>470928</v>
+        <v>470851</v>
       </c>
       <c r="R200" t="n">
-        <v>6770695</v>
+        <v>6770520</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22469,7 +22469,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129959375</v>
+        <v>129960891</v>
       </c>
       <c r="B201" t="n">
         <v>79095</v>
@@ -22504,10 +22504,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>470851</v>
+        <v>471147</v>
       </c>
       <c r="R201" t="n">
-        <v>6770520</v>
+        <v>6770575</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22790,10 +22790,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129958691</v>
+        <v>129962224</v>
       </c>
       <c r="B204" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22801,39 +22801,34 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="M204" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>470844</v>
+        <v>471098</v>
       </c>
       <c r="R204" t="n">
-        <v>6770699</v>
+        <v>6770634</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22902,10 +22897,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129962379</v>
+        <v>129958691</v>
       </c>
       <c r="B205" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22913,34 +22908,39 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>470996</v>
+        <v>470844</v>
       </c>
       <c r="R205" t="n">
-        <v>6770611</v>
+        <v>6770699</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23009,45 +23009,50 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129962224</v>
+        <v>129959223</v>
       </c>
       <c r="B206" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>471098</v>
+        <v>470921</v>
       </c>
       <c r="R206" t="n">
-        <v>6770634</v>
+        <v>6770579</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23228,50 +23233,45 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129959223</v>
+        <v>129962379</v>
       </c>
       <c r="B208" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470921</v>
+        <v>470996</v>
       </c>
       <c r="R208" t="n">
-        <v>6770579</v>
+        <v>6770611</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23768,7 +23768,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129954584</v>
+        <v>129962119</v>
       </c>
       <c r="B213" t="n">
         <v>79095</v>
@@ -23803,10 +23803,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>471062</v>
+        <v>471156</v>
       </c>
       <c r="R213" t="n">
-        <v>6770731</v>
+        <v>6770665</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23875,7 +23875,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129960790</v>
+        <v>129958133</v>
       </c>
       <c r="B214" t="n">
         <v>79095</v>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471073</v>
+        <v>470869</v>
       </c>
       <c r="R214" t="n">
-        <v>6770551</v>
+        <v>6770702</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23982,7 +23982,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129962119</v>
+        <v>129954584</v>
       </c>
       <c r="B215" t="n">
         <v>79095</v>
@@ -24017,10 +24017,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471156</v>
+        <v>471062</v>
       </c>
       <c r="R215" t="n">
-        <v>6770665</v>
+        <v>6770731</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24089,7 +24089,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129958133</v>
+        <v>129960790</v>
       </c>
       <c r="B216" t="n">
         <v>79095</v>
@@ -24124,10 +24124,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>470869</v>
+        <v>471073</v>
       </c>
       <c r="R216" t="n">
-        <v>6770702</v>
+        <v>6770551</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24751,50 +24751,45 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129959441</v>
+        <v>129959250</v>
       </c>
       <c r="B222" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
-      <c r="M222" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470824</v>
+        <v>470943</v>
       </c>
       <c r="R222" t="n">
-        <v>6770523</v>
+        <v>6770559</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24863,50 +24858,45 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129958131</v>
+        <v>129961818</v>
       </c>
       <c r="B223" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>470869</v>
+        <v>471228</v>
       </c>
       <c r="R223" t="n">
-        <v>6770702</v>
+        <v>6770667</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24975,50 +24965,45 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129960657</v>
+        <v>129957969</v>
       </c>
       <c r="B224" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>471025</v>
+        <v>470911</v>
       </c>
       <c r="R224" t="n">
-        <v>6770488</v>
+        <v>6770707</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25087,10 +25072,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129961818</v>
+        <v>129957253</v>
       </c>
       <c r="B225" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -25098,34 +25083,39 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P225" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>471228</v>
+        <v>470916</v>
       </c>
       <c r="R225" t="n">
-        <v>6770667</v>
+        <v>6770721</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25306,38 +25296,38 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129957253</v>
+        <v>129958131</v>
       </c>
       <c r="B227" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
       <c r="M227" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P227" t="inlineStr">
@@ -25346,10 +25336,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>470916</v>
+        <v>470869</v>
       </c>
       <c r="R227" t="n">
-        <v>6770721</v>
+        <v>6770702</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25418,45 +25408,50 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129959250</v>
+        <v>129959441</v>
       </c>
       <c r="B228" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470943</v>
+        <v>470824</v>
       </c>
       <c r="R228" t="n">
-        <v>6770559</v>
+        <v>6770523</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25525,45 +25520,50 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129957969</v>
+        <v>129960657</v>
       </c>
       <c r="B229" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>470911</v>
+        <v>471025</v>
       </c>
       <c r="R229" t="n">
-        <v>6770707</v>
+        <v>6770488</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -8059,7 +8059,7 @@
         <v>129944452</v>
       </c>
       <c r="B68" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8168,32 +8168,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129944454</v>
+        <v>129944817</v>
       </c>
       <c r="B69" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8203,10 +8203,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471330</v>
+        <v>471247</v>
       </c>
       <c r="R69" t="n">
-        <v>6770712</v>
+        <v>6770726</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8275,10 +8275,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129944817</v>
+        <v>129944495</v>
       </c>
       <c r="B70" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8310,10 +8310,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471247</v>
+        <v>471288</v>
       </c>
       <c r="R70" t="n">
-        <v>6770726</v>
+        <v>6770728</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8382,32 +8382,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129944495</v>
+        <v>129944454</v>
       </c>
       <c r="B71" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8417,10 +8417,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471288</v>
+        <v>471330</v>
       </c>
       <c r="R71" t="n">
-        <v>6770728</v>
+        <v>6770712</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8492,7 +8492,7 @@
         <v>129946062</v>
       </c>
       <c r="B72" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>129946408</v>
       </c>
       <c r="B73" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>129944164</v>
       </c>
       <c r="B74" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8813,7 +8813,7 @@
         <v>129946170</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>129946586</v>
       </c>
       <c r="B76" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         <v>129944813</v>
       </c>
       <c r="B77" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9131,10 +9131,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129944762</v>
+        <v>129946436</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9142,34 +9142,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>471276</v>
+        <v>470971</v>
       </c>
       <c r="R78" t="n">
-        <v>6770703</v>
+        <v>6770603</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9238,10 +9243,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129946436</v>
+        <v>129944762</v>
       </c>
       <c r="B79" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9249,39 +9254,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>470971</v>
+        <v>471276</v>
       </c>
       <c r="R79" t="n">
-        <v>6770603</v>
+        <v>6770703</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9353,7 +9353,7 @@
         <v>129945104</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>129946182</v>
       </c>
       <c r="B81" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9564,10 +9564,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129944037</v>
+        <v>129946321</v>
       </c>
       <c r="B82" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9575,34 +9575,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471417</v>
+        <v>470871</v>
       </c>
       <c r="R82" t="n">
-        <v>6770738</v>
+        <v>6770635</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9671,10 +9676,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944210</v>
+        <v>129944037</v>
       </c>
       <c r="B83" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9706,10 +9711,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471390</v>
+        <v>471417</v>
       </c>
       <c r="R83" t="n">
-        <v>6770705</v>
+        <v>6770738</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9778,50 +9783,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129946321</v>
+        <v>129946047</v>
       </c>
       <c r="B84" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>470871</v>
+        <v>471161</v>
       </c>
       <c r="R84" t="n">
-        <v>6770635</v>
+        <v>6770705</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9890,32 +9890,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129946047</v>
+        <v>129944210</v>
       </c>
       <c r="B85" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471161</v>
+        <v>471390</v>
       </c>
       <c r="R85" t="n">
         <v>6770705</v>
@@ -9997,10 +9997,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129944466</v>
+        <v>129945509</v>
       </c>
       <c r="B86" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471322</v>
+        <v>471198</v>
       </c>
       <c r="R86" t="n">
-        <v>6770702</v>
+        <v>6770689</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10078,6 +10078,11 @@
       <c r="AB86" t="inlineStr">
         <is>
           <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10104,10 +10109,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129945509</v>
+        <v>129946029</v>
       </c>
       <c r="B87" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10139,10 +10144,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471198</v>
+        <v>471185</v>
       </c>
       <c r="R87" t="n">
-        <v>6770689</v>
+        <v>6770690</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10185,11 +10190,6 @@
       <c r="AB87" t="inlineStr">
         <is>
           <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10216,10 +10216,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129946029</v>
+        <v>129944466</v>
       </c>
       <c r="B88" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471185</v>
+        <v>471322</v>
       </c>
       <c r="R88" t="n">
-        <v>6770690</v>
+        <v>6770702</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10326,7 +10326,7 @@
         <v>129944473</v>
       </c>
       <c r="B89" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10430,45 +10430,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129944975</v>
+        <v>129945161</v>
       </c>
       <c r="B90" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471242</v>
+        <v>471198</v>
       </c>
       <c r="R90" t="n">
-        <v>6770682</v>
+        <v>6770725</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10537,10 +10542,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129946708</v>
+        <v>129944975</v>
       </c>
       <c r="B91" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10572,10 +10577,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471171</v>
+        <v>471242</v>
       </c>
       <c r="R91" t="n">
-        <v>6770660</v>
+        <v>6770682</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10644,50 +10649,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129945161</v>
+        <v>129946708</v>
       </c>
       <c r="B92" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471198</v>
+        <v>471171</v>
       </c>
       <c r="R92" t="n">
-        <v>6770725</v>
+        <v>6770660</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10759,7 +10759,7 @@
         <v>129946391</v>
       </c>
       <c r="B93" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>129943855</v>
       </c>
       <c r="B94" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10975,45 +10975,50 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129945066</v>
+        <v>129946444</v>
       </c>
       <c r="B95" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471239</v>
+        <v>470971</v>
       </c>
       <c r="R95" t="n">
-        <v>6770732</v>
+        <v>6770603</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11082,10 +11087,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129944756</v>
+        <v>129944878</v>
       </c>
       <c r="B96" t="n">
-        <v>79095</v>
+        <v>57985</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11093,37 +11098,46 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471288</v>
+        <v>471258</v>
       </c>
       <c r="R96" t="n">
-        <v>6770685</v>
+        <v>6770712</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11189,10 +11203,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129944878</v>
+        <v>129945066</v>
       </c>
       <c r="B97" t="n">
-        <v>57900</v>
+        <v>79180</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11200,46 +11214,37 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471258</v>
+        <v>471239</v>
       </c>
       <c r="R97" t="n">
-        <v>6770712</v>
+        <v>6770732</v>
       </c>
       <c r="S97" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11305,50 +11310,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129946444</v>
+        <v>129944756</v>
       </c>
       <c r="B98" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>470971</v>
+        <v>471288</v>
       </c>
       <c r="R98" t="n">
-        <v>6770603</v>
+        <v>6770685</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11417,10 +11417,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129945156</v>
+        <v>129944926</v>
       </c>
       <c r="B99" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11428,39 +11428,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471198</v>
+        <v>471263</v>
       </c>
       <c r="R99" t="n">
-        <v>6770725</v>
+        <v>6770694</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11529,10 +11524,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944926</v>
+        <v>129944544</v>
       </c>
       <c r="B100" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11564,10 +11559,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471263</v>
+        <v>471330</v>
       </c>
       <c r="R100" t="n">
-        <v>6770694</v>
+        <v>6770712</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11636,10 +11631,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129944544</v>
+        <v>129945156</v>
       </c>
       <c r="B101" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11647,34 +11642,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471330</v>
+        <v>471198</v>
       </c>
       <c r="R101" t="n">
-        <v>6770712</v>
+        <v>6770725</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11743,50 +11743,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129944062</v>
+        <v>129945457</v>
       </c>
       <c r="B102" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471432</v>
+        <v>471189</v>
       </c>
       <c r="R102" t="n">
-        <v>6770716</v>
+        <v>6770706</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11855,10 +11850,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129945457</v>
+        <v>129943809</v>
       </c>
       <c r="B103" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11890,10 +11885,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471189</v>
+        <v>471447</v>
       </c>
       <c r="R103" t="n">
-        <v>6770706</v>
+        <v>6770716</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11962,42 +11957,47 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129943809</v>
+        <v>129944062</v>
       </c>
       <c r="B104" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471447</v>
+        <v>471432</v>
       </c>
       <c r="R104" t="n">
         <v>6770716</v>
@@ -12072,7 +12072,7 @@
         <v>129943914</v>
       </c>
       <c r="B105" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129944178</v>
+        <v>129943849</v>
       </c>
       <c r="B106" t="n">
-        <v>79095</v>
+        <v>91749</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12187,34 +12187,38 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471372</v>
+        <v>471451</v>
       </c>
       <c r="R106" t="n">
-        <v>6770719</v>
+        <v>6770706</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12283,10 +12287,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129943541</v>
+        <v>129944488</v>
       </c>
       <c r="B107" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12318,10 +12322,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471478</v>
+        <v>471318</v>
       </c>
       <c r="R107" t="n">
-        <v>6770707</v>
+        <v>6770729</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12390,10 +12394,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129944592</v>
+        <v>129944178</v>
       </c>
       <c r="B108" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12425,10 +12429,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471313</v>
+        <v>471372</v>
       </c>
       <c r="R108" t="n">
-        <v>6770688</v>
+        <v>6770719</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12497,10 +12501,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129943849</v>
+        <v>129943541</v>
       </c>
       <c r="B109" t="n">
-        <v>91662</v>
+        <v>79180</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12508,38 +12512,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471451</v>
+        <v>471478</v>
       </c>
       <c r="R109" t="n">
-        <v>6770706</v>
+        <v>6770707</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12608,10 +12608,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129944488</v>
+        <v>129944592</v>
       </c>
       <c r="B110" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12643,10 +12643,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471318</v>
+        <v>471313</v>
       </c>
       <c r="R110" t="n">
-        <v>6770729</v>
+        <v>6770688</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12718,7 +12718,7 @@
         <v>129943763</v>
       </c>
       <c r="B111" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>129944804</v>
       </c>
       <c r="B112" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>129946117</v>
       </c>
       <c r="B114" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>129943529</v>
       </c>
       <c r="B115" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>129946197</v>
       </c>
       <c r="B116" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>129945078</v>
       </c>
       <c r="B117" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>129946365</v>
       </c>
       <c r="B118" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13581,45 +13581,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129944523</v>
+        <v>129945444</v>
       </c>
       <c r="B119" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471303</v>
+        <v>471189</v>
       </c>
       <c r="R119" t="n">
-        <v>6770699</v>
+        <v>6770706</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13688,7 +13693,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129945444</v>
+        <v>129944158</v>
       </c>
       <c r="B120" t="n">
         <v>8451</v>
@@ -13728,10 +13733,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471189</v>
+        <v>471363</v>
       </c>
       <c r="R120" t="n">
-        <v>6770706</v>
+        <v>6770736</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13800,50 +13805,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129944158</v>
+        <v>129944523</v>
       </c>
       <c r="B121" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471363</v>
+        <v>471303</v>
       </c>
       <c r="R121" t="n">
-        <v>6770736</v>
+        <v>6770699</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13915,7 +13915,7 @@
         <v>129945440</v>
       </c>
       <c r="B122" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14024,45 +14024,50 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129960901</v>
+        <v>129962376</v>
       </c>
       <c r="B123" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>471185</v>
+        <v>470996</v>
       </c>
       <c r="R123" t="n">
-        <v>6770590</v>
+        <v>6770611</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14131,10 +14136,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129960002</v>
+        <v>129958842</v>
       </c>
       <c r="B124" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14166,10 +14171,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>470932</v>
+        <v>470820</v>
       </c>
       <c r="R124" t="n">
-        <v>6770480</v>
+        <v>6770624</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14238,10 +14243,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129957713</v>
+        <v>129960901</v>
       </c>
       <c r="B125" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14273,10 +14278,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470904</v>
+        <v>471185</v>
       </c>
       <c r="R125" t="n">
-        <v>6770718</v>
+        <v>6770590</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14345,10 +14350,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129959479</v>
+        <v>129960002</v>
       </c>
       <c r="B126" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14380,10 +14385,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470837</v>
+        <v>470932</v>
       </c>
       <c r="R126" t="n">
-        <v>6770498</v>
+        <v>6770480</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14452,10 +14457,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129959813</v>
+        <v>129957713</v>
       </c>
       <c r="B127" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14487,10 +14492,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470942</v>
+        <v>470904</v>
       </c>
       <c r="R127" t="n">
-        <v>6770455</v>
+        <v>6770718</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14559,10 +14564,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129959122</v>
+        <v>129962374</v>
       </c>
       <c r="B128" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14570,34 +14575,39 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470926</v>
+        <v>470996</v>
       </c>
       <c r="R128" t="n">
-        <v>6770613</v>
+        <v>6770611</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14666,10 +14676,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129958842</v>
+        <v>129958464</v>
       </c>
       <c r="B129" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14701,10 +14711,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470820</v>
+        <v>470822</v>
       </c>
       <c r="R129" t="n">
-        <v>6770624</v>
+        <v>6770673</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14773,10 +14783,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129954413</v>
+        <v>129959479</v>
       </c>
       <c r="B130" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14808,10 +14818,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>471028</v>
+        <v>470837</v>
       </c>
       <c r="R130" t="n">
-        <v>6770675</v>
+        <v>6770498</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14880,10 +14890,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129958464</v>
+        <v>129959787</v>
       </c>
       <c r="B131" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14915,10 +14925,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470822</v>
+        <v>470900</v>
       </c>
       <c r="R131" t="n">
-        <v>6770673</v>
+        <v>6770473</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14987,10 +14997,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129959787</v>
+        <v>129959813</v>
       </c>
       <c r="B132" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15022,10 +15032,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470900</v>
+        <v>470942</v>
       </c>
       <c r="R132" t="n">
-        <v>6770473</v>
+        <v>6770455</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15094,10 +15104,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129962374</v>
+        <v>129959122</v>
       </c>
       <c r="B133" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15105,39 +15115,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>470996</v>
+        <v>470926</v>
       </c>
       <c r="R133" t="n">
-        <v>6770611</v>
+        <v>6770613</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15206,50 +15211,45 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129962376</v>
+        <v>129954413</v>
       </c>
       <c r="B134" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
-      <c r="M134" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>470996</v>
+        <v>471028</v>
       </c>
       <c r="R134" t="n">
-        <v>6770611</v>
+        <v>6770675</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15318,10 +15318,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129959501</v>
+        <v>129959047</v>
       </c>
       <c r="B135" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15353,10 +15353,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470807</v>
+        <v>470908</v>
       </c>
       <c r="R135" t="n">
-        <v>6770491</v>
+        <v>6770622</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15425,10 +15425,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129954531</v>
+        <v>129959501</v>
       </c>
       <c r="B136" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15460,10 +15460,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>471106</v>
+        <v>470807</v>
       </c>
       <c r="R136" t="n">
-        <v>6770683</v>
+        <v>6770491</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15532,10 +15532,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129958895</v>
+        <v>129955100</v>
       </c>
       <c r="B137" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15567,10 +15567,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470887</v>
+        <v>470981</v>
       </c>
       <c r="R137" t="n">
-        <v>6770658</v>
+        <v>6770691</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15639,10 +15639,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129958499</v>
+        <v>129954531</v>
       </c>
       <c r="B138" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15674,10 +15674,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470850</v>
+        <v>471106</v>
       </c>
       <c r="R138" t="n">
-        <v>6770690</v>
+        <v>6770683</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15746,45 +15746,50 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129959047</v>
+        <v>129959110</v>
       </c>
       <c r="B139" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470908</v>
+        <v>470926</v>
       </c>
       <c r="R139" t="n">
-        <v>6770622</v>
+        <v>6770613</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15853,10 +15858,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129955100</v>
+        <v>129961622</v>
       </c>
       <c r="B140" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15888,10 +15893,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470981</v>
+        <v>471262</v>
       </c>
       <c r="R140" t="n">
-        <v>6770691</v>
+        <v>6770622</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15960,10 +15965,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129961622</v>
+        <v>129958010</v>
       </c>
       <c r="B141" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15995,10 +16000,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>471262</v>
+        <v>470894</v>
       </c>
       <c r="R141" t="n">
-        <v>6770622</v>
+        <v>6770713</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16067,10 +16072,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129958010</v>
+        <v>129958895</v>
       </c>
       <c r="B142" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16102,10 +16107,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>470894</v>
+        <v>470887</v>
       </c>
       <c r="R142" t="n">
-        <v>6770713</v>
+        <v>6770658</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16174,50 +16179,45 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129959110</v>
+        <v>129958499</v>
       </c>
       <c r="B143" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>470926</v>
+        <v>470850</v>
       </c>
       <c r="R143" t="n">
-        <v>6770613</v>
+        <v>6770690</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16286,45 +16286,50 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129962260</v>
+        <v>129960827</v>
       </c>
       <c r="B144" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471044</v>
+        <v>471078</v>
       </c>
       <c r="R144" t="n">
-        <v>6770615</v>
+        <v>6770561</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16393,10 +16398,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129959352</v>
+        <v>129962073</v>
       </c>
       <c r="B145" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16428,10 +16433,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>470879</v>
+        <v>471222</v>
       </c>
       <c r="R145" t="n">
-        <v>6770545</v>
+        <v>6770635</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16500,10 +16505,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129958937</v>
+        <v>129962430</v>
       </c>
       <c r="B146" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16511,34 +16516,39 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>470897</v>
+        <v>470989</v>
       </c>
       <c r="R146" t="n">
-        <v>6770647</v>
+        <v>6770629</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16607,10 +16617,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129958802</v>
+        <v>129962260</v>
       </c>
       <c r="B147" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16642,10 +16652,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470858</v>
+        <v>471044</v>
       </c>
       <c r="R147" t="n">
-        <v>6770602</v>
+        <v>6770615</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16714,10 +16724,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129962073</v>
+        <v>129959352</v>
       </c>
       <c r="B148" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16749,10 +16759,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>471222</v>
+        <v>470879</v>
       </c>
       <c r="R148" t="n">
-        <v>6770635</v>
+        <v>6770545</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16821,10 +16831,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129962430</v>
+        <v>129962343</v>
       </c>
       <c r="B149" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16852,7 +16862,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -16861,10 +16871,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>470989</v>
+        <v>471017</v>
       </c>
       <c r="R149" t="n">
-        <v>6770629</v>
+        <v>6770613</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16933,10 +16943,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129962343</v>
+        <v>129958937</v>
       </c>
       <c r="B150" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16944,39 +16954,34 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>471017</v>
+        <v>470897</v>
       </c>
       <c r="R150" t="n">
-        <v>6770613</v>
+        <v>6770647</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17045,50 +17050,45 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129960827</v>
+        <v>129958802</v>
       </c>
       <c r="B151" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>471078</v>
+        <v>470858</v>
       </c>
       <c r="R151" t="n">
-        <v>6770561</v>
+        <v>6770602</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17157,10 +17157,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129954534</v>
+        <v>129954803</v>
       </c>
       <c r="B152" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17192,10 +17192,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>471086</v>
+        <v>470938</v>
       </c>
       <c r="R152" t="n">
-        <v>6770684</v>
+        <v>6770693</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17264,10 +17264,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129958545</v>
+        <v>129954534</v>
       </c>
       <c r="B153" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17299,10 +17299,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>470877</v>
+        <v>471086</v>
       </c>
       <c r="R153" t="n">
-        <v>6770687</v>
+        <v>6770684</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17371,10 +17371,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129954408</v>
+        <v>129959294</v>
       </c>
       <c r="B154" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17406,10 +17406,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>471019</v>
+        <v>470904</v>
       </c>
       <c r="R154" t="n">
-        <v>6770666</v>
+        <v>6770537</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17478,10 +17478,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129954803</v>
+        <v>129958545</v>
       </c>
       <c r="B155" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17513,10 +17513,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470938</v>
+        <v>470877</v>
       </c>
       <c r="R155" t="n">
-        <v>6770693</v>
+        <v>6770687</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17585,10 +17585,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129959294</v>
+        <v>129954408</v>
       </c>
       <c r="B156" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>470904</v>
+        <v>471019</v>
       </c>
       <c r="R156" t="n">
-        <v>6770537</v>
+        <v>6770666</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17695,7 +17695,7 @@
         <v>129954442</v>
       </c>
       <c r="B157" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17799,10 +17799,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129960763</v>
+        <v>129958754</v>
       </c>
       <c r="B158" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17834,10 +17834,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>471062</v>
+        <v>470817</v>
       </c>
       <c r="R158" t="n">
-        <v>6770538</v>
+        <v>6770608</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17906,10 +17906,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129960642</v>
+        <v>129959389</v>
       </c>
       <c r="B159" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17917,39 +17917,34 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>471025</v>
+        <v>470824</v>
       </c>
       <c r="R159" t="n">
-        <v>6770488</v>
+        <v>6770523</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18018,10 +18013,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129958754</v>
+        <v>129960642</v>
       </c>
       <c r="B160" t="n">
-        <v>79095</v>
+        <v>57823</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18029,34 +18024,39 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>470817</v>
+        <v>471025</v>
       </c>
       <c r="R160" t="n">
-        <v>6770608</v>
+        <v>6770488</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18125,10 +18125,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129959389</v>
+        <v>129954452</v>
       </c>
       <c r="B161" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18160,10 +18160,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>470824</v>
+        <v>471058</v>
       </c>
       <c r="R161" t="n">
-        <v>6770523</v>
+        <v>6770677</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18232,10 +18232,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129954452</v>
+        <v>129959519</v>
       </c>
       <c r="B162" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18267,10 +18267,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>471058</v>
+        <v>470822</v>
       </c>
       <c r="R162" t="n">
-        <v>6770677</v>
+        <v>6770452</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18339,10 +18339,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129959519</v>
+        <v>129960763</v>
       </c>
       <c r="B163" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18374,10 +18374,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>470822</v>
+        <v>471062</v>
       </c>
       <c r="R163" t="n">
-        <v>6770452</v>
+        <v>6770538</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18449,7 +18449,7 @@
         <v>129958775</v>
       </c>
       <c r="B164" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18553,10 +18553,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129955313</v>
+        <v>129960929</v>
       </c>
       <c r="B165" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18588,10 +18588,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>470992</v>
+        <v>471159</v>
       </c>
       <c r="R165" t="n">
-        <v>6770702</v>
+        <v>6770613</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18660,10 +18660,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129959994</v>
+        <v>129955313</v>
       </c>
       <c r="B166" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18695,10 +18695,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470954</v>
+        <v>470992</v>
       </c>
       <c r="R166" t="n">
-        <v>6770475</v>
+        <v>6770702</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18767,10 +18767,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129958841</v>
+        <v>129959994</v>
       </c>
       <c r="B167" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18802,10 +18802,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470828</v>
+        <v>470954</v>
       </c>
       <c r="R167" t="n">
-        <v>6770636</v>
+        <v>6770475</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18874,10 +18874,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129962390</v>
+        <v>129958841</v>
       </c>
       <c r="B168" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18909,10 +18909,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>471004</v>
+        <v>470828</v>
       </c>
       <c r="R168" t="n">
-        <v>6770581</v>
+        <v>6770636</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18981,10 +18981,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129958466</v>
+        <v>129962390</v>
       </c>
       <c r="B169" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19016,10 +19016,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>470812</v>
+        <v>471004</v>
       </c>
       <c r="R169" t="n">
-        <v>6770670</v>
+        <v>6770581</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19091,7 +19091,7 @@
         <v>129954441</v>
       </c>
       <c r="B170" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19200,10 +19200,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129960929</v>
+        <v>129958466</v>
       </c>
       <c r="B171" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19235,10 +19235,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>471159</v>
+        <v>470812</v>
       </c>
       <c r="R171" t="n">
-        <v>6770613</v>
+        <v>6770670</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19307,10 +19307,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129962243</v>
+        <v>129959740</v>
       </c>
       <c r="B172" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19342,10 +19342,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>471074</v>
+        <v>470905</v>
       </c>
       <c r="R172" t="n">
-        <v>6770617</v>
+        <v>6770435</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19414,10 +19414,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129959717</v>
+        <v>129962243</v>
       </c>
       <c r="B173" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19449,10 +19449,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>470864</v>
+        <v>471074</v>
       </c>
       <c r="R173" t="n">
-        <v>6770438</v>
+        <v>6770617</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19521,10 +19521,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129962351</v>
+        <v>129959717</v>
       </c>
       <c r="B174" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19556,10 +19556,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>471017</v>
+        <v>470864</v>
       </c>
       <c r="R174" t="n">
-        <v>6770613</v>
+        <v>6770438</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19628,50 +19628,45 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129959579</v>
+        <v>129962351</v>
       </c>
       <c r="B175" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
-      <c r="M175" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P175" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>470822</v>
+        <v>471017</v>
       </c>
       <c r="R175" t="n">
-        <v>6770452</v>
+        <v>6770613</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19740,7 +19735,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129962436</v>
+        <v>129959285</v>
       </c>
       <c r="B176" t="n">
         <v>8451</v>
@@ -19780,10 +19775,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>470989</v>
+        <v>470922</v>
       </c>
       <c r="R176" t="n">
-        <v>6770629</v>
+        <v>6770556</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19852,50 +19847,45 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129959285</v>
+        <v>129962290</v>
       </c>
       <c r="B177" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>470922</v>
+        <v>471033</v>
       </c>
       <c r="R177" t="n">
-        <v>6770556</v>
+        <v>6770614</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19964,45 +19954,50 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129959740</v>
+        <v>129962436</v>
       </c>
       <c r="B178" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>470905</v>
+        <v>470989</v>
       </c>
       <c r="R178" t="n">
-        <v>6770435</v>
+        <v>6770629</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20071,45 +20066,50 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129962290</v>
+        <v>129959579</v>
       </c>
       <c r="B179" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P179" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>471033</v>
+        <v>470822</v>
       </c>
       <c r="R179" t="n">
-        <v>6770614</v>
+        <v>6770452</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20178,45 +20178,50 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129962443</v>
+        <v>129961109</v>
       </c>
       <c r="B180" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>470989</v>
+        <v>471175</v>
       </c>
       <c r="R180" t="n">
-        <v>6770629</v>
+        <v>6770631</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20285,10 +20290,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129958214</v>
+        <v>129962443</v>
       </c>
       <c r="B181" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20320,10 +20325,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>470823</v>
+        <v>470989</v>
       </c>
       <c r="R181" t="n">
-        <v>6770705</v>
+        <v>6770629</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20395,7 +20400,7 @@
         <v>129961937</v>
       </c>
       <c r="B182" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20499,50 +20504,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129961109</v>
+        <v>129958214</v>
       </c>
       <c r="B183" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>471175</v>
+        <v>470823</v>
       </c>
       <c r="R183" t="n">
-        <v>6770631</v>
+        <v>6770705</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20611,10 +20611,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129960864</v>
+        <v>129962447</v>
       </c>
       <c r="B184" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20646,10 +20646,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>471116</v>
+        <v>470993</v>
       </c>
       <c r="R184" t="n">
-        <v>6770565</v>
+        <v>6770643</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20721,7 +20721,7 @@
         <v>129959256</v>
       </c>
       <c r="B185" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20825,10 +20825,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129956859</v>
+        <v>129960864</v>
       </c>
       <c r="B186" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20860,10 +20860,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>470936</v>
+        <v>471116</v>
       </c>
       <c r="R186" t="n">
-        <v>6770721</v>
+        <v>6770565</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20932,10 +20932,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129958694</v>
+        <v>129956859</v>
       </c>
       <c r="B187" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -20967,10 +20967,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>470844</v>
+        <v>470936</v>
       </c>
       <c r="R187" t="n">
-        <v>6770699</v>
+        <v>6770721</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21039,10 +21039,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129959667</v>
+        <v>129959870</v>
       </c>
       <c r="B188" t="n">
-        <v>91662</v>
+        <v>57823</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21050,26 +21050,27 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P188" t="inlineStr">
@@ -21078,10 +21079,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>470864</v>
+        <v>470952</v>
       </c>
       <c r="R188" t="n">
-        <v>6770438</v>
+        <v>6770464</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21150,10 +21151,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129958228</v>
+        <v>129958694</v>
       </c>
       <c r="B189" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21185,10 +21186,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>470813</v>
+        <v>470844</v>
       </c>
       <c r="R189" t="n">
-        <v>6770681</v>
+        <v>6770699</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21257,10 +21258,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129959870</v>
+        <v>129959667</v>
       </c>
       <c r="B190" t="n">
-        <v>57738</v>
+        <v>91749</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21268,27 +21269,26 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -21297,10 +21297,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>470952</v>
+        <v>470864</v>
       </c>
       <c r="R190" t="n">
-        <v>6770464</v>
+        <v>6770438</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21369,10 +21369,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129962447</v>
+        <v>129958228</v>
       </c>
       <c r="B191" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21404,10 +21404,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>470993</v>
+        <v>470813</v>
       </c>
       <c r="R191" t="n">
-        <v>6770643</v>
+        <v>6770681</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21476,7 +21476,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129958199</v>
+        <v>129960746</v>
       </c>
       <c r="B192" t="n">
         <v>8451</v>
@@ -21516,10 +21516,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>470823</v>
+        <v>471053</v>
       </c>
       <c r="R192" t="n">
-        <v>6770705</v>
+        <v>6770528</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21588,50 +21588,45 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129960746</v>
+        <v>129954590</v>
       </c>
       <c r="B193" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="M193" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>471053</v>
+        <v>471013</v>
       </c>
       <c r="R193" t="n">
-        <v>6770528</v>
+        <v>6770715</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21700,45 +21695,50 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129954590</v>
+        <v>129958199</v>
       </c>
       <c r="B194" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P194" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>471013</v>
+        <v>470823</v>
       </c>
       <c r="R194" t="n">
-        <v>6770715</v>
+        <v>6770705</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21810,7 +21810,7 @@
         <v>129959434</v>
       </c>
       <c r="B195" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21922,7 +21922,7 @@
         <v>129959567</v>
       </c>
       <c r="B196" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22143,50 +22143,45 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129962346</v>
+        <v>129960891</v>
       </c>
       <c r="B198" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>471017</v>
+        <v>471147</v>
       </c>
       <c r="R198" t="n">
-        <v>6770613</v>
+        <v>6770575</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22258,7 +22253,7 @@
         <v>129956851</v>
       </c>
       <c r="B199" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22365,7 +22360,7 @@
         <v>129959375</v>
       </c>
       <c r="B200" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22469,45 +22464,50 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129960891</v>
+        <v>129962346</v>
       </c>
       <c r="B201" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>471147</v>
+        <v>471017</v>
       </c>
       <c r="R201" t="n">
-        <v>6770575</v>
+        <v>6770613</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22579,7 +22579,7 @@
         <v>129958828</v>
       </c>
       <c r="B202" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>129960843</v>
       </c>
       <c r="B203" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22790,10 +22790,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129962224</v>
+        <v>129962379</v>
       </c>
       <c r="B204" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22825,10 +22825,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>471098</v>
+        <v>470996</v>
       </c>
       <c r="R204" t="n">
-        <v>6770634</v>
+        <v>6770611</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22897,10 +22897,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129958691</v>
+        <v>129962224</v>
       </c>
       <c r="B205" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22908,39 +22908,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>470844</v>
+        <v>471098</v>
       </c>
       <c r="R205" t="n">
-        <v>6770699</v>
+        <v>6770634</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23009,7 +23004,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129959223</v>
+        <v>129954662</v>
       </c>
       <c r="B206" t="n">
         <v>8451</v>
@@ -23049,10 +23044,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470921</v>
+        <v>470941</v>
       </c>
       <c r="R206" t="n">
-        <v>6770579</v>
+        <v>6770708</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23121,38 +23116,38 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129954662</v>
+        <v>129958691</v>
       </c>
       <c r="B207" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -23161,10 +23156,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470941</v>
+        <v>470844</v>
       </c>
       <c r="R207" t="n">
-        <v>6770708</v>
+        <v>6770699</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23233,45 +23228,50 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129962379</v>
+        <v>129959223</v>
       </c>
       <c r="B208" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470996</v>
+        <v>470921</v>
       </c>
       <c r="R208" t="n">
-        <v>6770611</v>
+        <v>6770579</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23343,7 +23343,7 @@
         <v>129962417</v>
       </c>
       <c r="B209" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23450,7 +23450,7 @@
         <v>129960884</v>
       </c>
       <c r="B210" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23557,7 +23557,7 @@
         <v>129958706</v>
       </c>
       <c r="B211" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>129956843</v>
       </c>
       <c r="B212" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -23768,10 +23768,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129962119</v>
+        <v>129954584</v>
       </c>
       <c r="B213" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -23803,10 +23803,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>471156</v>
+        <v>471062</v>
       </c>
       <c r="R213" t="n">
-        <v>6770665</v>
+        <v>6770731</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23875,10 +23875,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129958133</v>
+        <v>129960790</v>
       </c>
       <c r="B214" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>470869</v>
+        <v>471073</v>
       </c>
       <c r="R214" t="n">
-        <v>6770702</v>
+        <v>6770551</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23982,10 +23982,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129954584</v>
+        <v>129962119</v>
       </c>
       <c r="B215" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24017,10 +24017,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471062</v>
+        <v>471156</v>
       </c>
       <c r="R215" t="n">
-        <v>6770731</v>
+        <v>6770665</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24089,45 +24089,50 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129960790</v>
+        <v>129959735</v>
       </c>
       <c r="B216" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471073</v>
+        <v>470868</v>
       </c>
       <c r="R216" t="n">
-        <v>6770551</v>
+        <v>6770431</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24196,50 +24201,45 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129959735</v>
+        <v>129958133</v>
       </c>
       <c r="B217" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>470868</v>
+        <v>470869</v>
       </c>
       <c r="R217" t="n">
-        <v>6770431</v>
+        <v>6770702</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24420,48 +24420,53 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129960823</v>
+        <v>129960514</v>
       </c>
       <c r="B219" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>471078</v>
+        <v>470976</v>
       </c>
       <c r="R219" t="n">
-        <v>6770561</v>
+        <v>6770536</v>
       </c>
       <c r="S219" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24501,11 +24506,6 @@
       <c r="AB219" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC219" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24535,7 +24535,7 @@
         <v>129962320</v>
       </c>
       <c r="B220" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -24639,53 +24639,48 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129960514</v>
+        <v>129960823</v>
       </c>
       <c r="B221" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>470976</v>
+        <v>471078</v>
       </c>
       <c r="R221" t="n">
-        <v>6770536</v>
+        <v>6770561</v>
       </c>
       <c r="S221" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24725,6 +24720,11 @@
       <c r="AB221" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24754,7 +24754,7 @@
         <v>129959250</v>
       </c>
       <c r="B222" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24858,45 +24858,50 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129961818</v>
+        <v>129959441</v>
       </c>
       <c r="B223" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>471228</v>
+        <v>470824</v>
       </c>
       <c r="R223" t="n">
-        <v>6770667</v>
+        <v>6770523</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24965,45 +24970,50 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129957969</v>
+        <v>129958131</v>
       </c>
       <c r="B224" t="n">
-        <v>79095</v>
+        <v>8451</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470911</v>
+        <v>470869</v>
       </c>
       <c r="R224" t="n">
-        <v>6770707</v>
+        <v>6770702</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25072,38 +25082,38 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129957253</v>
+        <v>129959710</v>
       </c>
       <c r="B225" t="n">
-        <v>57738</v>
+        <v>8451</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -25112,10 +25122,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470916</v>
+        <v>470864</v>
       </c>
       <c r="R225" t="n">
-        <v>6770721</v>
+        <v>6770438</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25184,38 +25194,38 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129959710</v>
+        <v>129957253</v>
       </c>
       <c r="B226" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -25224,10 +25234,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>470864</v>
+        <v>470916</v>
       </c>
       <c r="R226" t="n">
-        <v>6770438</v>
+        <v>6770721</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25296,50 +25306,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129958131</v>
+        <v>129961818</v>
       </c>
       <c r="B227" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>470869</v>
+        <v>471228</v>
       </c>
       <c r="R227" t="n">
-        <v>6770702</v>
+        <v>6770667</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25408,7 +25413,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129959441</v>
+        <v>129960657</v>
       </c>
       <c r="B228" t="n">
         <v>8451</v>
@@ -25448,10 +25453,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470824</v>
+        <v>471025</v>
       </c>
       <c r="R228" t="n">
-        <v>6770523</v>
+        <v>6770488</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25520,50 +25525,45 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129960657</v>
+        <v>129957969</v>
       </c>
       <c r="B229" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>471025</v>
+        <v>470911</v>
       </c>
       <c r="R229" t="n">
-        <v>6770488</v>
+        <v>6770707</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25635,7 +25635,7 @@
         <v>129959730</v>
       </c>
       <c r="B230" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>129960437</v>
       </c>
       <c r="B231" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>129960691</v>
       </c>
       <c r="B232" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>129958151</v>
       </c>
       <c r="B233" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -26068,7 +26068,7 @@
         <v>129958795</v>
       </c>
       <c r="B234" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -19307,45 +19307,50 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129959740</v>
+        <v>129959579</v>
       </c>
       <c r="B172" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>470905</v>
+        <v>470822</v>
       </c>
       <c r="R172" t="n">
-        <v>6770435</v>
+        <v>6770452</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19414,7 +19419,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129962243</v>
+        <v>129959740</v>
       </c>
       <c r="B173" t="n">
         <v>79180</v>
@@ -19449,10 +19454,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>471074</v>
+        <v>470905</v>
       </c>
       <c r="R173" t="n">
-        <v>6770617</v>
+        <v>6770435</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19521,7 +19526,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129959717</v>
+        <v>129962243</v>
       </c>
       <c r="B174" t="n">
         <v>79180</v>
@@ -19556,10 +19561,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>470864</v>
+        <v>471074</v>
       </c>
       <c r="R174" t="n">
-        <v>6770438</v>
+        <v>6770617</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19628,7 +19633,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129962351</v>
+        <v>129959717</v>
       </c>
       <c r="B175" t="n">
         <v>79180</v>
@@ -19663,10 +19668,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>471017</v>
+        <v>470864</v>
       </c>
       <c r="R175" t="n">
-        <v>6770613</v>
+        <v>6770438</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19735,50 +19740,45 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129959285</v>
+        <v>129962351</v>
       </c>
       <c r="B176" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P176" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>470922</v>
+        <v>471017</v>
       </c>
       <c r="R176" t="n">
-        <v>6770556</v>
+        <v>6770613</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19847,45 +19847,50 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129962290</v>
+        <v>129959285</v>
       </c>
       <c r="B177" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>471033</v>
+        <v>470922</v>
       </c>
       <c r="R177" t="n">
-        <v>6770614</v>
+        <v>6770556</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19954,50 +19959,45 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129962436</v>
+        <v>129962290</v>
       </c>
       <c r="B178" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
-      <c r="M178" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>470989</v>
+        <v>471033</v>
       </c>
       <c r="R178" t="n">
-        <v>6770629</v>
+        <v>6770614</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20066,7 +20066,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129959579</v>
+        <v>129962436</v>
       </c>
       <c r="B179" t="n">
         <v>8451</v>
@@ -20106,10 +20106,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>470822</v>
+        <v>470989</v>
       </c>
       <c r="R179" t="n">
-        <v>6770452</v>
+        <v>6770629</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20178,50 +20178,45 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129961109</v>
+        <v>129962443</v>
       </c>
       <c r="B180" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
-      <c r="M180" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P180" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>471175</v>
+        <v>470989</v>
       </c>
       <c r="R180" t="n">
-        <v>6770631</v>
+        <v>6770629</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20290,7 +20285,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129962443</v>
+        <v>129961937</v>
       </c>
       <c r="B181" t="n">
         <v>79180</v>
@@ -20325,10 +20320,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>470989</v>
+        <v>471216</v>
       </c>
       <c r="R181" t="n">
-        <v>6770629</v>
+        <v>6770650</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20397,7 +20392,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129961937</v>
+        <v>129958214</v>
       </c>
       <c r="B182" t="n">
         <v>79180</v>
@@ -20432,10 +20427,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471216</v>
+        <v>470823</v>
       </c>
       <c r="R182" t="n">
-        <v>6770650</v>
+        <v>6770705</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20504,45 +20499,50 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129958214</v>
+        <v>129961109</v>
       </c>
       <c r="B183" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>470823</v>
+        <v>471175</v>
       </c>
       <c r="R183" t="n">
-        <v>6770705</v>
+        <v>6770631</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -21476,38 +21476,38 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129960746</v>
+        <v>129959434</v>
       </c>
       <c r="B192" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
       <c r="M192" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P192" t="inlineStr">
@@ -21516,10 +21516,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>471053</v>
+        <v>470824</v>
       </c>
       <c r="R192" t="n">
-        <v>6770528</v>
+        <v>6770523</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21588,45 +21588,50 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129954590</v>
+        <v>129958199</v>
       </c>
       <c r="B193" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P193" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>471013</v>
+        <v>470823</v>
       </c>
       <c r="R193" t="n">
-        <v>6770715</v>
+        <v>6770705</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21695,7 +21700,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129958199</v>
+        <v>129960746</v>
       </c>
       <c r="B194" t="n">
         <v>8451</v>
@@ -21735,10 +21740,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>470823</v>
+        <v>471053</v>
       </c>
       <c r="R194" t="n">
-        <v>6770705</v>
+        <v>6770528</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21807,10 +21812,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129959434</v>
+        <v>129954590</v>
       </c>
       <c r="B195" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21818,39 +21823,34 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>470824</v>
+        <v>471013</v>
       </c>
       <c r="R195" t="n">
-        <v>6770523</v>
+        <v>6770715</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22143,45 +22143,50 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129960891</v>
+        <v>129962346</v>
       </c>
       <c r="B198" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>471147</v>
+        <v>471017</v>
       </c>
       <c r="R198" t="n">
-        <v>6770575</v>
+        <v>6770613</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22250,7 +22255,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129956851</v>
+        <v>129960891</v>
       </c>
       <c r="B199" t="n">
         <v>79180</v>
@@ -22285,10 +22290,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>470928</v>
+        <v>471147</v>
       </c>
       <c r="R199" t="n">
-        <v>6770695</v>
+        <v>6770575</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22357,7 +22362,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129959375</v>
+        <v>129956851</v>
       </c>
       <c r="B200" t="n">
         <v>79180</v>
@@ -22392,10 +22397,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>470851</v>
+        <v>470928</v>
       </c>
       <c r="R200" t="n">
-        <v>6770520</v>
+        <v>6770695</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22464,50 +22469,45 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129962346</v>
+        <v>129959375</v>
       </c>
       <c r="B201" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
-      <c r="M201" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>471017</v>
+        <v>470851</v>
       </c>
       <c r="R201" t="n">
-        <v>6770613</v>
+        <v>6770520</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22790,7 +22790,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129962379</v>
+        <v>129962224</v>
       </c>
       <c r="B204" t="n">
         <v>79180</v>
@@ -22825,10 +22825,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>470996</v>
+        <v>471098</v>
       </c>
       <c r="R204" t="n">
-        <v>6770611</v>
+        <v>6770634</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22897,10 +22897,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129962224</v>
+        <v>129958691</v>
       </c>
       <c r="B205" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22908,34 +22908,39 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>471098</v>
+        <v>470844</v>
       </c>
       <c r="R205" t="n">
-        <v>6770634</v>
+        <v>6770699</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23004,50 +23009,45 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129954662</v>
+        <v>129962379</v>
       </c>
       <c r="B206" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
-      <c r="M206" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470941</v>
+        <v>470996</v>
       </c>
       <c r="R206" t="n">
-        <v>6770708</v>
+        <v>6770611</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23116,38 +23116,38 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129958691</v>
+        <v>129959223</v>
       </c>
       <c r="B207" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
       <c r="M207" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P207" t="inlineStr">
@@ -23156,10 +23156,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470844</v>
+        <v>470921</v>
       </c>
       <c r="R207" t="n">
-        <v>6770699</v>
+        <v>6770579</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23228,7 +23228,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129959223</v>
+        <v>129954662</v>
       </c>
       <c r="B208" t="n">
         <v>8451</v>
@@ -23268,10 +23268,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470921</v>
+        <v>470941</v>
       </c>
       <c r="R208" t="n">
-        <v>6770579</v>
+        <v>6770708</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23661,7 +23661,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129956843</v>
+        <v>129962119</v>
       </c>
       <c r="B212" t="n">
         <v>79180</v>
@@ -23696,10 +23696,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>470953</v>
+        <v>471156</v>
       </c>
       <c r="R212" t="n">
-        <v>6770692</v>
+        <v>6770665</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23768,7 +23768,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129954584</v>
+        <v>129956843</v>
       </c>
       <c r="B213" t="n">
         <v>79180</v>
@@ -23803,10 +23803,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>471062</v>
+        <v>470953</v>
       </c>
       <c r="R213" t="n">
-        <v>6770731</v>
+        <v>6770692</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23875,7 +23875,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129960790</v>
+        <v>129954584</v>
       </c>
       <c r="B214" t="n">
         <v>79180</v>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471073</v>
+        <v>471062</v>
       </c>
       <c r="R214" t="n">
-        <v>6770551</v>
+        <v>6770731</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23982,7 +23982,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129962119</v>
+        <v>129960790</v>
       </c>
       <c r="B215" t="n">
         <v>79180</v>
@@ -24017,10 +24017,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471156</v>
+        <v>471073</v>
       </c>
       <c r="R215" t="n">
-        <v>6770665</v>
+        <v>6770551</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -8382,32 +8382,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129944454</v>
+        <v>129946062</v>
       </c>
       <c r="B71" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8417,10 +8417,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471330</v>
+        <v>471161</v>
       </c>
       <c r="R71" t="n">
-        <v>6770712</v>
+        <v>6770705</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8489,7 +8489,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129946062</v>
+        <v>129946408</v>
       </c>
       <c r="B72" t="n">
         <v>79180</v>
@@ -8524,10 +8524,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471161</v>
+        <v>470921</v>
       </c>
       <c r="R72" t="n">
-        <v>6770705</v>
+        <v>6770579</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8596,7 +8596,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129946408</v>
+        <v>129944164</v>
       </c>
       <c r="B73" t="n">
         <v>79180</v>
@@ -8631,10 +8631,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>470921</v>
+        <v>471363</v>
       </c>
       <c r="R73" t="n">
-        <v>6770579</v>
+        <v>6770736</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8703,32 +8703,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129944164</v>
+        <v>129944454</v>
       </c>
       <c r="B74" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471363</v>
+        <v>471330</v>
       </c>
       <c r="R74" t="n">
-        <v>6770736</v>
+        <v>6770712</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9131,10 +9131,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129946436</v>
+        <v>129944762</v>
       </c>
       <c r="B78" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9142,39 +9142,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>470971</v>
+        <v>471276</v>
       </c>
       <c r="R78" t="n">
-        <v>6770603</v>
+        <v>6770703</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9243,10 +9238,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129944762</v>
+        <v>129946436</v>
       </c>
       <c r="B79" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9254,34 +9249,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>471276</v>
+        <v>470971</v>
       </c>
       <c r="R79" t="n">
-        <v>6770703</v>
+        <v>6770603</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9564,10 +9564,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129946321</v>
+        <v>129944037</v>
       </c>
       <c r="B82" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9575,39 +9575,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>470871</v>
+        <v>471417</v>
       </c>
       <c r="R82" t="n">
-        <v>6770635</v>
+        <v>6770738</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9676,7 +9671,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944037</v>
+        <v>129944210</v>
       </c>
       <c r="B83" t="n">
         <v>79180</v>
@@ -9711,10 +9706,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471417</v>
+        <v>471390</v>
       </c>
       <c r="R83" t="n">
-        <v>6770738</v>
+        <v>6770705</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9783,45 +9778,50 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129946047</v>
+        <v>129946321</v>
       </c>
       <c r="B84" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471161</v>
+        <v>470871</v>
       </c>
       <c r="R84" t="n">
-        <v>6770705</v>
+        <v>6770635</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9890,32 +9890,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129944210</v>
+        <v>129946047</v>
       </c>
       <c r="B85" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9925,7 +9925,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471390</v>
+        <v>471161</v>
       </c>
       <c r="R85" t="n">
         <v>6770705</v>
@@ -10430,50 +10430,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129945161</v>
+        <v>129944975</v>
       </c>
       <c r="B90" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471198</v>
+        <v>471242</v>
       </c>
       <c r="R90" t="n">
-        <v>6770725</v>
+        <v>6770682</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10542,7 +10537,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129944975</v>
+        <v>129946708</v>
       </c>
       <c r="B91" t="n">
         <v>79180</v>
@@ -10577,10 +10572,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471242</v>
+        <v>471171</v>
       </c>
       <c r="R91" t="n">
-        <v>6770682</v>
+        <v>6770660</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10649,45 +10644,50 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129946708</v>
+        <v>129945161</v>
       </c>
       <c r="B92" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471171</v>
+        <v>471198</v>
       </c>
       <c r="R92" t="n">
-        <v>6770660</v>
+        <v>6770725</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129946391</v>
+        <v>129943855</v>
       </c>
       <c r="B93" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10767,39 +10767,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>470921</v>
+        <v>471451</v>
       </c>
       <c r="R93" t="n">
-        <v>6770579</v>
+        <v>6770706</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10868,7 +10863,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129943855</v>
+        <v>129945066</v>
       </c>
       <c r="B94" t="n">
         <v>79180</v>
@@ -10903,10 +10898,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471451</v>
+        <v>471239</v>
       </c>
       <c r="R94" t="n">
-        <v>6770706</v>
+        <v>6770732</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10975,50 +10970,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129946444</v>
+        <v>129944756</v>
       </c>
       <c r="B95" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>470971</v>
+        <v>471288</v>
       </c>
       <c r="R95" t="n">
-        <v>6770603</v>
+        <v>6770685</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11203,45 +11193,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129945066</v>
+        <v>129946444</v>
       </c>
       <c r="B97" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>471239</v>
+        <v>470971</v>
       </c>
       <c r="R97" t="n">
-        <v>6770732</v>
+        <v>6770603</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11310,10 +11305,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129944756</v>
+        <v>129946391</v>
       </c>
       <c r="B98" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11321,34 +11316,39 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>471288</v>
+        <v>470921</v>
       </c>
       <c r="R98" t="n">
-        <v>6770685</v>
+        <v>6770579</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11417,10 +11417,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129944926</v>
+        <v>129945156</v>
       </c>
       <c r="B99" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11428,34 +11428,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471263</v>
+        <v>471198</v>
       </c>
       <c r="R99" t="n">
-        <v>6770694</v>
+        <v>6770725</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11524,7 +11529,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944544</v>
+        <v>129944926</v>
       </c>
       <c r="B100" t="n">
         <v>79180</v>
@@ -11559,10 +11564,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471330</v>
+        <v>471263</v>
       </c>
       <c r="R100" t="n">
-        <v>6770712</v>
+        <v>6770694</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11631,10 +11636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129945156</v>
+        <v>129944544</v>
       </c>
       <c r="B101" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11642,39 +11647,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471198</v>
+        <v>471330</v>
       </c>
       <c r="R101" t="n">
-        <v>6770725</v>
+        <v>6770712</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129943849</v>
+        <v>129944488</v>
       </c>
       <c r="B106" t="n">
-        <v>91749</v>
+        <v>79180</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12187,38 +12187,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471451</v>
+        <v>471318</v>
       </c>
       <c r="R106" t="n">
-        <v>6770706</v>
+        <v>6770729</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12287,7 +12283,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129944488</v>
+        <v>129944178</v>
       </c>
       <c r="B107" t="n">
         <v>79180</v>
@@ -12322,10 +12318,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471318</v>
+        <v>471372</v>
       </c>
       <c r="R107" t="n">
-        <v>6770729</v>
+        <v>6770719</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12394,10 +12390,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129944178</v>
+        <v>129943849</v>
       </c>
       <c r="B108" t="n">
-        <v>79180</v>
+        <v>91749</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12405,34 +12401,38 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471372</v>
+        <v>471451</v>
       </c>
       <c r="R108" t="n">
-        <v>6770719</v>
+        <v>6770706</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13581,50 +13581,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129945444</v>
+        <v>129944523</v>
       </c>
       <c r="B119" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>471189</v>
+        <v>471303</v>
       </c>
       <c r="R119" t="n">
-        <v>6770706</v>
+        <v>6770699</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13693,7 +13688,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129944158</v>
+        <v>129945444</v>
       </c>
       <c r="B120" t="n">
         <v>8451</v>
@@ -13733,10 +13728,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>471363</v>
+        <v>471189</v>
       </c>
       <c r="R120" t="n">
-        <v>6770736</v>
+        <v>6770706</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13805,45 +13800,50 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129944523</v>
+        <v>129944158</v>
       </c>
       <c r="B121" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>471303</v>
+        <v>471363</v>
       </c>
       <c r="R121" t="n">
-        <v>6770699</v>
+        <v>6770736</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14136,7 +14136,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129958842</v>
+        <v>129959122</v>
       </c>
       <c r="B124" t="n">
         <v>79180</v>
@@ -14171,10 +14171,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>470820</v>
+        <v>470926</v>
       </c>
       <c r="R124" t="n">
-        <v>6770624</v>
+        <v>6770613</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14243,7 +14243,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129960901</v>
+        <v>129959787</v>
       </c>
       <c r="B125" t="n">
         <v>79180</v>
@@ -14278,10 +14278,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>471185</v>
+        <v>470900</v>
       </c>
       <c r="R125" t="n">
-        <v>6770590</v>
+        <v>6770473</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14350,7 +14350,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129960002</v>
+        <v>129960901</v>
       </c>
       <c r="B126" t="n">
         <v>79180</v>
@@ -14385,10 +14385,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470932</v>
+        <v>471185</v>
       </c>
       <c r="R126" t="n">
-        <v>6770480</v>
+        <v>6770590</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14457,7 +14457,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129957713</v>
+        <v>129960002</v>
       </c>
       <c r="B127" t="n">
         <v>79180</v>
@@ -14492,10 +14492,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470904</v>
+        <v>470932</v>
       </c>
       <c r="R127" t="n">
-        <v>6770718</v>
+        <v>6770480</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14564,10 +14564,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129962374</v>
+        <v>129957713</v>
       </c>
       <c r="B128" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14575,39 +14575,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P128" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470996</v>
+        <v>470904</v>
       </c>
       <c r="R128" t="n">
-        <v>6770611</v>
+        <v>6770718</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14890,7 +14885,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129959787</v>
+        <v>129959813</v>
       </c>
       <c r="B131" t="n">
         <v>79180</v>
@@ -14925,10 +14920,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470900</v>
+        <v>470942</v>
       </c>
       <c r="R131" t="n">
-        <v>6770473</v>
+        <v>6770455</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14997,7 +14992,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129959813</v>
+        <v>129958842</v>
       </c>
       <c r="B132" t="n">
         <v>79180</v>
@@ -15032,10 +15027,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470942</v>
+        <v>470820</v>
       </c>
       <c r="R132" t="n">
-        <v>6770455</v>
+        <v>6770624</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15104,7 +15099,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129959122</v>
+        <v>129954413</v>
       </c>
       <c r="B133" t="n">
         <v>79180</v>
@@ -15139,10 +15134,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>470926</v>
+        <v>471028</v>
       </c>
       <c r="R133" t="n">
-        <v>6770613</v>
+        <v>6770675</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15211,10 +15206,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129954413</v>
+        <v>129962374</v>
       </c>
       <c r="B134" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15222,34 +15217,39 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>471028</v>
+        <v>470996</v>
       </c>
       <c r="R134" t="n">
-        <v>6770675</v>
+        <v>6770611</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15318,45 +15318,50 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129959047</v>
+        <v>129959110</v>
       </c>
       <c r="B135" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470908</v>
+        <v>470926</v>
       </c>
       <c r="R135" t="n">
-        <v>6770622</v>
+        <v>6770613</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15425,7 +15430,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129959501</v>
+        <v>129955100</v>
       </c>
       <c r="B136" t="n">
         <v>79180</v>
@@ -15460,10 +15465,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470807</v>
+        <v>470981</v>
       </c>
       <c r="R136" t="n">
-        <v>6770491</v>
+        <v>6770691</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15532,7 +15537,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129955100</v>
+        <v>129958010</v>
       </c>
       <c r="B137" t="n">
         <v>79180</v>
@@ -15567,10 +15572,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470981</v>
+        <v>470894</v>
       </c>
       <c r="R137" t="n">
-        <v>6770691</v>
+        <v>6770713</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15639,7 +15644,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129954531</v>
+        <v>129959047</v>
       </c>
       <c r="B138" t="n">
         <v>79180</v>
@@ -15674,10 +15679,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>471106</v>
+        <v>470908</v>
       </c>
       <c r="R138" t="n">
-        <v>6770683</v>
+        <v>6770622</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15746,50 +15751,45 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129959110</v>
+        <v>129959501</v>
       </c>
       <c r="B139" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="M139" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470926</v>
+        <v>470807</v>
       </c>
       <c r="R139" t="n">
-        <v>6770613</v>
+        <v>6770491</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15965,7 +15965,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129958010</v>
+        <v>129954531</v>
       </c>
       <c r="B141" t="n">
         <v>79180</v>
@@ -16000,10 +16000,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>470894</v>
+        <v>471106</v>
       </c>
       <c r="R141" t="n">
-        <v>6770713</v>
+        <v>6770683</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16286,50 +16286,45 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129960827</v>
+        <v>129959352</v>
       </c>
       <c r="B144" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P144" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471078</v>
+        <v>470879</v>
       </c>
       <c r="R144" t="n">
-        <v>6770561</v>
+        <v>6770545</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16505,10 +16500,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129962430</v>
+        <v>129962260</v>
       </c>
       <c r="B146" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16516,39 +16511,34 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="M146" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P146" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>470989</v>
+        <v>471044</v>
       </c>
       <c r="R146" t="n">
-        <v>6770629</v>
+        <v>6770615</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16617,7 +16607,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129962260</v>
+        <v>129958937</v>
       </c>
       <c r="B147" t="n">
         <v>79180</v>
@@ -16652,10 +16642,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>471044</v>
+        <v>470897</v>
       </c>
       <c r="R147" t="n">
-        <v>6770615</v>
+        <v>6770647</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16724,7 +16714,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129959352</v>
+        <v>129958802</v>
       </c>
       <c r="B148" t="n">
         <v>79180</v>
@@ -16759,10 +16749,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470879</v>
+        <v>470858</v>
       </c>
       <c r="R148" t="n">
-        <v>6770545</v>
+        <v>6770602</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16831,7 +16821,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129962343</v>
+        <v>129962430</v>
       </c>
       <c r="B149" t="n">
         <v>57823</v>
@@ -16862,7 +16852,7 @@
       <c r="I149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P149" t="inlineStr">
@@ -16871,10 +16861,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>471017</v>
+        <v>470989</v>
       </c>
       <c r="R149" t="n">
-        <v>6770613</v>
+        <v>6770629</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16943,10 +16933,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129958937</v>
+        <v>129962343</v>
       </c>
       <c r="B150" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16954,34 +16944,39 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P150" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>470897</v>
+        <v>471017</v>
       </c>
       <c r="R150" t="n">
-        <v>6770647</v>
+        <v>6770613</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17050,45 +17045,50 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129958802</v>
+        <v>129960827</v>
       </c>
       <c r="B151" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P151" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>470858</v>
+        <v>471078</v>
       </c>
       <c r="R151" t="n">
-        <v>6770602</v>
+        <v>6770561</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17264,7 +17264,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129954534</v>
+        <v>129958545</v>
       </c>
       <c r="B153" t="n">
         <v>79180</v>
@@ -17299,10 +17299,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>471086</v>
+        <v>470877</v>
       </c>
       <c r="R153" t="n">
-        <v>6770684</v>
+        <v>6770687</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17371,7 +17371,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>129959294</v>
+        <v>129954408</v>
       </c>
       <c r="B154" t="n">
         <v>79180</v>
@@ -17406,10 +17406,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>470904</v>
+        <v>471019</v>
       </c>
       <c r="R154" t="n">
-        <v>6770537</v>
+        <v>6770666</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17478,7 +17478,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129958545</v>
+        <v>129954534</v>
       </c>
       <c r="B155" t="n">
         <v>79180</v>
@@ -17513,10 +17513,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470877</v>
+        <v>471086</v>
       </c>
       <c r="R155" t="n">
-        <v>6770687</v>
+        <v>6770684</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17585,7 +17585,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129954408</v>
+        <v>129959294</v>
       </c>
       <c r="B156" t="n">
         <v>79180</v>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>471019</v>
+        <v>470904</v>
       </c>
       <c r="R156" t="n">
-        <v>6770666</v>
+        <v>6770537</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17692,7 +17692,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129954442</v>
+        <v>129958754</v>
       </c>
       <c r="B157" t="n">
         <v>79180</v>
@@ -17727,10 +17727,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>471053</v>
+        <v>470817</v>
       </c>
       <c r="R157" t="n">
-        <v>6770682</v>
+        <v>6770608</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17799,7 +17799,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129958754</v>
+        <v>129959389</v>
       </c>
       <c r="B158" t="n">
         <v>79180</v>
@@ -17834,10 +17834,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470817</v>
+        <v>470824</v>
       </c>
       <c r="R158" t="n">
-        <v>6770608</v>
+        <v>6770523</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17906,7 +17906,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129959389</v>
+        <v>129954445</v>
       </c>
       <c r="B159" t="n">
         <v>79180</v>
@@ -17941,10 +17941,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>470824</v>
+        <v>471053</v>
       </c>
       <c r="R159" t="n">
-        <v>6770523</v>
+        <v>6770682</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18013,10 +18013,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129960642</v>
+        <v>129954452</v>
       </c>
       <c r="B160" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18024,39 +18024,34 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P160" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>471025</v>
+        <v>471058</v>
       </c>
       <c r="R160" t="n">
-        <v>6770488</v>
+        <v>6770677</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18125,7 +18120,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129954452</v>
+        <v>129959519</v>
       </c>
       <c r="B161" t="n">
         <v>79180</v>
@@ -18160,10 +18155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>471058</v>
+        <v>470822</v>
       </c>
       <c r="R161" t="n">
-        <v>6770677</v>
+        <v>6770452</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18232,10 +18227,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129959519</v>
+        <v>129960642</v>
       </c>
       <c r="B162" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18243,34 +18238,39 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>470822</v>
+        <v>471025</v>
       </c>
       <c r="R162" t="n">
-        <v>6770452</v>
+        <v>6770488</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18553,7 +18553,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129960929</v>
+        <v>129962390</v>
       </c>
       <c r="B165" t="n">
         <v>79180</v>
@@ -18588,10 +18588,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>471159</v>
+        <v>471004</v>
       </c>
       <c r="R165" t="n">
-        <v>6770613</v>
+        <v>6770581</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18660,7 +18660,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129955313</v>
+        <v>129960929</v>
       </c>
       <c r="B166" t="n">
         <v>79180</v>
@@ -18695,10 +18695,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470992</v>
+        <v>471159</v>
       </c>
       <c r="R166" t="n">
-        <v>6770702</v>
+        <v>6770613</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18767,7 +18767,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129959994</v>
+        <v>129955313</v>
       </c>
       <c r="B167" t="n">
         <v>79180</v>
@@ -18802,10 +18802,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470954</v>
+        <v>470992</v>
       </c>
       <c r="R167" t="n">
-        <v>6770475</v>
+        <v>6770702</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18874,7 +18874,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129958841</v>
+        <v>129959994</v>
       </c>
       <c r="B168" t="n">
         <v>79180</v>
@@ -18909,10 +18909,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>470828</v>
+        <v>470954</v>
       </c>
       <c r="R168" t="n">
-        <v>6770636</v>
+        <v>6770475</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18981,7 +18981,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129962390</v>
+        <v>129958841</v>
       </c>
       <c r="B169" t="n">
         <v>79180</v>
@@ -19016,10 +19016,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>471004</v>
+        <v>470828</v>
       </c>
       <c r="R169" t="n">
-        <v>6770581</v>
+        <v>6770636</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19088,10 +19088,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129954441</v>
+        <v>129958466</v>
       </c>
       <c r="B170" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19099,39 +19099,34 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
-      <c r="M170" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P170" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>471052</v>
+        <v>470812</v>
       </c>
       <c r="R170" t="n">
-        <v>6770696</v>
+        <v>6770670</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19200,10 +19195,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129958466</v>
+        <v>129954441</v>
       </c>
       <c r="B171" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19211,34 +19206,39 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>470812</v>
+        <v>471052</v>
       </c>
       <c r="R171" t="n">
-        <v>6770670</v>
+        <v>6770696</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19307,50 +19307,45 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129959579</v>
+        <v>129962290</v>
       </c>
       <c r="B172" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>470822</v>
+        <v>471033</v>
       </c>
       <c r="R172" t="n">
-        <v>6770452</v>
+        <v>6770614</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19959,45 +19954,50 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129962290</v>
+        <v>129962436</v>
       </c>
       <c r="B178" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P178" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>471033</v>
+        <v>470989</v>
       </c>
       <c r="R178" t="n">
-        <v>6770614</v>
+        <v>6770629</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20066,7 +20066,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129962436</v>
+        <v>129959579</v>
       </c>
       <c r="B179" t="n">
         <v>8451</v>
@@ -20106,10 +20106,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>470989</v>
+        <v>470822</v>
       </c>
       <c r="R179" t="n">
-        <v>6770629</v>
+        <v>6770452</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20178,7 +20178,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129962443</v>
+        <v>129958214</v>
       </c>
       <c r="B180" t="n">
         <v>79180</v>
@@ -20213,10 +20213,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>470989</v>
+        <v>470823</v>
       </c>
       <c r="R180" t="n">
-        <v>6770629</v>
+        <v>6770705</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20392,45 +20392,50 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129958214</v>
+        <v>129961109</v>
       </c>
       <c r="B182" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>470823</v>
+        <v>471175</v>
       </c>
       <c r="R182" t="n">
-        <v>6770705</v>
+        <v>6770631</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20499,50 +20504,45 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129961109</v>
+        <v>129962443</v>
       </c>
       <c r="B183" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
-      <c r="M183" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>471175</v>
+        <v>470989</v>
       </c>
       <c r="R183" t="n">
-        <v>6770631</v>
+        <v>6770629</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20611,10 +20611,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129962447</v>
+        <v>129959667</v>
       </c>
       <c r="B184" t="n">
-        <v>79180</v>
+        <v>91749</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20622,34 +20622,38 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P184" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>470993</v>
+        <v>470864</v>
       </c>
       <c r="R184" t="n">
-        <v>6770643</v>
+        <v>6770438</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20718,7 +20722,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129959256</v>
+        <v>129962447</v>
       </c>
       <c r="B185" t="n">
         <v>79180</v>
@@ -20753,10 +20757,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>470922</v>
+        <v>470993</v>
       </c>
       <c r="R185" t="n">
-        <v>6770556</v>
+        <v>6770643</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20932,7 +20936,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129956859</v>
+        <v>129959256</v>
       </c>
       <c r="B187" t="n">
         <v>79180</v>
@@ -20967,10 +20971,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>470936</v>
+        <v>470922</v>
       </c>
       <c r="R187" t="n">
-        <v>6770721</v>
+        <v>6770556</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21039,10 +21043,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129959870</v>
+        <v>129956859</v>
       </c>
       <c r="B188" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21050,39 +21054,34 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
-      <c r="M188" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P188" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>470952</v>
+        <v>470936</v>
       </c>
       <c r="R188" t="n">
-        <v>6770464</v>
+        <v>6770721</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21151,7 +21150,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129958694</v>
+        <v>129958228</v>
       </c>
       <c r="B189" t="n">
         <v>79180</v>
@@ -21186,10 +21185,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>470844</v>
+        <v>470813</v>
       </c>
       <c r="R189" t="n">
-        <v>6770699</v>
+        <v>6770681</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21258,10 +21257,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129959667</v>
+        <v>129959870</v>
       </c>
       <c r="B190" t="n">
-        <v>91749</v>
+        <v>57823</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21269,26 +21268,27 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I190" t="inlineStr">
-        <is>
-          <t>2</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P190" t="inlineStr">
@@ -21297,10 +21297,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>470864</v>
+        <v>470952</v>
       </c>
       <c r="R190" t="n">
-        <v>6770438</v>
+        <v>6770464</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21369,7 +21369,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129958228</v>
+        <v>129958694</v>
       </c>
       <c r="B191" t="n">
         <v>79180</v>
@@ -21404,10 +21404,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>470813</v>
+        <v>470844</v>
       </c>
       <c r="R191" t="n">
-        <v>6770681</v>
+        <v>6770699</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21919,10 +21919,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129959567</v>
+        <v>129960891</v>
       </c>
       <c r="B196" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21930,39 +21930,34 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P196" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>470822</v>
+        <v>471147</v>
       </c>
       <c r="R196" t="n">
-        <v>6770452</v>
+        <v>6770575</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22031,50 +22026,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129959924</v>
+        <v>129959375</v>
       </c>
       <c r="B197" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>470944</v>
+        <v>470851</v>
       </c>
       <c r="R197" t="n">
-        <v>6770458</v>
+        <v>6770520</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22143,38 +22133,38 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129962346</v>
+        <v>129959567</v>
       </c>
       <c r="B198" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P198" t="inlineStr">
@@ -22183,10 +22173,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>471017</v>
+        <v>470822</v>
       </c>
       <c r="R198" t="n">
-        <v>6770613</v>
+        <v>6770452</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22255,7 +22245,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129960891</v>
+        <v>129956851</v>
       </c>
       <c r="B199" t="n">
         <v>79180</v>
@@ -22290,10 +22280,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>471147</v>
+        <v>470928</v>
       </c>
       <c r="R199" t="n">
-        <v>6770575</v>
+        <v>6770695</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22362,45 +22352,50 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129956851</v>
+        <v>129959924</v>
       </c>
       <c r="B200" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P200" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>470928</v>
+        <v>470944</v>
       </c>
       <c r="R200" t="n">
-        <v>6770695</v>
+        <v>6770458</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22469,45 +22464,50 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129959375</v>
+        <v>129962346</v>
       </c>
       <c r="B201" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P201" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>470851</v>
+        <v>471017</v>
       </c>
       <c r="R201" t="n">
-        <v>6770520</v>
+        <v>6770613</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22790,7 +22790,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129962224</v>
+        <v>129962379</v>
       </c>
       <c r="B204" t="n">
         <v>79180</v>
@@ -22825,10 +22825,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>471098</v>
+        <v>470996</v>
       </c>
       <c r="R204" t="n">
-        <v>6770634</v>
+        <v>6770611</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22897,10 +22897,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129958691</v>
+        <v>129962224</v>
       </c>
       <c r="B205" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22908,39 +22908,34 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
-      <c r="M205" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>470844</v>
+        <v>471098</v>
       </c>
       <c r="R205" t="n">
-        <v>6770699</v>
+        <v>6770634</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23009,10 +23004,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129962379</v>
+        <v>129958691</v>
       </c>
       <c r="B206" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23020,34 +23015,39 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P206" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470996</v>
+        <v>470844</v>
       </c>
       <c r="R206" t="n">
-        <v>6770611</v>
+        <v>6770699</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23116,7 +23116,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129959223</v>
+        <v>129954662</v>
       </c>
       <c r="B207" t="n">
         <v>8451</v>
@@ -23156,10 +23156,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470921</v>
+        <v>470941</v>
       </c>
       <c r="R207" t="n">
-        <v>6770579</v>
+        <v>6770708</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23228,7 +23228,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129954662</v>
+        <v>129959223</v>
       </c>
       <c r="B208" t="n">
         <v>8451</v>
@@ -23268,10 +23268,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470941</v>
+        <v>470921</v>
       </c>
       <c r="R208" t="n">
-        <v>6770708</v>
+        <v>6770579</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23661,7 +23661,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129962119</v>
+        <v>129956843</v>
       </c>
       <c r="B212" t="n">
         <v>79180</v>
@@ -23696,10 +23696,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>471156</v>
+        <v>470953</v>
       </c>
       <c r="R212" t="n">
-        <v>6770665</v>
+        <v>6770692</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23768,7 +23768,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129956843</v>
+        <v>129958133</v>
       </c>
       <c r="B213" t="n">
         <v>79180</v>
@@ -23803,10 +23803,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>470953</v>
+        <v>470869</v>
       </c>
       <c r="R213" t="n">
-        <v>6770692</v>
+        <v>6770702</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23875,7 +23875,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129954584</v>
+        <v>129960790</v>
       </c>
       <c r="B214" t="n">
         <v>79180</v>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471062</v>
+        <v>471073</v>
       </c>
       <c r="R214" t="n">
-        <v>6770731</v>
+        <v>6770551</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23982,7 +23982,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129960790</v>
+        <v>129954584</v>
       </c>
       <c r="B215" t="n">
         <v>79180</v>
@@ -24017,10 +24017,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471073</v>
+        <v>471062</v>
       </c>
       <c r="R215" t="n">
-        <v>6770551</v>
+        <v>6770731</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24089,50 +24089,45 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129959735</v>
+        <v>129962119</v>
       </c>
       <c r="B216" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
-      <c r="M216" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P216" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>470868</v>
+        <v>471156</v>
       </c>
       <c r="R216" t="n">
-        <v>6770431</v>
+        <v>6770665</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24201,45 +24196,50 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129958133</v>
+        <v>129959735</v>
       </c>
       <c r="B217" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
+      <c r="M217" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>470869</v>
+        <v>470868</v>
       </c>
       <c r="R217" t="n">
-        <v>6770702</v>
+        <v>6770431</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24858,50 +24858,45 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129959441</v>
+        <v>129961818</v>
       </c>
       <c r="B223" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>470824</v>
+        <v>471228</v>
       </c>
       <c r="R223" t="n">
-        <v>6770523</v>
+        <v>6770667</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24970,50 +24965,45 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129958131</v>
+        <v>129957969</v>
       </c>
       <c r="B224" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
-      <c r="M224" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470869</v>
+        <v>470911</v>
       </c>
       <c r="R224" t="n">
-        <v>6770702</v>
+        <v>6770707</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25082,38 +25072,38 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129959710</v>
+        <v>129957253</v>
       </c>
       <c r="B225" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -25122,10 +25112,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470864</v>
+        <v>470916</v>
       </c>
       <c r="R225" t="n">
-        <v>6770438</v>
+        <v>6770721</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25194,38 +25184,38 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129957253</v>
+        <v>129959441</v>
       </c>
       <c r="B226" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P226" t="inlineStr">
@@ -25234,10 +25224,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>470916</v>
+        <v>470824</v>
       </c>
       <c r="R226" t="n">
-        <v>6770721</v>
+        <v>6770523</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25306,45 +25296,50 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129961818</v>
+        <v>129958131</v>
       </c>
       <c r="B227" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>471228</v>
+        <v>470869</v>
       </c>
       <c r="R227" t="n">
-        <v>6770667</v>
+        <v>6770702</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25413,7 +25408,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129960657</v>
+        <v>129959710</v>
       </c>
       <c r="B228" t="n">
         <v>8451</v>
@@ -25453,10 +25448,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>471025</v>
+        <v>470864</v>
       </c>
       <c r="R228" t="n">
-        <v>6770488</v>
+        <v>6770438</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25525,45 +25520,50 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129957969</v>
+        <v>129960657</v>
       </c>
       <c r="B229" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>470911</v>
+        <v>471025</v>
       </c>
       <c r="R229" t="n">
-        <v>6770707</v>
+        <v>6770488</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25632,10 +25632,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>129959730</v>
+        <v>129960437</v>
       </c>
       <c r="B230" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -25643,39 +25643,34 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P230" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>470868</v>
+        <v>470948</v>
       </c>
       <c r="R230" t="n">
-        <v>6770431</v>
+        <v>6770533</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -25744,10 +25739,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>129960437</v>
+        <v>129959730</v>
       </c>
       <c r="B231" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -25755,34 +25750,39 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P231" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>470948</v>
+        <v>470868</v>
       </c>
       <c r="R231" t="n">
-        <v>6770533</v>
+        <v>6770431</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -25851,7 +25851,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129960691</v>
+        <v>129958151</v>
       </c>
       <c r="B232" t="n">
         <v>79180</v>
@@ -25886,10 +25886,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>471056</v>
+        <v>470842</v>
       </c>
       <c r="R232" t="n">
-        <v>6770494</v>
+        <v>6770709</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25958,7 +25958,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129958151</v>
+        <v>129958795</v>
       </c>
       <c r="B233" t="n">
         <v>79180</v>
@@ -25993,10 +25993,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>470842</v>
+        <v>470822</v>
       </c>
       <c r="R233" t="n">
-        <v>6770709</v>
+        <v>6770615</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26039,6 +26039,11 @@
       <c r="AB233" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC233" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD233" t="b">
@@ -26065,7 +26070,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>129958795</v>
+        <v>129960691</v>
       </c>
       <c r="B234" t="n">
         <v>79180</v>
@@ -26100,10 +26105,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>470822</v>
+        <v>471056</v>
       </c>
       <c r="R234" t="n">
-        <v>6770615</v>
+        <v>6770494</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -26146,11 +26151,6 @@
       <c r="AB234" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC234" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD234" t="b">

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -8056,10 +8056,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129944452</v>
+        <v>129944817</v>
       </c>
       <c r="B68" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8067,39 +8067,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471330</v>
+        <v>471247</v>
       </c>
       <c r="R68" t="n">
-        <v>6770712</v>
+        <v>6770726</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8168,7 +8163,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129944817</v>
+        <v>129944495</v>
       </c>
       <c r="B69" t="n">
         <v>79180</v>
@@ -8203,10 +8198,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471247</v>
+        <v>471288</v>
       </c>
       <c r="R69" t="n">
-        <v>6770726</v>
+        <v>6770728</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8275,7 +8270,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129944495</v>
+        <v>129946062</v>
       </c>
       <c r="B70" t="n">
         <v>79180</v>
@@ -8310,10 +8305,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471288</v>
+        <v>471161</v>
       </c>
       <c r="R70" t="n">
-        <v>6770728</v>
+        <v>6770705</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8382,7 +8377,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129946062</v>
+        <v>129946408</v>
       </c>
       <c r="B71" t="n">
         <v>79180</v>
@@ -8417,10 +8412,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>471161</v>
+        <v>470921</v>
       </c>
       <c r="R71" t="n">
-        <v>6770705</v>
+        <v>6770579</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8489,7 +8484,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129946408</v>
+        <v>129944164</v>
       </c>
       <c r="B72" t="n">
         <v>79180</v>
@@ -8524,10 +8519,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>470921</v>
+        <v>471363</v>
       </c>
       <c r="R72" t="n">
-        <v>6770579</v>
+        <v>6770736</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8596,10 +8591,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129944164</v>
+        <v>129944452</v>
       </c>
       <c r="B73" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8607,34 +8602,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471363</v>
+        <v>471330</v>
       </c>
       <c r="R73" t="n">
-        <v>6770736</v>
+        <v>6770712</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8810,7 +8810,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129946170</v>
+        <v>129946586</v>
       </c>
       <c r="B75" t="n">
         <v>79180</v>
@@ -8845,10 +8845,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471030</v>
+        <v>471095</v>
       </c>
       <c r="R75" t="n">
-        <v>6770688</v>
+        <v>6770660</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8917,7 +8917,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129946586</v>
+        <v>129946170</v>
       </c>
       <c r="B76" t="n">
         <v>79180</v>
@@ -8952,10 +8952,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471095</v>
+        <v>471030</v>
       </c>
       <c r="R76" t="n">
-        <v>6770660</v>
+        <v>6770688</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9564,32 +9564,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129944037</v>
+        <v>129946047</v>
       </c>
       <c r="B82" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471417</v>
+        <v>471161</v>
       </c>
       <c r="R82" t="n">
-        <v>6770738</v>
+        <v>6770705</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9671,7 +9671,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944210</v>
+        <v>129944037</v>
       </c>
       <c r="B83" t="n">
         <v>79180</v>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471390</v>
+        <v>471417</v>
       </c>
       <c r="R83" t="n">
-        <v>6770705</v>
+        <v>6770738</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9778,10 +9778,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129946321</v>
+        <v>129944210</v>
       </c>
       <c r="B84" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9789,39 +9789,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>470871</v>
+        <v>471390</v>
       </c>
       <c r="R84" t="n">
-        <v>6770635</v>
+        <v>6770705</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9890,45 +9885,50 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129946047</v>
+        <v>129946321</v>
       </c>
       <c r="B85" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>471161</v>
+        <v>470871</v>
       </c>
       <c r="R85" t="n">
-        <v>6770705</v>
+        <v>6770635</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10430,45 +10430,50 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129944975</v>
+        <v>129945161</v>
       </c>
       <c r="B90" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471242</v>
+        <v>471198</v>
       </c>
       <c r="R90" t="n">
-        <v>6770682</v>
+        <v>6770725</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10537,7 +10542,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129946708</v>
+        <v>129944975</v>
       </c>
       <c r="B91" t="n">
         <v>79180</v>
@@ -10572,10 +10577,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471171</v>
+        <v>471242</v>
       </c>
       <c r="R91" t="n">
-        <v>6770660</v>
+        <v>6770682</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10644,50 +10649,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129945161</v>
+        <v>129946708</v>
       </c>
       <c r="B92" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471198</v>
+        <v>471171</v>
       </c>
       <c r="R92" t="n">
-        <v>6770725</v>
+        <v>6770660</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11077,10 +11077,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129944878</v>
+        <v>129946391</v>
       </c>
       <c r="B96" t="n">
-        <v>57985</v>
+        <v>57823</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11088,31 +11088,27 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -11121,13 +11117,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>471258</v>
+        <v>470921</v>
       </c>
       <c r="R96" t="n">
-        <v>6770712</v>
+        <v>6770579</v>
       </c>
       <c r="S96" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11193,38 +11189,42 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129946444</v>
+        <v>129944878</v>
       </c>
       <c r="B97" t="n">
-        <v>8451</v>
+        <v>57985</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11233,13 +11233,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>470971</v>
+        <v>471258</v>
       </c>
       <c r="R97" t="n">
-        <v>6770603</v>
+        <v>6770712</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11305,38 +11305,38 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129946391</v>
+        <v>129946444</v>
       </c>
       <c r="B98" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="M98" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
@@ -11345,10 +11345,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>470921</v>
+        <v>470971</v>
       </c>
       <c r="R98" t="n">
-        <v>6770579</v>
+        <v>6770603</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11417,10 +11417,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129945156</v>
+        <v>129944926</v>
       </c>
       <c r="B99" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11428,39 +11428,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471198</v>
+        <v>471263</v>
       </c>
       <c r="R99" t="n">
-        <v>6770725</v>
+        <v>6770694</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11529,7 +11524,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944926</v>
+        <v>129944544</v>
       </c>
       <c r="B100" t="n">
         <v>79180</v>
@@ -11564,10 +11559,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471263</v>
+        <v>471330</v>
       </c>
       <c r="R100" t="n">
-        <v>6770694</v>
+        <v>6770712</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11636,10 +11631,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129944544</v>
+        <v>129945156</v>
       </c>
       <c r="B101" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11647,34 +11642,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471330</v>
+        <v>471198</v>
       </c>
       <c r="R101" t="n">
-        <v>6770712</v>
+        <v>6770725</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12390,10 +12390,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129943849</v>
+        <v>129943541</v>
       </c>
       <c r="B108" t="n">
-        <v>91749</v>
+        <v>79180</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12401,38 +12401,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471451</v>
+        <v>471478</v>
       </c>
       <c r="R108" t="n">
-        <v>6770706</v>
+        <v>6770707</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12501,7 +12497,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129943541</v>
+        <v>129944592</v>
       </c>
       <c r="B109" t="n">
         <v>79180</v>
@@ -12536,10 +12532,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471478</v>
+        <v>471313</v>
       </c>
       <c r="R109" t="n">
-        <v>6770707</v>
+        <v>6770688</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12608,10 +12604,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129944592</v>
+        <v>129943849</v>
       </c>
       <c r="B110" t="n">
-        <v>79180</v>
+        <v>91749</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12619,34 +12615,38 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471313</v>
+        <v>471451</v>
       </c>
       <c r="R110" t="n">
-        <v>6770688</v>
+        <v>6770706</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -14024,50 +14024,45 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129962376</v>
+        <v>129958464</v>
       </c>
       <c r="B123" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>470996</v>
+        <v>470822</v>
       </c>
       <c r="R123" t="n">
-        <v>6770611</v>
+        <v>6770673</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14136,7 +14131,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129959122</v>
+        <v>129959787</v>
       </c>
       <c r="B124" t="n">
         <v>79180</v>
@@ -14171,10 +14166,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>470926</v>
+        <v>470900</v>
       </c>
       <c r="R124" t="n">
-        <v>6770613</v>
+        <v>6770473</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14243,7 +14238,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129959787</v>
+        <v>129960901</v>
       </c>
       <c r="B125" t="n">
         <v>79180</v>
@@ -14278,10 +14273,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>470900</v>
+        <v>471185</v>
       </c>
       <c r="R125" t="n">
-        <v>6770473</v>
+        <v>6770590</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14350,7 +14345,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129960901</v>
+        <v>129960002</v>
       </c>
       <c r="B126" t="n">
         <v>79180</v>
@@ -14385,10 +14380,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>471185</v>
+        <v>470932</v>
       </c>
       <c r="R126" t="n">
-        <v>6770590</v>
+        <v>6770480</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14457,7 +14452,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129960002</v>
+        <v>129957713</v>
       </c>
       <c r="B127" t="n">
         <v>79180</v>
@@ -14492,10 +14487,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470932</v>
+        <v>470904</v>
       </c>
       <c r="R127" t="n">
-        <v>6770480</v>
+        <v>6770718</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14564,7 +14559,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129957713</v>
+        <v>129959479</v>
       </c>
       <c r="B128" t="n">
         <v>79180</v>
@@ -14599,10 +14594,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470904</v>
+        <v>470837</v>
       </c>
       <c r="R128" t="n">
-        <v>6770718</v>
+        <v>6770498</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14671,7 +14666,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129958464</v>
+        <v>129959813</v>
       </c>
       <c r="B129" t="n">
         <v>79180</v>
@@ -14706,10 +14701,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>470822</v>
+        <v>470942</v>
       </c>
       <c r="R129" t="n">
-        <v>6770673</v>
+        <v>6770455</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14778,7 +14773,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129959479</v>
+        <v>129959122</v>
       </c>
       <c r="B130" t="n">
         <v>79180</v>
@@ -14813,10 +14808,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470837</v>
+        <v>470926</v>
       </c>
       <c r="R130" t="n">
-        <v>6770498</v>
+        <v>6770613</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14885,7 +14880,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129959813</v>
+        <v>129958842</v>
       </c>
       <c r="B131" t="n">
         <v>79180</v>
@@ -14920,10 +14915,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470942</v>
+        <v>470820</v>
       </c>
       <c r="R131" t="n">
-        <v>6770455</v>
+        <v>6770624</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14992,7 +14987,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129958842</v>
+        <v>129954413</v>
       </c>
       <c r="B132" t="n">
         <v>79180</v>
@@ -15027,10 +15022,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>470820</v>
+        <v>471028</v>
       </c>
       <c r="R132" t="n">
-        <v>6770624</v>
+        <v>6770675</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15099,10 +15094,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129954413</v>
+        <v>129962374</v>
       </c>
       <c r="B133" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15110,34 +15105,39 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>471028</v>
+        <v>470996</v>
       </c>
       <c r="R133" t="n">
-        <v>6770675</v>
+        <v>6770611</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15206,38 +15206,38 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>129962374</v>
+        <v>129962376</v>
       </c>
       <c r="B134" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P134" t="inlineStr">
@@ -15430,7 +15430,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129955100</v>
+        <v>129959501</v>
       </c>
       <c r="B136" t="n">
         <v>79180</v>
@@ -15465,10 +15465,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470981</v>
+        <v>470807</v>
       </c>
       <c r="R136" t="n">
-        <v>6770691</v>
+        <v>6770491</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15537,7 +15537,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129958010</v>
+        <v>129954531</v>
       </c>
       <c r="B137" t="n">
         <v>79180</v>
@@ -15572,10 +15572,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>470894</v>
+        <v>471106</v>
       </c>
       <c r="R137" t="n">
-        <v>6770713</v>
+        <v>6770683</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15644,7 +15644,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129959047</v>
+        <v>129958895</v>
       </c>
       <c r="B138" t="n">
         <v>79180</v>
@@ -15679,10 +15679,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>470908</v>
+        <v>470887</v>
       </c>
       <c r="R138" t="n">
-        <v>6770622</v>
+        <v>6770658</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15751,7 +15751,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129959501</v>
+        <v>129958499</v>
       </c>
       <c r="B139" t="n">
         <v>79180</v>
@@ -15786,10 +15786,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470807</v>
+        <v>470850</v>
       </c>
       <c r="R139" t="n">
-        <v>6770491</v>
+        <v>6770690</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15858,7 +15858,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129961622</v>
+        <v>129959047</v>
       </c>
       <c r="B140" t="n">
         <v>79180</v>
@@ -15893,7 +15893,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>471262</v>
+        <v>470908</v>
       </c>
       <c r="R140" t="n">
         <v>6770622</v>
@@ -15965,7 +15965,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129954531</v>
+        <v>129955100</v>
       </c>
       <c r="B141" t="n">
         <v>79180</v>
@@ -16000,10 +16000,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>471106</v>
+        <v>470981</v>
       </c>
       <c r="R141" t="n">
-        <v>6770683</v>
+        <v>6770691</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16072,7 +16072,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129958895</v>
+        <v>129961622</v>
       </c>
       <c r="B142" t="n">
         <v>79180</v>
@@ -16107,10 +16107,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>470887</v>
+        <v>471262</v>
       </c>
       <c r="R142" t="n">
-        <v>6770658</v>
+        <v>6770622</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16179,7 +16179,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129958499</v>
+        <v>129958010</v>
       </c>
       <c r="B143" t="n">
         <v>79180</v>
@@ -16214,10 +16214,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>470850</v>
+        <v>470894</v>
       </c>
       <c r="R143" t="n">
-        <v>6770690</v>
+        <v>6770713</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16286,7 +16286,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129959352</v>
+        <v>129962260</v>
       </c>
       <c r="B144" t="n">
         <v>79180</v>
@@ -16321,10 +16321,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>470879</v>
+        <v>471044</v>
       </c>
       <c r="R144" t="n">
-        <v>6770545</v>
+        <v>6770615</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16393,7 +16393,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129962073</v>
+        <v>129959352</v>
       </c>
       <c r="B145" t="n">
         <v>79180</v>
@@ -16428,10 +16428,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>471222</v>
+        <v>470879</v>
       </c>
       <c r="R145" t="n">
-        <v>6770635</v>
+        <v>6770545</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16500,7 +16500,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129962260</v>
+        <v>129958937</v>
       </c>
       <c r="B146" t="n">
         <v>79180</v>
@@ -16535,10 +16535,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>471044</v>
+        <v>470897</v>
       </c>
       <c r="R146" t="n">
-        <v>6770615</v>
+        <v>6770647</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16607,7 +16607,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129958937</v>
+        <v>129958802</v>
       </c>
       <c r="B147" t="n">
         <v>79180</v>
@@ -16642,10 +16642,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470897</v>
+        <v>470858</v>
       </c>
       <c r="R147" t="n">
-        <v>6770647</v>
+        <v>6770602</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16714,45 +16714,50 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129958802</v>
+        <v>129960827</v>
       </c>
       <c r="B148" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>470858</v>
+        <v>471078</v>
       </c>
       <c r="R148" t="n">
-        <v>6770602</v>
+        <v>6770561</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16821,10 +16826,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129962430</v>
+        <v>129962073</v>
       </c>
       <c r="B149" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16832,39 +16837,34 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>470989</v>
+        <v>471222</v>
       </c>
       <c r="R149" t="n">
-        <v>6770629</v>
+        <v>6770635</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16933,7 +16933,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129962343</v>
+        <v>129962430</v>
       </c>
       <c r="B150" t="n">
         <v>57823</v>
@@ -16964,7 +16964,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -16973,10 +16973,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>471017</v>
+        <v>470989</v>
       </c>
       <c r="R150" t="n">
-        <v>6770613</v>
+        <v>6770629</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17045,38 +17045,38 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129960827</v>
+        <v>129962343</v>
       </c>
       <c r="B151" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -17085,10 +17085,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>471078</v>
+        <v>471017</v>
       </c>
       <c r="R151" t="n">
-        <v>6770561</v>
+        <v>6770613</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17157,7 +17157,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>129954803</v>
+        <v>129954534</v>
       </c>
       <c r="B152" t="n">
         <v>79180</v>
@@ -17192,10 +17192,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>470938</v>
+        <v>471086</v>
       </c>
       <c r="R152" t="n">
-        <v>6770693</v>
+        <v>6770684</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17478,7 +17478,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129954534</v>
+        <v>129954803</v>
       </c>
       <c r="B155" t="n">
         <v>79180</v>
@@ -17513,10 +17513,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>471086</v>
+        <v>470938</v>
       </c>
       <c r="R155" t="n">
-        <v>6770684</v>
+        <v>6770693</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17906,7 +17906,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129954445</v>
+        <v>129954452</v>
       </c>
       <c r="B159" t="n">
         <v>79180</v>
@@ -17941,10 +17941,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>471053</v>
+        <v>471058</v>
       </c>
       <c r="R159" t="n">
-        <v>6770682</v>
+        <v>6770677</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18013,7 +18013,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129954452</v>
+        <v>129959519</v>
       </c>
       <c r="B160" t="n">
         <v>79180</v>
@@ -18048,10 +18048,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>471058</v>
+        <v>470822</v>
       </c>
       <c r="R160" t="n">
-        <v>6770677</v>
+        <v>6770452</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18120,7 +18120,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129959519</v>
+        <v>129954442</v>
       </c>
       <c r="B161" t="n">
         <v>79180</v>
@@ -18155,10 +18155,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>470822</v>
+        <v>471053</v>
       </c>
       <c r="R161" t="n">
-        <v>6770452</v>
+        <v>6770682</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18227,10 +18227,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129960642</v>
+        <v>129960763</v>
       </c>
       <c r="B162" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18238,39 +18238,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="M162" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P162" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>471025</v>
+        <v>471062</v>
       </c>
       <c r="R162" t="n">
-        <v>6770488</v>
+        <v>6770538</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18339,10 +18334,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129960763</v>
+        <v>129960642</v>
       </c>
       <c r="B163" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18350,34 +18345,39 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>471062</v>
+        <v>471025</v>
       </c>
       <c r="R163" t="n">
-        <v>6770538</v>
+        <v>6770488</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18446,7 +18446,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129958775</v>
+        <v>129960929</v>
       </c>
       <c r="B164" t="n">
         <v>79180</v>
@@ -18481,10 +18481,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>470803</v>
+        <v>471159</v>
       </c>
       <c r="R164" t="n">
-        <v>6770595</v>
+        <v>6770613</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18553,7 +18553,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129962390</v>
+        <v>129958775</v>
       </c>
       <c r="B165" t="n">
         <v>79180</v>
@@ -18588,10 +18588,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>471004</v>
+        <v>470803</v>
       </c>
       <c r="R165" t="n">
-        <v>6770581</v>
+        <v>6770595</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18660,7 +18660,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129960929</v>
+        <v>129955313</v>
       </c>
       <c r="B166" t="n">
         <v>79180</v>
@@ -18695,10 +18695,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>471159</v>
+        <v>470992</v>
       </c>
       <c r="R166" t="n">
-        <v>6770613</v>
+        <v>6770702</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18767,7 +18767,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129955313</v>
+        <v>129959994</v>
       </c>
       <c r="B167" t="n">
         <v>79180</v>
@@ -18802,10 +18802,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470992</v>
+        <v>470954</v>
       </c>
       <c r="R167" t="n">
-        <v>6770702</v>
+        <v>6770475</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18874,7 +18874,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129959994</v>
+        <v>129958841</v>
       </c>
       <c r="B168" t="n">
         <v>79180</v>
@@ -18909,10 +18909,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>470954</v>
+        <v>470828</v>
       </c>
       <c r="R168" t="n">
-        <v>6770475</v>
+        <v>6770636</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18981,7 +18981,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129958841</v>
+        <v>129962390</v>
       </c>
       <c r="B169" t="n">
         <v>79180</v>
@@ -19016,10 +19016,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>470828</v>
+        <v>471004</v>
       </c>
       <c r="R169" t="n">
-        <v>6770636</v>
+        <v>6770581</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19307,7 +19307,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129962290</v>
+        <v>129962243</v>
       </c>
       <c r="B172" t="n">
         <v>79180</v>
@@ -19342,10 +19342,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>471033</v>
+        <v>471074</v>
       </c>
       <c r="R172" t="n">
-        <v>6770614</v>
+        <v>6770617</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19414,7 +19414,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>129959740</v>
+        <v>129959717</v>
       </c>
       <c r="B173" t="n">
         <v>79180</v>
@@ -19449,10 +19449,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>470905</v>
+        <v>470864</v>
       </c>
       <c r="R173" t="n">
-        <v>6770435</v>
+        <v>6770438</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19521,7 +19521,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129962243</v>
+        <v>129962351</v>
       </c>
       <c r="B174" t="n">
         <v>79180</v>
@@ -19556,10 +19556,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>471074</v>
+        <v>471017</v>
       </c>
       <c r="R174" t="n">
-        <v>6770617</v>
+        <v>6770613</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19628,7 +19628,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129959717</v>
+        <v>129959740</v>
       </c>
       <c r="B175" t="n">
         <v>79180</v>
@@ -19663,10 +19663,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>470864</v>
+        <v>470905</v>
       </c>
       <c r="R175" t="n">
-        <v>6770438</v>
+        <v>6770435</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19735,7 +19735,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129962351</v>
+        <v>129962290</v>
       </c>
       <c r="B176" t="n">
         <v>79180</v>
@@ -19770,10 +19770,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471017</v>
+        <v>471033</v>
       </c>
       <c r="R176" t="n">
-        <v>6770613</v>
+        <v>6770614</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -20178,7 +20178,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>129958214</v>
+        <v>129962443</v>
       </c>
       <c r="B180" t="n">
         <v>79180</v>
@@ -20213,10 +20213,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>470823</v>
+        <v>470989</v>
       </c>
       <c r="R180" t="n">
-        <v>6770705</v>
+        <v>6770629</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -20504,7 +20504,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129962443</v>
+        <v>129958214</v>
       </c>
       <c r="B183" t="n">
         <v>79180</v>
@@ -20539,10 +20539,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>470989</v>
+        <v>470823</v>
       </c>
       <c r="R183" t="n">
-        <v>6770629</v>
+        <v>6770705</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20722,7 +20722,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129962447</v>
+        <v>129960864</v>
       </c>
       <c r="B185" t="n">
         <v>79180</v>
@@ -20757,10 +20757,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>470993</v>
+        <v>471116</v>
       </c>
       <c r="R185" t="n">
-        <v>6770643</v>
+        <v>6770565</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20829,7 +20829,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>129960864</v>
+        <v>129959256</v>
       </c>
       <c r="B186" t="n">
         <v>79180</v>
@@ -20864,10 +20864,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>471116</v>
+        <v>470922</v>
       </c>
       <c r="R186" t="n">
-        <v>6770565</v>
+        <v>6770556</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20936,7 +20936,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129959256</v>
+        <v>129958694</v>
       </c>
       <c r="B187" t="n">
         <v>79180</v>
@@ -20971,10 +20971,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>470922</v>
+        <v>470844</v>
       </c>
       <c r="R187" t="n">
-        <v>6770556</v>
+        <v>6770699</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21043,7 +21043,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>129956859</v>
+        <v>129958228</v>
       </c>
       <c r="B188" t="n">
         <v>79180</v>
@@ -21078,10 +21078,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>470936</v>
+        <v>470813</v>
       </c>
       <c r="R188" t="n">
-        <v>6770721</v>
+        <v>6770681</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -21150,7 +21150,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129958228</v>
+        <v>129962447</v>
       </c>
       <c r="B189" t="n">
         <v>79180</v>
@@ -21185,10 +21185,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>470813</v>
+        <v>470993</v>
       </c>
       <c r="R189" t="n">
-        <v>6770681</v>
+        <v>6770643</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21257,10 +21257,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129959870</v>
+        <v>129956859</v>
       </c>
       <c r="B190" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21268,39 +21268,34 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>470952</v>
+        <v>470936</v>
       </c>
       <c r="R190" t="n">
-        <v>6770464</v>
+        <v>6770721</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21369,10 +21364,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129958694</v>
+        <v>129959870</v>
       </c>
       <c r="B191" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21380,34 +21375,39 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="M191" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P191" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>470844</v>
+        <v>470952</v>
       </c>
       <c r="R191" t="n">
-        <v>6770699</v>
+        <v>6770464</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21476,10 +21476,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129959434</v>
+        <v>129954590</v>
       </c>
       <c r="B192" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21487,39 +21487,34 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
-      <c r="M192" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>470824</v>
+        <v>471013</v>
       </c>
       <c r="R192" t="n">
-        <v>6770523</v>
+        <v>6770715</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21588,38 +21583,38 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129958199</v>
+        <v>129959434</v>
       </c>
       <c r="B193" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -21628,10 +21623,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>470823</v>
+        <v>470824</v>
       </c>
       <c r="R193" t="n">
-        <v>6770705</v>
+        <v>6770523</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21700,7 +21695,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129960746</v>
+        <v>129958199</v>
       </c>
       <c r="B194" t="n">
         <v>8451</v>
@@ -21740,10 +21735,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>471053</v>
+        <v>470823</v>
       </c>
       <c r="R194" t="n">
-        <v>6770528</v>
+        <v>6770705</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21812,45 +21807,50 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129954590</v>
+        <v>129960746</v>
       </c>
       <c r="B195" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>471013</v>
+        <v>471053</v>
       </c>
       <c r="R195" t="n">
-        <v>6770715</v>
+        <v>6770528</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -22026,45 +22026,50 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129959375</v>
+        <v>129962346</v>
       </c>
       <c r="B197" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>470851</v>
+        <v>471017</v>
       </c>
       <c r="R197" t="n">
-        <v>6770520</v>
+        <v>6770613</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22133,10 +22138,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>129959567</v>
+        <v>129956851</v>
       </c>
       <c r="B198" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22144,39 +22149,34 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
-      <c r="M198" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P198" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>470822</v>
+        <v>470928</v>
       </c>
       <c r="R198" t="n">
-        <v>6770452</v>
+        <v>6770695</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -22245,7 +22245,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129956851</v>
+        <v>129959375</v>
       </c>
       <c r="B199" t="n">
         <v>79180</v>
@@ -22280,10 +22280,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>470928</v>
+        <v>470851</v>
       </c>
       <c r="R199" t="n">
-        <v>6770695</v>
+        <v>6770520</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22352,38 +22352,38 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>129959924</v>
+        <v>129959567</v>
       </c>
       <c r="B200" t="n">
-        <v>8451</v>
+        <v>57823</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
       <c r="M200" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P200" t="inlineStr">
@@ -22392,10 +22392,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>470944</v>
+        <v>470822</v>
       </c>
       <c r="R200" t="n">
-        <v>6770458</v>
+        <v>6770452</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22464,7 +22464,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129962346</v>
+        <v>129959924</v>
       </c>
       <c r="B201" t="n">
         <v>8451</v>
@@ -22504,10 +22504,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>471017</v>
+        <v>470944</v>
       </c>
       <c r="R201" t="n">
-        <v>6770613</v>
+        <v>6770458</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -23768,7 +23768,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>129958133</v>
+        <v>129962119</v>
       </c>
       <c r="B213" t="n">
         <v>79180</v>
@@ -23803,10 +23803,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>470869</v>
+        <v>471156</v>
       </c>
       <c r="R213" t="n">
-        <v>6770702</v>
+        <v>6770665</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23875,7 +23875,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129960790</v>
+        <v>129958133</v>
       </c>
       <c r="B214" t="n">
         <v>79180</v>
@@ -23910,10 +23910,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>471073</v>
+        <v>470869</v>
       </c>
       <c r="R214" t="n">
-        <v>6770551</v>
+        <v>6770702</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -24089,7 +24089,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129962119</v>
+        <v>129960790</v>
       </c>
       <c r="B216" t="n">
         <v>79180</v>
@@ -24124,10 +24124,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471156</v>
+        <v>471073</v>
       </c>
       <c r="R216" t="n">
-        <v>6770665</v>
+        <v>6770551</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24420,53 +24420,48 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>129960514</v>
+        <v>129962320</v>
       </c>
       <c r="B219" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
-      <c r="M219" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P219" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>470976</v>
+        <v>471024</v>
       </c>
       <c r="R219" t="n">
-        <v>6770536</v>
+        <v>6770624</v>
       </c>
       <c r="S219" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T219" t="inlineStr">
         <is>
@@ -24532,7 +24527,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>129962320</v>
+        <v>129960823</v>
       </c>
       <c r="B220" t="n">
         <v>79180</v>
@@ -24567,10 +24562,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>471024</v>
+        <v>471078</v>
       </c>
       <c r="R220" t="n">
-        <v>6770624</v>
+        <v>6770561</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24613,6 +24608,11 @@
       <c r="AB220" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC220" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24639,48 +24639,53 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>129960823</v>
+        <v>129960514</v>
       </c>
       <c r="B221" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P221" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>471078</v>
+        <v>470976</v>
       </c>
       <c r="R221" t="n">
-        <v>6770561</v>
+        <v>6770536</v>
       </c>
       <c r="S221" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T221" t="inlineStr">
         <is>
@@ -24720,11 +24725,6 @@
       <c r="AB221" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD221" t="b">

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -8056,10 +8056,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129944817</v>
+        <v>129944452</v>
       </c>
       <c r="B68" t="n">
-        <v>79180</v>
+        <v>57738</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8067,34 +8067,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>471247</v>
+        <v>471330</v>
       </c>
       <c r="R68" t="n">
-        <v>6770726</v>
+        <v>6770712</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8163,32 +8168,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129944495</v>
+        <v>129944454</v>
       </c>
       <c r="B69" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8198,10 +8203,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>471288</v>
+        <v>471330</v>
       </c>
       <c r="R69" t="n">
-        <v>6770728</v>
+        <v>6770712</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8270,10 +8275,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129946062</v>
+        <v>129944817</v>
       </c>
       <c r="B70" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8305,10 +8310,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>471161</v>
+        <v>471247</v>
       </c>
       <c r="R70" t="n">
-        <v>6770705</v>
+        <v>6770726</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8377,10 +8382,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129946408</v>
+        <v>129944495</v>
       </c>
       <c r="B71" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8412,10 +8417,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>470921</v>
+        <v>471288</v>
       </c>
       <c r="R71" t="n">
-        <v>6770579</v>
+        <v>6770728</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8484,10 +8489,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129944164</v>
+        <v>129946062</v>
       </c>
       <c r="B72" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8519,10 +8524,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>471363</v>
+        <v>471161</v>
       </c>
       <c r="R72" t="n">
-        <v>6770736</v>
+        <v>6770705</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8591,10 +8596,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129944452</v>
+        <v>129946408</v>
       </c>
       <c r="B73" t="n">
-        <v>57823</v>
+        <v>79095</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8602,39 +8607,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>471330</v>
+        <v>470921</v>
       </c>
       <c r="R73" t="n">
-        <v>6770712</v>
+        <v>6770579</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8703,32 +8703,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129944454</v>
+        <v>129944164</v>
       </c>
       <c r="B74" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8738,10 +8738,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>471330</v>
+        <v>471363</v>
       </c>
       <c r="R74" t="n">
-        <v>6770712</v>
+        <v>6770736</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8810,10 +8810,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129946586</v>
+        <v>129946170</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8845,10 +8845,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>471095</v>
+        <v>471030</v>
       </c>
       <c r="R75" t="n">
-        <v>6770660</v>
+        <v>6770688</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8917,10 +8917,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129946170</v>
+        <v>129946586</v>
       </c>
       <c r="B76" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8952,10 +8952,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>471030</v>
+        <v>471095</v>
       </c>
       <c r="R76" t="n">
-        <v>6770688</v>
+        <v>6770660</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9027,7 +9027,7 @@
         <v>129944813</v>
       </c>
       <c r="B77" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9134,7 +9134,7 @@
         <v>129944762</v>
       </c>
       <c r="B78" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9241,7 +9241,7 @@
         <v>129946436</v>
       </c>
       <c r="B79" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9353,7 +9353,7 @@
         <v>129945104</v>
       </c>
       <c r="B80" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>129946182</v>
       </c>
       <c r="B81" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9564,32 +9564,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129946047</v>
+        <v>129944037</v>
       </c>
       <c r="B82" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9599,10 +9599,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>471161</v>
+        <v>471417</v>
       </c>
       <c r="R82" t="n">
-        <v>6770705</v>
+        <v>6770738</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9671,10 +9671,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129944037</v>
+        <v>129944210</v>
       </c>
       <c r="B83" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9706,10 +9706,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>471417</v>
+        <v>471390</v>
       </c>
       <c r="R83" t="n">
-        <v>6770738</v>
+        <v>6770705</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9778,10 +9778,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129944210</v>
+        <v>129946321</v>
       </c>
       <c r="B84" t="n">
-        <v>79180</v>
+        <v>57738</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9789,34 +9789,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>471390</v>
+        <v>470871</v>
       </c>
       <c r="R84" t="n">
-        <v>6770705</v>
+        <v>6770635</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9885,50 +9890,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129946321</v>
+        <v>129946047</v>
       </c>
       <c r="B85" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>470871</v>
+        <v>471161</v>
       </c>
       <c r="R85" t="n">
-        <v>6770635</v>
+        <v>6770705</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9997,10 +9997,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129945509</v>
+        <v>129944466</v>
       </c>
       <c r="B86" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10032,10 +10032,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>471198</v>
+        <v>471322</v>
       </c>
       <c r="R86" t="n">
-        <v>6770689</v>
+        <v>6770702</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10078,11 +10078,6 @@
       <c r="AB86" t="inlineStr">
         <is>
           <t>11:17</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10109,10 +10104,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129946029</v>
+        <v>129945509</v>
       </c>
       <c r="B87" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10144,10 +10139,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>471185</v>
+        <v>471198</v>
       </c>
       <c r="R87" t="n">
-        <v>6770690</v>
+        <v>6770689</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10190,6 +10185,11 @@
       <c r="AB87" t="inlineStr">
         <is>
           <t>11:17</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10216,10 +10216,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129944466</v>
+        <v>129946029</v>
       </c>
       <c r="B88" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10251,10 +10251,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>471322</v>
+        <v>471185</v>
       </c>
       <c r="R88" t="n">
-        <v>6770702</v>
+        <v>6770690</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10326,7 +10326,7 @@
         <v>129944473</v>
       </c>
       <c r="B89" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10430,50 +10430,45 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129945161</v>
+        <v>129944975</v>
       </c>
       <c r="B90" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>471198</v>
+        <v>471242</v>
       </c>
       <c r="R90" t="n">
-        <v>6770725</v>
+        <v>6770682</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10542,10 +10537,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129944975</v>
+        <v>129946708</v>
       </c>
       <c r="B91" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10577,10 +10572,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>471242</v>
+        <v>471171</v>
       </c>
       <c r="R91" t="n">
-        <v>6770682</v>
+        <v>6770660</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10649,45 +10644,50 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129946708</v>
+        <v>129945161</v>
       </c>
       <c r="B92" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>471171</v>
+        <v>471198</v>
       </c>
       <c r="R92" t="n">
-        <v>6770660</v>
+        <v>6770725</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10756,10 +10756,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129943855</v>
+        <v>129946391</v>
       </c>
       <c r="B93" t="n">
-        <v>79180</v>
+        <v>57738</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10767,34 +10767,39 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>471451</v>
+        <v>470921</v>
       </c>
       <c r="R93" t="n">
-        <v>6770706</v>
+        <v>6770579</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10863,10 +10868,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129945066</v>
+        <v>129943855</v>
       </c>
       <c r="B94" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10898,10 +10903,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>471239</v>
+        <v>471451</v>
       </c>
       <c r="R94" t="n">
-        <v>6770732</v>
+        <v>6770706</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10970,10 +10975,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129944756</v>
+        <v>129945066</v>
       </c>
       <c r="B95" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11005,10 +11010,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>471288</v>
+        <v>471239</v>
       </c>
       <c r="R95" t="n">
-        <v>6770685</v>
+        <v>6770732</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11077,10 +11082,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129946391</v>
+        <v>129944756</v>
       </c>
       <c r="B96" t="n">
-        <v>57823</v>
+        <v>79095</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11088,39 +11093,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>470921</v>
+        <v>471288</v>
       </c>
       <c r="R96" t="n">
-        <v>6770579</v>
+        <v>6770685</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11192,7 +11192,7 @@
         <v>129944878</v>
       </c>
       <c r="B97" t="n">
-        <v>57985</v>
+        <v>57900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11417,10 +11417,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129944926</v>
+        <v>129945156</v>
       </c>
       <c r="B99" t="n">
-        <v>79180</v>
+        <v>57738</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11428,34 +11428,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>471263</v>
+        <v>471198</v>
       </c>
       <c r="R99" t="n">
-        <v>6770694</v>
+        <v>6770725</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11524,10 +11529,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129944544</v>
+        <v>129944926</v>
       </c>
       <c r="B100" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11559,10 +11564,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>471330</v>
+        <v>471263</v>
       </c>
       <c r="R100" t="n">
-        <v>6770712</v>
+        <v>6770694</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11631,10 +11636,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129945156</v>
+        <v>129944544</v>
       </c>
       <c r="B101" t="n">
-        <v>57823</v>
+        <v>79095</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11642,39 +11647,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>471198</v>
+        <v>471330</v>
       </c>
       <c r="R101" t="n">
-        <v>6770725</v>
+        <v>6770712</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11743,45 +11743,50 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129945457</v>
+        <v>129944062</v>
       </c>
       <c r="B102" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>471189</v>
+        <v>471432</v>
       </c>
       <c r="R102" t="n">
-        <v>6770706</v>
+        <v>6770716</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11850,10 +11855,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129943809</v>
+        <v>129945457</v>
       </c>
       <c r="B103" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11885,10 +11890,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>471447</v>
+        <v>471189</v>
       </c>
       <c r="R103" t="n">
-        <v>6770716</v>
+        <v>6770706</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11957,47 +11962,42 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129944062</v>
+        <v>129943809</v>
       </c>
       <c r="B104" t="n">
-        <v>8451</v>
+        <v>79095</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>471432</v>
+        <v>471447</v>
       </c>
       <c r="R104" t="n">
         <v>6770716</v>
@@ -12072,7 +12072,7 @@
         <v>129943914</v>
       </c>
       <c r="B105" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129944488</v>
+        <v>129944178</v>
       </c>
       <c r="B106" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12211,10 +12211,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>471318</v>
+        <v>471372</v>
       </c>
       <c r="R106" t="n">
-        <v>6770729</v>
+        <v>6770719</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12283,10 +12283,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129944178</v>
+        <v>129943541</v>
       </c>
       <c r="B107" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12318,10 +12318,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>471372</v>
+        <v>471478</v>
       </c>
       <c r="R107" t="n">
-        <v>6770719</v>
+        <v>6770707</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12390,10 +12390,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129943541</v>
+        <v>129944592</v>
       </c>
       <c r="B108" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12425,10 +12425,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>471478</v>
+        <v>471313</v>
       </c>
       <c r="R108" t="n">
-        <v>6770707</v>
+        <v>6770688</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12497,10 +12497,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129944592</v>
+        <v>129943849</v>
       </c>
       <c r="B109" t="n">
-        <v>79180</v>
+        <v>91662</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12508,34 +12508,38 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>471313</v>
+        <v>471451</v>
       </c>
       <c r="R109" t="n">
-        <v>6770688</v>
+        <v>6770706</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12604,10 +12608,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129943849</v>
+        <v>129944488</v>
       </c>
       <c r="B110" t="n">
-        <v>91749</v>
+        <v>79095</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12615,38 +12619,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>471451</v>
+        <v>471318</v>
       </c>
       <c r="R110" t="n">
-        <v>6770706</v>
+        <v>6770729</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12718,7 +12718,7 @@
         <v>129943763</v>
       </c>
       <c r="B111" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>129944804</v>
       </c>
       <c r="B112" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>129946117</v>
       </c>
       <c r="B114" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13151,7 +13151,7 @@
         <v>129943529</v>
       </c>
       <c r="B115" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>129946197</v>
       </c>
       <c r="B116" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13365,7 +13365,7 @@
         <v>129945078</v>
       </c>
       <c r="B117" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13472,7 +13472,7 @@
         <v>129946365</v>
       </c>
       <c r="B118" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13584,7 +13584,7 @@
         <v>129944523</v>
       </c>
       <c r="B119" t="n">
-        <v>79180</v>
+        <v>79095</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>129945440</v>
       </c>
       <c r="B122" t="n">
-        <v>57823</v>
+        <v>57738</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129958464</v>
+        <v>129959787</v>
       </c>
       <c r="B123" t="n">
         <v>79180</v>
@@ -14059,10 +14059,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>470822</v>
+        <v>470900</v>
       </c>
       <c r="R123" t="n">
-        <v>6770673</v>
+        <v>6770473</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14131,7 +14131,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129959787</v>
+        <v>129957713</v>
       </c>
       <c r="B124" t="n">
         <v>79180</v>
@@ -14166,10 +14166,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>470900</v>
+        <v>470904</v>
       </c>
       <c r="R124" t="n">
-        <v>6770473</v>
+        <v>6770718</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14238,7 +14238,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129960901</v>
+        <v>129958842</v>
       </c>
       <c r="B125" t="n">
         <v>79180</v>
@@ -14273,10 +14273,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>471185</v>
+        <v>470820</v>
       </c>
       <c r="R125" t="n">
-        <v>6770590</v>
+        <v>6770624</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14345,7 +14345,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129960002</v>
+        <v>129959479</v>
       </c>
       <c r="B126" t="n">
         <v>79180</v>
@@ -14380,10 +14380,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>470932</v>
+        <v>470837</v>
       </c>
       <c r="R126" t="n">
-        <v>6770480</v>
+        <v>6770498</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14452,7 +14452,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129957713</v>
+        <v>129954413</v>
       </c>
       <c r="B127" t="n">
         <v>79180</v>
@@ -14487,10 +14487,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>470904</v>
+        <v>471028</v>
       </c>
       <c r="R127" t="n">
-        <v>6770718</v>
+        <v>6770675</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14559,7 +14559,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129959479</v>
+        <v>129959122</v>
       </c>
       <c r="B128" t="n">
         <v>79180</v>
@@ -14594,10 +14594,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>470837</v>
+        <v>470926</v>
       </c>
       <c r="R128" t="n">
-        <v>6770498</v>
+        <v>6770613</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14773,7 +14773,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129959122</v>
+        <v>129960002</v>
       </c>
       <c r="B130" t="n">
         <v>79180</v>
@@ -14808,10 +14808,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>470926</v>
+        <v>470932</v>
       </c>
       <c r="R130" t="n">
-        <v>6770613</v>
+        <v>6770480</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14880,7 +14880,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129958842</v>
+        <v>129958464</v>
       </c>
       <c r="B131" t="n">
         <v>79180</v>
@@ -14915,10 +14915,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>470820</v>
+        <v>470822</v>
       </c>
       <c r="R131" t="n">
-        <v>6770624</v>
+        <v>6770673</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14987,7 +14987,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129954413</v>
+        <v>129960901</v>
       </c>
       <c r="B132" t="n">
         <v>79180</v>
@@ -15022,10 +15022,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>471028</v>
+        <v>471185</v>
       </c>
       <c r="R132" t="n">
-        <v>6770675</v>
+        <v>6770590</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15318,50 +15318,45 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>129959110</v>
+        <v>129959501</v>
       </c>
       <c r="B135" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>470926</v>
+        <v>470807</v>
       </c>
       <c r="R135" t="n">
-        <v>6770613</v>
+        <v>6770491</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15430,7 +15425,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>129959501</v>
+        <v>129954531</v>
       </c>
       <c r="B136" t="n">
         <v>79180</v>
@@ -15465,10 +15460,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>470807</v>
+        <v>471106</v>
       </c>
       <c r="R136" t="n">
-        <v>6770491</v>
+        <v>6770683</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15537,7 +15532,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129954531</v>
+        <v>129958010</v>
       </c>
       <c r="B137" t="n">
         <v>79180</v>
@@ -15572,10 +15567,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>471106</v>
+        <v>470894</v>
       </c>
       <c r="R137" t="n">
-        <v>6770683</v>
+        <v>6770713</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15751,7 +15746,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129958499</v>
+        <v>129959047</v>
       </c>
       <c r="B139" t="n">
         <v>79180</v>
@@ -15786,10 +15781,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>470850</v>
+        <v>470908</v>
       </c>
       <c r="R139" t="n">
-        <v>6770690</v>
+        <v>6770622</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15858,7 +15853,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>129959047</v>
+        <v>129961622</v>
       </c>
       <c r="B140" t="n">
         <v>79180</v>
@@ -15893,7 +15888,7 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>470908</v>
+        <v>471262</v>
       </c>
       <c r="R140" t="n">
         <v>6770622</v>
@@ -15965,7 +15960,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>129955100</v>
+        <v>129958499</v>
       </c>
       <c r="B141" t="n">
         <v>79180</v>
@@ -16000,10 +15995,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>470981</v>
+        <v>470850</v>
       </c>
       <c r="R141" t="n">
-        <v>6770691</v>
+        <v>6770690</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16072,7 +16067,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>129961622</v>
+        <v>129955100</v>
       </c>
       <c r="B142" t="n">
         <v>79180</v>
@@ -16107,10 +16102,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>471262</v>
+        <v>470981</v>
       </c>
       <c r="R142" t="n">
-        <v>6770622</v>
+        <v>6770691</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16179,45 +16174,50 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>129958010</v>
+        <v>129959110</v>
       </c>
       <c r="B143" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P143" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>470894</v>
+        <v>470926</v>
       </c>
       <c r="R143" t="n">
-        <v>6770713</v>
+        <v>6770613</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16286,7 +16286,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>129962260</v>
+        <v>129958802</v>
       </c>
       <c r="B144" t="n">
         <v>79180</v>
@@ -16321,10 +16321,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>471044</v>
+        <v>470858</v>
       </c>
       <c r="R144" t="n">
-        <v>6770615</v>
+        <v>6770602</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16393,7 +16393,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>129959352</v>
+        <v>129962260</v>
       </c>
       <c r="B145" t="n">
         <v>79180</v>
@@ -16428,10 +16428,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>470879</v>
+        <v>471044</v>
       </c>
       <c r="R145" t="n">
-        <v>6770545</v>
+        <v>6770615</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16500,7 +16500,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129958937</v>
+        <v>129959352</v>
       </c>
       <c r="B146" t="n">
         <v>79180</v>
@@ -16535,10 +16535,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>470897</v>
+        <v>470879</v>
       </c>
       <c r="R146" t="n">
-        <v>6770647</v>
+        <v>6770545</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16607,7 +16607,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>129958802</v>
+        <v>129958937</v>
       </c>
       <c r="B147" t="n">
         <v>79180</v>
@@ -16642,10 +16642,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>470858</v>
+        <v>470897</v>
       </c>
       <c r="R147" t="n">
-        <v>6770602</v>
+        <v>6770647</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16714,50 +16714,45 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>129960827</v>
+        <v>129962073</v>
       </c>
       <c r="B148" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P148" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>471078</v>
+        <v>471222</v>
       </c>
       <c r="R148" t="n">
-        <v>6770561</v>
+        <v>6770635</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16826,10 +16821,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>129962073</v>
+        <v>129962430</v>
       </c>
       <c r="B149" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16837,34 +16832,39 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P149" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>471222</v>
+        <v>470989</v>
       </c>
       <c r="R149" t="n">
-        <v>6770635</v>
+        <v>6770629</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16933,7 +16933,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>129962430</v>
+        <v>129962343</v>
       </c>
       <c r="B150" t="n">
         <v>57823</v>
@@ -16964,7 +16964,7 @@
       <c r="I150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P150" t="inlineStr">
@@ -16973,10 +16973,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>470989</v>
+        <v>471017</v>
       </c>
       <c r="R150" t="n">
-        <v>6770629</v>
+        <v>6770613</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17045,38 +17045,38 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>129962343</v>
+        <v>129960827</v>
       </c>
       <c r="B151" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P151" t="inlineStr">
@@ -17085,10 +17085,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>471017</v>
+        <v>471078</v>
       </c>
       <c r="R151" t="n">
-        <v>6770613</v>
+        <v>6770561</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17264,7 +17264,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>129958545</v>
+        <v>129954803</v>
       </c>
       <c r="B153" t="n">
         <v>79180</v>
@@ -17299,10 +17299,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>470877</v>
+        <v>470938</v>
       </c>
       <c r="R153" t="n">
-        <v>6770687</v>
+        <v>6770693</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17478,7 +17478,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>129954803</v>
+        <v>129959294</v>
       </c>
       <c r="B155" t="n">
         <v>79180</v>
@@ -17513,10 +17513,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>470938</v>
+        <v>470904</v>
       </c>
       <c r="R155" t="n">
-        <v>6770693</v>
+        <v>6770537</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17585,7 +17585,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>129959294</v>
+        <v>129958545</v>
       </c>
       <c r="B156" t="n">
         <v>79180</v>
@@ -17620,10 +17620,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>470904</v>
+        <v>470877</v>
       </c>
       <c r="R156" t="n">
-        <v>6770537</v>
+        <v>6770687</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17692,7 +17692,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>129958754</v>
+        <v>129960763</v>
       </c>
       <c r="B157" t="n">
         <v>79180</v>
@@ -17727,10 +17727,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>470817</v>
+        <v>471062</v>
       </c>
       <c r="R157" t="n">
-        <v>6770608</v>
+        <v>6770538</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17799,7 +17799,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>129959389</v>
+        <v>129958754</v>
       </c>
       <c r="B158" t="n">
         <v>79180</v>
@@ -17834,10 +17834,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>470824</v>
+        <v>470817</v>
       </c>
       <c r="R158" t="n">
-        <v>6770523</v>
+        <v>6770608</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17906,10 +17906,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>129954452</v>
+        <v>129960642</v>
       </c>
       <c r="B159" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17917,34 +17917,39 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P159" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>471058</v>
+        <v>471025</v>
       </c>
       <c r="R159" t="n">
-        <v>6770677</v>
+        <v>6770488</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18013,7 +18018,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>129959519</v>
+        <v>129959389</v>
       </c>
       <c r="B160" t="n">
         <v>79180</v>
@@ -18048,10 +18053,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>470822</v>
+        <v>470824</v>
       </c>
       <c r="R160" t="n">
-        <v>6770452</v>
+        <v>6770523</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18120,7 +18125,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>129954442</v>
+        <v>129959519</v>
       </c>
       <c r="B161" t="n">
         <v>79180</v>
@@ -18155,10 +18160,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>471053</v>
+        <v>470822</v>
       </c>
       <c r="R161" t="n">
-        <v>6770682</v>
+        <v>6770452</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18227,7 +18232,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129960763</v>
+        <v>129954452</v>
       </c>
       <c r="B162" t="n">
         <v>79180</v>
@@ -18262,10 +18267,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>471062</v>
+        <v>471058</v>
       </c>
       <c r="R162" t="n">
-        <v>6770538</v>
+        <v>6770677</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18334,10 +18339,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129960642</v>
+        <v>129954442</v>
       </c>
       <c r="B163" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18345,39 +18350,34 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
-      <c r="M163" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P163" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>471025</v>
+        <v>471053</v>
       </c>
       <c r="R163" t="n">
-        <v>6770488</v>
+        <v>6770682</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18446,10 +18446,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>129960929</v>
+        <v>129954441</v>
       </c>
       <c r="B164" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18457,34 +18457,39 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P164" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>471159</v>
+        <v>471052</v>
       </c>
       <c r="R164" t="n">
-        <v>6770613</v>
+        <v>6770696</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18553,7 +18558,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>129958775</v>
+        <v>129955313</v>
       </c>
       <c r="B165" t="n">
         <v>79180</v>
@@ -18588,10 +18593,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>470803</v>
+        <v>470992</v>
       </c>
       <c r="R165" t="n">
-        <v>6770595</v>
+        <v>6770702</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18660,7 +18665,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>129955313</v>
+        <v>129960929</v>
       </c>
       <c r="B166" t="n">
         <v>79180</v>
@@ -18695,10 +18700,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>470992</v>
+        <v>471159</v>
       </c>
       <c r="R166" t="n">
-        <v>6770702</v>
+        <v>6770613</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18767,7 +18772,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>129959994</v>
+        <v>129958466</v>
       </c>
       <c r="B167" t="n">
         <v>79180</v>
@@ -18802,10 +18807,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>470954</v>
+        <v>470812</v>
       </c>
       <c r="R167" t="n">
-        <v>6770475</v>
+        <v>6770670</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18874,7 +18879,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>129958841</v>
+        <v>129958775</v>
       </c>
       <c r="B168" t="n">
         <v>79180</v>
@@ -18909,10 +18914,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>470828</v>
+        <v>470803</v>
       </c>
       <c r="R168" t="n">
-        <v>6770636</v>
+        <v>6770595</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18981,7 +18986,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129962390</v>
+        <v>129958841</v>
       </c>
       <c r="B169" t="n">
         <v>79180</v>
@@ -19016,10 +19021,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>471004</v>
+        <v>470828</v>
       </c>
       <c r="R169" t="n">
-        <v>6770581</v>
+        <v>6770636</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19088,7 +19093,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>129958466</v>
+        <v>129959994</v>
       </c>
       <c r="B170" t="n">
         <v>79180</v>
@@ -19123,10 +19128,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>470812</v>
+        <v>470954</v>
       </c>
       <c r="R170" t="n">
-        <v>6770670</v>
+        <v>6770475</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19195,10 +19200,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>129954441</v>
+        <v>129962390</v>
       </c>
       <c r="B171" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19206,39 +19211,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
-      <c r="M171" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P171" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>471052</v>
+        <v>471004</v>
       </c>
       <c r="R171" t="n">
-        <v>6770696</v>
+        <v>6770581</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19307,45 +19307,50 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>129962243</v>
+        <v>129959579</v>
       </c>
       <c r="B172" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P172" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>471074</v>
+        <v>470822</v>
       </c>
       <c r="R172" t="n">
-        <v>6770617</v>
+        <v>6770452</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19521,7 +19526,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>129962351</v>
+        <v>129959740</v>
       </c>
       <c r="B174" t="n">
         <v>79180</v>
@@ -19556,10 +19561,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>471017</v>
+        <v>470905</v>
       </c>
       <c r="R174" t="n">
-        <v>6770613</v>
+        <v>6770435</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19628,7 +19633,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>129959740</v>
+        <v>129962290</v>
       </c>
       <c r="B175" t="n">
         <v>79180</v>
@@ -19663,10 +19668,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>470905</v>
+        <v>471033</v>
       </c>
       <c r="R175" t="n">
-        <v>6770435</v>
+        <v>6770614</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19735,7 +19740,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>129962290</v>
+        <v>129962243</v>
       </c>
       <c r="B176" t="n">
         <v>79180</v>
@@ -19770,10 +19775,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>471033</v>
+        <v>471074</v>
       </c>
       <c r="R176" t="n">
-        <v>6770614</v>
+        <v>6770617</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19842,50 +19847,45 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>129959285</v>
+        <v>129962351</v>
       </c>
       <c r="B177" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
-      <c r="M177" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P177" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>470922</v>
+        <v>471017</v>
       </c>
       <c r="R177" t="n">
-        <v>6770556</v>
+        <v>6770613</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19954,7 +19954,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>129962436</v>
+        <v>129959285</v>
       </c>
       <c r="B178" t="n">
         <v>8451</v>
@@ -19994,10 +19994,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>470989</v>
+        <v>470922</v>
       </c>
       <c r="R178" t="n">
-        <v>6770629</v>
+        <v>6770556</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -20066,7 +20066,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>129959579</v>
+        <v>129962436</v>
       </c>
       <c r="B179" t="n">
         <v>8451</v>
@@ -20106,10 +20106,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>470822</v>
+        <v>470989</v>
       </c>
       <c r="R179" t="n">
-        <v>6770452</v>
+        <v>6770629</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -20285,7 +20285,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>129961937</v>
+        <v>129958214</v>
       </c>
       <c r="B181" t="n">
         <v>79180</v>
@@ -20320,10 +20320,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>471216</v>
+        <v>470823</v>
       </c>
       <c r="R181" t="n">
-        <v>6770650</v>
+        <v>6770705</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20392,50 +20392,45 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>129961109</v>
+        <v>129961937</v>
       </c>
       <c r="B182" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
-      <c r="M182" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P182" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>471175</v>
+        <v>471216</v>
       </c>
       <c r="R182" t="n">
-        <v>6770631</v>
+        <v>6770650</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20504,45 +20499,50 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>129958214</v>
+        <v>129961109</v>
       </c>
       <c r="B183" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P183" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>470823</v>
+        <v>471175</v>
       </c>
       <c r="R183" t="n">
-        <v>6770705</v>
+        <v>6770631</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20611,10 +20611,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>129959667</v>
+        <v>129962447</v>
       </c>
       <c r="B184" t="n">
-        <v>91749</v>
+        <v>79180</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20622,38 +20622,34 @@
         </is>
       </c>
       <c r="E184" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>470864</v>
+        <v>470993</v>
       </c>
       <c r="R184" t="n">
-        <v>6770438</v>
+        <v>6770643</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20722,7 +20718,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>129960864</v>
+        <v>129958694</v>
       </c>
       <c r="B185" t="n">
         <v>79180</v>
@@ -20757,10 +20753,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>471116</v>
+        <v>470844</v>
       </c>
       <c r="R185" t="n">
-        <v>6770565</v>
+        <v>6770699</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20936,7 +20932,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>129958694</v>
+        <v>129956859</v>
       </c>
       <c r="B187" t="n">
         <v>79180</v>
@@ -20971,10 +20967,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>470844</v>
+        <v>470936</v>
       </c>
       <c r="R187" t="n">
-        <v>6770699</v>
+        <v>6770721</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -21150,7 +21146,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>129962447</v>
+        <v>129960864</v>
       </c>
       <c r="B189" t="n">
         <v>79180</v>
@@ -21185,10 +21181,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>470993</v>
+        <v>471116</v>
       </c>
       <c r="R189" t="n">
-        <v>6770643</v>
+        <v>6770565</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -21257,10 +21253,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>129956859</v>
+        <v>129959870</v>
       </c>
       <c r="B190" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21268,34 +21264,39 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P190" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>470936</v>
+        <v>470952</v>
       </c>
       <c r="R190" t="n">
-        <v>6770721</v>
+        <v>6770464</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21364,10 +21365,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>129959870</v>
+        <v>129959667</v>
       </c>
       <c r="B191" t="n">
-        <v>57823</v>
+        <v>91749</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21375,27 +21376,26 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr"/>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>2</t>
         </is>
       </c>
       <c r="P191" t="inlineStr">
@@ -21404,10 +21404,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>470952</v>
+        <v>470864</v>
       </c>
       <c r="R191" t="n">
-        <v>6770464</v>
+        <v>6770438</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21476,10 +21476,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>129954590</v>
+        <v>129959434</v>
       </c>
       <c r="B192" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21487,34 +21487,39 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P192" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>471013</v>
+        <v>470824</v>
       </c>
       <c r="R192" t="n">
-        <v>6770715</v>
+        <v>6770523</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21583,38 +21588,38 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>129959434</v>
+        <v>129958199</v>
       </c>
       <c r="B193" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
       <c r="M193" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P193" t="inlineStr">
@@ -21623,10 +21628,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>470824</v>
+        <v>470823</v>
       </c>
       <c r="R193" t="n">
-        <v>6770523</v>
+        <v>6770705</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21695,7 +21700,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>129958199</v>
+        <v>129960746</v>
       </c>
       <c r="B194" t="n">
         <v>8451</v>
@@ -21735,10 +21740,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>470823</v>
+        <v>471053</v>
       </c>
       <c r="R194" t="n">
-        <v>6770705</v>
+        <v>6770528</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21807,50 +21812,45 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>129960746</v>
+        <v>129954590</v>
       </c>
       <c r="B195" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
-      <c r="M195" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P195" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>471053</v>
+        <v>471013</v>
       </c>
       <c r="R195" t="n">
-        <v>6770528</v>
+        <v>6770715</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21919,7 +21919,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>129960891</v>
+        <v>129959375</v>
       </c>
       <c r="B196" t="n">
         <v>79180</v>
@@ -21954,10 +21954,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>471147</v>
+        <v>470851</v>
       </c>
       <c r="R196" t="n">
-        <v>6770575</v>
+        <v>6770520</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -22026,50 +22026,45 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>129962346</v>
+        <v>129960891</v>
       </c>
       <c r="B197" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
-      <c r="M197" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P197" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>471017</v>
+        <v>471147</v>
       </c>
       <c r="R197" t="n">
-        <v>6770613</v>
+        <v>6770575</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -22245,45 +22240,50 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>129959375</v>
+        <v>129959924</v>
       </c>
       <c r="B199" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P199" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>470851</v>
+        <v>470944</v>
       </c>
       <c r="R199" t="n">
-        <v>6770520</v>
+        <v>6770458</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22464,7 +22464,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>129959924</v>
+        <v>129962346</v>
       </c>
       <c r="B201" t="n">
         <v>8451</v>
@@ -22504,10 +22504,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>470944</v>
+        <v>471017</v>
       </c>
       <c r="R201" t="n">
-        <v>6770458</v>
+        <v>6770613</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22576,7 +22576,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>129958828</v>
+        <v>129960843</v>
       </c>
       <c r="B202" t="n">
         <v>79180</v>
@@ -22611,10 +22611,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>470871</v>
+        <v>471097</v>
       </c>
       <c r="R202" t="n">
-        <v>6770635</v>
+        <v>6770561</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22683,7 +22683,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>129960843</v>
+        <v>129958828</v>
       </c>
       <c r="B203" t="n">
         <v>79180</v>
@@ -22718,10 +22718,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>471097</v>
+        <v>470871</v>
       </c>
       <c r="R203" t="n">
-        <v>6770561</v>
+        <v>6770635</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22790,10 +22790,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>129962379</v>
+        <v>129958691</v>
       </c>
       <c r="B204" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22801,34 +22801,39 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P204" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>470996</v>
+        <v>470844</v>
       </c>
       <c r="R204" t="n">
-        <v>6770611</v>
+        <v>6770699</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22897,45 +22902,50 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>129962224</v>
+        <v>129954662</v>
       </c>
       <c r="B205" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P205" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>471098</v>
+        <v>470941</v>
       </c>
       <c r="R205" t="n">
-        <v>6770634</v>
+        <v>6770708</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -23004,38 +23014,38 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>129958691</v>
+        <v>129959223</v>
       </c>
       <c r="B206" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
       <c r="M206" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P206" t="inlineStr">
@@ -23044,10 +23054,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>470844</v>
+        <v>470921</v>
       </c>
       <c r="R206" t="n">
-        <v>6770699</v>
+        <v>6770579</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -23116,50 +23126,45 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>129954662</v>
+        <v>129962379</v>
       </c>
       <c r="B207" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
-      <c r="M207" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P207" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>470941</v>
+        <v>470996</v>
       </c>
       <c r="R207" t="n">
-        <v>6770708</v>
+        <v>6770611</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -23228,50 +23233,45 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>129959223</v>
+        <v>129962224</v>
       </c>
       <c r="B208" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
-      <c r="M208" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P208" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>470921</v>
+        <v>471098</v>
       </c>
       <c r="R208" t="n">
-        <v>6770579</v>
+        <v>6770634</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23340,7 +23340,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>129962417</v>
+        <v>129958706</v>
       </c>
       <c r="B209" t="n">
         <v>79180</v>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>471002</v>
+        <v>470816</v>
       </c>
       <c r="R209" t="n">
-        <v>6770618</v>
+        <v>6770646</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23447,7 +23447,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>129960884</v>
+        <v>129962417</v>
       </c>
       <c r="B210" t="n">
         <v>79180</v>
@@ -23482,10 +23482,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>471129</v>
+        <v>471002</v>
       </c>
       <c r="R210" t="n">
-        <v>6770567</v>
+        <v>6770618</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23554,7 +23554,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>129958706</v>
+        <v>129960884</v>
       </c>
       <c r="B211" t="n">
         <v>79180</v>
@@ -23589,10 +23589,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>470816</v>
+        <v>471129</v>
       </c>
       <c r="R211" t="n">
-        <v>6770646</v>
+        <v>6770567</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23661,45 +23661,50 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>129956843</v>
+        <v>129959735</v>
       </c>
       <c r="B212" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P212" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>470953</v>
+        <v>470868</v>
       </c>
       <c r="R212" t="n">
-        <v>6770692</v>
+        <v>6770431</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23875,7 +23880,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>129958133</v>
+        <v>129954584</v>
       </c>
       <c r="B214" t="n">
         <v>79180</v>
@@ -23910,10 +23915,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>470869</v>
+        <v>471062</v>
       </c>
       <c r="R214" t="n">
-        <v>6770702</v>
+        <v>6770731</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23982,7 +23987,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>129954584</v>
+        <v>129956843</v>
       </c>
       <c r="B215" t="n">
         <v>79180</v>
@@ -24017,10 +24022,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>471062</v>
+        <v>470953</v>
       </c>
       <c r="R215" t="n">
-        <v>6770731</v>
+        <v>6770692</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -24089,7 +24094,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>129960790</v>
+        <v>129958133</v>
       </c>
       <c r="B216" t="n">
         <v>79180</v>
@@ -24124,10 +24129,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>471073</v>
+        <v>470869</v>
       </c>
       <c r="R216" t="n">
-        <v>6770551</v>
+        <v>6770702</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -24196,50 +24201,45 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>129959735</v>
+        <v>129960790</v>
       </c>
       <c r="B217" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P217" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>470868</v>
+        <v>471073</v>
       </c>
       <c r="R217" t="n">
-        <v>6770431</v>
+        <v>6770551</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24751,10 +24751,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>129959250</v>
+        <v>129957253</v>
       </c>
       <c r="B222" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -24762,34 +24762,39 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P222" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>470943</v>
+        <v>470916</v>
       </c>
       <c r="R222" t="n">
-        <v>6770559</v>
+        <v>6770721</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24858,45 +24863,50 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>129961818</v>
+        <v>129959441</v>
       </c>
       <c r="B223" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P223" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>471228</v>
+        <v>470824</v>
       </c>
       <c r="R223" t="n">
-        <v>6770667</v>
+        <v>6770523</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24965,45 +24975,50 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>129957969</v>
+        <v>129958131</v>
       </c>
       <c r="B224" t="n">
-        <v>79180</v>
+        <v>8451</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P224" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>470911</v>
+        <v>470869</v>
       </c>
       <c r="R224" t="n">
-        <v>6770707</v>
+        <v>6770702</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -25072,38 +25087,38 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>129957253</v>
+        <v>129959710</v>
       </c>
       <c r="B225" t="n">
-        <v>57823</v>
+        <v>8451</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
       <c r="M225" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P225" t="inlineStr">
@@ -25112,10 +25127,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>470916</v>
+        <v>470864</v>
       </c>
       <c r="R225" t="n">
-        <v>6770721</v>
+        <v>6770438</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -25184,7 +25199,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>129959441</v>
+        <v>129960657</v>
       </c>
       <c r="B226" t="n">
         <v>8451</v>
@@ -25224,10 +25239,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>470824</v>
+        <v>471025</v>
       </c>
       <c r="R226" t="n">
-        <v>6770523</v>
+        <v>6770488</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -25296,50 +25311,45 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>129958131</v>
+        <v>129961818</v>
       </c>
       <c r="B227" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P227" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>470869</v>
+        <v>471228</v>
       </c>
       <c r="R227" t="n">
-        <v>6770702</v>
+        <v>6770667</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25408,50 +25418,45 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>129959710</v>
+        <v>129957969</v>
       </c>
       <c r="B228" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P228" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>470864</v>
+        <v>470911</v>
       </c>
       <c r="R228" t="n">
-        <v>6770438</v>
+        <v>6770707</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25520,50 +25525,45 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>129960657</v>
+        <v>129959250</v>
       </c>
       <c r="B229" t="n">
-        <v>8451</v>
+        <v>79180</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P229" t="inlineStr">
         <is>
           <t>Svenlindor, Dlr</t>
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>471025</v>
+        <v>470943</v>
       </c>
       <c r="R229" t="n">
-        <v>6770488</v>
+        <v>6770559</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -25851,7 +25851,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>129958151</v>
+        <v>129958795</v>
       </c>
       <c r="B232" t="n">
         <v>79180</v>
@@ -25886,10 +25886,10 @@
         </is>
       </c>
       <c r="Q232" t="n">
-        <v>470842</v>
+        <v>470822</v>
       </c>
       <c r="R232" t="n">
-        <v>6770709</v>
+        <v>6770615</v>
       </c>
       <c r="S232" t="n">
         <v>10</v>
@@ -25932,6 +25932,11 @@
       <c r="AB232" t="inlineStr">
         <is>
           <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC232" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD232" t="b">
@@ -25958,7 +25963,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>129958795</v>
+        <v>129958151</v>
       </c>
       <c r="B233" t="n">
         <v>79180</v>
@@ -25993,10 +25998,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>470822</v>
+        <v>470842</v>
       </c>
       <c r="R233" t="n">
-        <v>6770615</v>
+        <v>6770709</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -26039,11 +26044,6 @@
       <c r="AB233" t="inlineStr">
         <is>
           <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC233" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD233" t="b">

--- a/artfynd/A 54991-2025 artfynd.xlsx
+++ b/artfynd/A 54991-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY255"/>
+  <dimension ref="A1:AZ255"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96004174</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714962</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714992</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714989</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1216,6 +1241,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79630978</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1350,6 +1380,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79630988</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1484,6 +1519,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79630998</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1581,6 +1621,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714922</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1678,6 +1723,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714925</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1775,6 +1825,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714949</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1872,6 +1927,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714969</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1969,6 +2029,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714983</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2066,6 +2131,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714990</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2163,6 +2233,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715011</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2260,6 +2335,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2371,6 +2451,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/559589</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2482,6 +2567,11 @@
           <t>Åtgärdsprogram för hotade arter</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/559590</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2615,6 +2705,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73388500</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2712,6 +2807,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714917</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2809,6 +2909,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714918</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2906,6 +3011,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714919</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3003,6 +3113,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714920</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3100,6 +3215,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714926</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3197,6 +3317,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714927</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3294,6 +3419,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714928</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3391,6 +3521,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714931</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3488,6 +3623,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714936</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3585,6 +3725,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714939</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3682,6 +3827,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714951</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3779,6 +3929,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714955</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3876,6 +4031,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714963</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3973,6 +4133,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714965</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4070,6 +4235,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714966</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4167,6 +4337,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714970</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4264,6 +4439,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714972</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4361,6 +4541,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714978</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4458,6 +4643,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714985</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4555,6 +4745,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714986</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4652,6 +4847,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714993</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4749,6 +4949,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714997</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4846,6 +5051,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715000</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4943,6 +5153,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715002</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5040,6 +5255,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715008</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5137,6 +5357,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715009</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5234,6 +5459,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715013</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5331,6 +5561,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715016</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5428,6 +5663,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715018</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5525,6 +5765,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715019</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5622,6 +5867,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714976</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5719,6 +5969,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714921</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5816,6 +6071,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714930</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5913,6 +6173,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714934</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6010,6 +6275,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714943</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6107,6 +6377,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714950</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6204,6 +6479,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714958</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6301,6 +6581,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714967</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6398,6 +6683,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714977</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6495,6 +6785,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714980</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6592,6 +6887,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714987</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6689,6 +6989,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715006</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6786,6 +7091,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714971</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6883,6 +7193,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714979</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6994,6 +7309,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129943849</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7105,6 +7425,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944262</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7216,6 +7541,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959667</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7313,6 +7643,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714915</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7410,6 +7745,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714991</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7507,6 +7847,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714961</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7604,6 +7949,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715014</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7701,6 +8051,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715007</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7808,6 +8163,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129943529</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7915,6 +8275,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129943541</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8022,6 +8387,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129943580</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8129,6 +8499,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129943763</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8236,6 +8611,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129943809</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8343,6 +8723,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129943855</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8450,6 +8835,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129943914</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8557,6 +8947,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129943999</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8664,6 +9059,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944026</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8771,6 +9171,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944037</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8878,6 +9283,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944164</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8985,6 +9395,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944178</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9092,6 +9507,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944210</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9199,6 +9619,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944228</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9306,6 +9731,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944311</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9413,6 +9843,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944355</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9520,6 +9955,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944466</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9627,6 +10067,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944473</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9734,6 +10179,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944488</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9841,6 +10291,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944495</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9948,6 +10403,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944523</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10055,6 +10515,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944544</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10162,6 +10627,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944592</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10269,6 +10739,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944756</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10376,6 +10851,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944762</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10483,6 +10963,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944804</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10590,6 +11075,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944807</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10697,6 +11187,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944809</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10804,6 +11299,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944917</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10911,6 +11411,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944975</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11018,6 +11523,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945066</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11125,6 +11635,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945078</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11232,6 +11747,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945104</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11339,6 +11859,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945451</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11451,6 +11976,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945509</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11558,6 +12088,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946029</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11665,6 +12200,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946053</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11772,6 +12312,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946117</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11879,6 +12424,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946170</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11986,6 +12536,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946182</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12093,6 +12648,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946197</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12200,6 +12760,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946408</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12307,6 +12872,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946586</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12414,6 +12984,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946708</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12521,6 +13096,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129954408</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12628,6 +13208,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129954413</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12735,6 +13320,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129954442</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12842,6 +13432,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129954452</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12949,6 +13544,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129954531</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13056,6 +13656,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129954534</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13163,6 +13768,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129954584</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13270,6 +13880,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129954590</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13377,6 +13992,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129954674</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13484,6 +14104,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129955100</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13591,6 +14216,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129955313</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13698,6 +14328,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129956843</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13805,6 +14440,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129956851</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13912,6 +14552,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129956859</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14019,6 +14664,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129957713</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14126,6 +14776,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129957969</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14233,6 +14888,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958010</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14340,6 +15000,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958133</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14447,6 +15112,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958151</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14554,6 +15224,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958214</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14661,6 +15336,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958228</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14768,6 +15448,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958464</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14875,6 +15560,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958466</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14982,6 +15672,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958499</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15089,6 +15784,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958545</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15196,6 +15896,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958694</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15303,6 +16008,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958706</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15410,6 +16120,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958754</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15517,6 +16232,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958775</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15629,6 +16349,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958795</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15736,6 +16461,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958800</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15843,6 +16573,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958828</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15950,6 +16685,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958841</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16057,6 +16797,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958842</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16164,6 +16909,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958895</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16271,6 +17021,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958937</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16378,6 +17133,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959037</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16485,6 +17245,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959060</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16592,6 +17357,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959250</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16699,6 +17469,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959256</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16806,6 +17581,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959294</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16913,6 +17693,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959303</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17020,6 +17805,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959375</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17127,6 +17917,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959389</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17234,6 +18029,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959479</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17341,6 +18141,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959501</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17448,6 +18253,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959519</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17555,6 +18365,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959692</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17662,6 +18477,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959740</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17769,6 +18589,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959772</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17876,6 +18701,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959808</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -17983,6 +18813,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959994</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18090,6 +18925,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960002</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18197,6 +19037,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960437</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18304,6 +19149,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960691</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18411,6 +19261,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960763</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18518,6 +19373,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960790</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18630,6 +19490,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960823</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18737,6 +19602,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960843</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18844,6 +19714,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960864</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18951,6 +19826,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960884</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19058,6 +19938,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960891</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19165,6 +20050,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960901</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19272,6 +20162,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960929</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19379,6 +20274,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129961603</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19486,6 +20386,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129961818</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19593,6 +20498,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129961937</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19700,6 +20610,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962073</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19807,6 +20722,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962119</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19914,6 +20834,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962224</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20021,6 +20946,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962243</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20128,6 +21058,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962260</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20235,6 +21170,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962290</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20342,6 +21282,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962320</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20449,6 +21394,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962351</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20556,6 +21506,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962379</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20663,6 +21618,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962390</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20770,6 +21730,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962417</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20877,6 +21842,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962443</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20984,6 +21954,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962446</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21096,6 +22071,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944452</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21208,6 +22188,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945156</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21320,6 +22305,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945440</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21432,6 +22422,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946321</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21544,6 +22539,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946365</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21656,6 +22656,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946391</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21768,6 +22773,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946436</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21880,6 +22890,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129954441</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21992,6 +23007,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129957253</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22104,6 +23124,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958691</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22216,6 +23241,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959434</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22328,6 +23358,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959567</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22440,6 +23475,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959730</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22552,6 +23592,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959870</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22664,6 +23709,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960642</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22776,6 +23826,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962343</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22888,6 +23943,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962374</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23000,6 +24060,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962430</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23116,6 +24181,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944878</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23228,6 +24298,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944062</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23340,6 +24415,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944158</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23447,6 +24527,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129944454</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23559,6 +24644,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945161</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23671,6 +24761,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129945444</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23778,6 +24873,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946047</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -23890,6 +24990,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946334</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24002,6 +25107,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129946444</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24114,6 +25224,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129954662</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24226,6 +25341,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958131</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24338,6 +25458,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958199</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24450,6 +25575,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129958686</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24562,6 +25692,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959110</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24674,6 +25809,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959223</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24786,6 +25926,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959285</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24898,6 +26043,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959441</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25010,6 +26160,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959579</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25122,6 +26277,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959710</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25234,6 +26394,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959735</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -25346,6 +26511,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129959924</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25458,6 +26628,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960514</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25570,6 +26745,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960657</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25682,6 +26862,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960746</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25794,6 +26979,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129960827</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25906,6 +27096,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129961109</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -26018,6 +27213,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962346</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -26130,6 +27330,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962376</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -26242,6 +27447,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129962436</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -26343,6 +27553,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129271581</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -26440,6 +27655,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714923</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26537,6 +27757,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714929</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26634,6 +27859,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714933</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26731,6 +27961,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714941</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26828,6 +28063,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714946</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -26925,6 +28165,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714952</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -27022,6 +28267,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714953</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -27119,6 +28369,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714960</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -27216,6 +28471,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714973</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -27313,6 +28573,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96714981</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -27410,6 +28675,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715005</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27507,8 +28777,269 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96715010</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>